--- a/進捗確認.xlsx
+++ b/進捗確認.xlsx
@@ -6083,10 +6083,12 @@
           <t>戦略機種(Pt)</t>
         </is>
       </c>
-      <c r="D14" s="28" t="n"/>
+      <c r="D14" s="28" t="n">
+        <v>849</v>
+      </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>目標Pt未設定(要入力)/機種販売入力から自動加算</t>
+          <t>目標はPt / 機種販売入力から自動加算</t>
         </is>
       </c>
       <c r="F14" s="29" t="n"/>

--- a/進捗確認.xlsx
+++ b/進捗確認.xlsx
@@ -24,12 +24,12 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy/m/d"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="m/d"/>
+    <numFmt numFmtId="167" formatCode="m/d(aaa)"/>
     <numFmt numFmtId="168" formatCode="yyyy&quot;年&quot;m&quot;月&quot;"/>
     <numFmt numFmtId="169" formatCode="0&quot;日&quot;"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="+0.0;-0.0;0.0"/>
-    <numFmt numFmtId="172" formatCode="m/d(aaa)"/>
+    <numFmt numFmtId="172" formatCode="m/d"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -227,7 +227,7 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -240,7 +240,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6803,7 +6803,7 @@
   <dimension ref="A1:K503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -19433,8 +19433,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="A4:A503" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="日付(例 10/3)を入力してください。" type="date" operator="greaterThan">
-      <formula1>36526</formula1>
+    <dataValidation sqref="A4:A503" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="対象月以外は入力できません" error="「目標設定」で指定した対象月の日付を、プルダウンから選ぶか、同じ月の日付(例 10/3)を入力してください。" promptTitle="販売日" prompt="▼で対象月の日付を選択(今日の日付は Ctrl+; でも入力できます)" type="list" errorStyle="stop">
+      <formula1>=OFFSET(進捗確認!$B$42,0,0,目標設定!$C$4,1)</formula1>
     </dataValidation>
     <dataValidation sqref="B4:B503" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="機種マスタに登録されている機種名を選んでください。" type="list">
       <formula1>=機種マスタ!$B$4:$B$203</formula1>

--- a/進捗確認.xlsx
+++ b/進捗確認.xlsx
@@ -2125,7 +2125,9 @@
       </c>
       <c r="C42" s="29" t="n"/>
       <c r="D42" s="29" t="n"/>
-      <c r="E42" s="29" t="n"/>
+      <c r="E42" s="29" t="n">
+        <v>4</v>
+      </c>
       <c r="F42" s="29" t="n"/>
       <c r="G42" s="29" t="n"/>
       <c r="H42" s="29" t="n"/>
@@ -2134,10 +2136,18 @@
         <f>IF($B42="","",SUMIFS(機種販売入力!$H$4:$H$503,機種販売入力!$A$4:$A$503,$B42))</f>
         <v/>
       </c>
-      <c r="K42" s="29" t="n"/>
-      <c r="L42" s="29" t="n"/>
-      <c r="M42" s="29" t="n"/>
-      <c r="N42" s="29" t="n"/>
+      <c r="K42" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M42" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="O42" s="31">
         <f>IF(OR(COUNT(C42:I42,K42:N42)&gt;0,N(J42)&gt;0),1,0)</f>
         <v/>
@@ -2151,8 +2161,12 @@
         <f>IF(A43&lt;=$D$3,目標設定!$C$3+A43-1,"")</f>
         <v/>
       </c>
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="29" t="n"/>
+      <c r="C43" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="E43" s="29" t="n"/>
       <c r="F43" s="29" t="n"/>
       <c r="G43" s="29" t="n"/>
@@ -2181,19 +2195,29 @@
       </c>
       <c r="C44" s="29" t="n"/>
       <c r="D44" s="29" t="n"/>
-      <c r="E44" s="29" t="n"/>
+      <c r="E44" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="F44" s="29" t="n"/>
       <c r="G44" s="29" t="n"/>
-      <c r="H44" s="29" t="n"/>
+      <c r="H44" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="I44" s="29" t="n"/>
       <c r="J44" s="30">
         <f>IF($B44="","",SUMIFS(機種販売入力!$H$4:$H$503,機種販売入力!$A$4:$A$503,$B44))</f>
         <v/>
       </c>
-      <c r="K44" s="29" t="n"/>
-      <c r="L44" s="29" t="n"/>
+      <c r="K44" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="29" t="n">
+        <v>5</v>
+      </c>
       <c r="M44" s="29" t="n"/>
-      <c r="N44" s="29" t="n"/>
+      <c r="N44" s="29" t="n">
+        <v>1</v>
+      </c>
       <c r="O44" s="31">
         <f>IF(OR(COUNT(C44:I44,K44:N44)&gt;0,N(J44)&gt;0),1,0)</f>
         <v/>
@@ -2209,7 +2233,9 @@
       </c>
       <c r="C45" s="29" t="n"/>
       <c r="D45" s="29" t="n"/>
-      <c r="E45" s="29" t="n"/>
+      <c r="E45" s="29" t="n">
+        <v>3</v>
+      </c>
       <c r="F45" s="29" t="n"/>
       <c r="G45" s="29" t="n"/>
       <c r="H45" s="29" t="n"/>
@@ -2219,7 +2245,9 @@
         <v/>
       </c>
       <c r="K45" s="29" t="n"/>
-      <c r="L45" s="29" t="n"/>
+      <c r="L45" s="29" t="n">
+        <v>10</v>
+      </c>
       <c r="M45" s="29" t="n"/>
       <c r="N45" s="29" t="n"/>
       <c r="O45" s="31">
@@ -2240,14 +2268,18 @@
       <c r="E46" s="29" t="n"/>
       <c r="F46" s="29" t="n"/>
       <c r="G46" s="29" t="n"/>
-      <c r="H46" s="29" t="n"/>
+      <c r="H46" s="29" t="n">
+        <v>1</v>
+      </c>
       <c r="I46" s="29" t="n"/>
       <c r="J46" s="30">
         <f>IF($B46="","",SUMIFS(機種販売入力!$H$4:$H$503,機種販売入力!$A$4:$A$503,$B46))</f>
         <v/>
       </c>
       <c r="K46" s="29" t="n"/>
-      <c r="L46" s="29" t="n"/>
+      <c r="L46" s="29" t="n">
+        <v>5</v>
+      </c>
       <c r="M46" s="29" t="n"/>
       <c r="N46" s="29" t="n"/>
       <c r="O46" s="31">
@@ -2265,7 +2297,9 @@
       </c>
       <c r="C47" s="29" t="n"/>
       <c r="D47" s="29" t="n"/>
-      <c r="E47" s="29" t="n"/>
+      <c r="E47" s="29" t="n">
+        <v>1</v>
+      </c>
       <c r="F47" s="29" t="n"/>
       <c r="G47" s="29" t="n"/>
       <c r="H47" s="29" t="n"/>
@@ -2274,8 +2308,12 @@
         <f>IF($B47="","",SUMIFS(機種販売入力!$H$4:$H$503,機種販売入力!$A$4:$A$503,$B47))</f>
         <v/>
       </c>
-      <c r="K47" s="29" t="n"/>
-      <c r="L47" s="29" t="n"/>
+      <c r="K47" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="29" t="n">
+        <v>1</v>
+      </c>
       <c r="M47" s="29" t="n"/>
       <c r="N47" s="29" t="n"/>
       <c r="O47" s="31">
@@ -2291,19 +2329,29 @@
         <f>IF(A48&lt;=$D$3,目標設定!$C$3+A48-1,"")</f>
         <v/>
       </c>
-      <c r="C48" s="29" t="n"/>
-      <c r="D48" s="29" t="n"/>
-      <c r="E48" s="29" t="n"/>
+      <c r="C48" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="29" t="n">
+        <v>3</v>
+      </c>
       <c r="F48" s="29" t="n"/>
       <c r="G48" s="29" t="n"/>
-      <c r="H48" s="29" t="n"/>
+      <c r="H48" s="29" t="n">
+        <v>2</v>
+      </c>
       <c r="I48" s="29" t="n"/>
       <c r="J48" s="30">
         <f>IF($B48="","",SUMIFS(機種販売入力!$H$4:$H$503,機種販売入力!$A$4:$A$503,$B48))</f>
         <v/>
       </c>
       <c r="K48" s="29" t="n"/>
-      <c r="L48" s="29" t="n"/>
+      <c r="L48" s="29" t="n">
+        <v>3</v>
+      </c>
       <c r="M48" s="29" t="n"/>
       <c r="N48" s="29" t="n"/>
       <c r="O48" s="31">
@@ -4866,8 +4914,14 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="39" t="n"/>
-      <c r="B4" s="40" t="n"/>
+      <c r="A4" s="39" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro Max(256GB)</t>
+        </is>
+      </c>
       <c r="C4" s="41" t="n"/>
       <c r="D4" s="30">
         <f>IF($B4="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B4,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -4901,8 +4955,14 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="39" t="n"/>
-      <c r="B5" s="40" t="n"/>
+      <c r="A5" s="39" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>motorola razr 60s</t>
+        </is>
+      </c>
       <c r="C5" s="41" t="n"/>
       <c r="D5" s="30">
         <f>IF($B5="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B5,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -4935,8 +4995,14 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="39" t="n"/>
-      <c r="B6" s="40" t="n"/>
+      <c r="A6" s="39" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>moto g37</t>
+        </is>
+      </c>
       <c r="C6" s="41" t="n"/>
       <c r="D6" s="30">
         <f>IF($B6="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B6,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -4970,8 +5036,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="n"/>
-      <c r="B7" s="40" t="n"/>
+      <c r="A7" s="39" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>AQUOS wish6</t>
+        </is>
+      </c>
       <c r="C7" s="41" t="n"/>
       <c r="D7" s="30">
         <f>IF($B7="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B7,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -4995,8 +5067,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="n"/>
-      <c r="B8" s="40" t="n"/>
+      <c r="A8" s="39" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 17(256GB)</t>
+        </is>
+      </c>
       <c r="C8" s="41" t="n"/>
       <c r="D8" s="30">
         <f>IF($B8="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B8,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5020,8 +5098,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="n"/>
-      <c r="B9" s="40" t="n"/>
+      <c r="A9" s="39" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S26(256GB)</t>
+        </is>
+      </c>
       <c r="C9" s="41" t="n"/>
       <c r="D9" s="30">
         <f>IF($B9="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B9,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5045,8 +5129,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="n"/>
-      <c r="B10" s="40" t="n"/>
+      <c r="A10" s="39" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>motorola edge 60s pro</t>
+        </is>
+      </c>
       <c r="C10" s="41" t="n"/>
       <c r="D10" s="30">
         <f>IF($B10="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B10,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5070,8 +5160,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="n"/>
-      <c r="B11" s="40" t="n"/>
+      <c r="A11" s="39" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S26+(512GB)</t>
+        </is>
+      </c>
       <c r="C11" s="41" t="n"/>
       <c r="D11" s="30">
         <f>IF($B11="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B11,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5095,8 +5191,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="n"/>
-      <c r="B12" s="40" t="n"/>
+      <c r="A12" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro(512GB)</t>
+        </is>
+      </c>
       <c r="C12" s="41" t="n"/>
       <c r="D12" s="30">
         <f>IF($B12="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B12,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5120,8 +5222,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="n"/>
-      <c r="B13" s="40" t="n"/>
+      <c r="A13" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro Max(512GB)</t>
+        </is>
+      </c>
       <c r="C13" s="41" t="n"/>
       <c r="D13" s="30">
         <f>IF($B13="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B13,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5145,8 +5253,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="n"/>
-      <c r="B14" s="40" t="n"/>
+      <c r="A14" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro Max(256GB)</t>
+        </is>
+      </c>
       <c r="C14" s="41" t="n"/>
       <c r="D14" s="30">
         <f>IF($B14="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B14,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5170,8 +5284,14 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="n"/>
-      <c r="B15" s="40" t="n"/>
+      <c r="A15" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro(256GB)</t>
+        </is>
+      </c>
       <c r="C15" s="41" t="n"/>
       <c r="D15" s="30">
         <f>IF($B15="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B15,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5195,8 +5315,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="n"/>
-      <c r="B16" s="40" t="n"/>
+      <c r="A16" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 17(256GB)</t>
+        </is>
+      </c>
       <c r="C16" s="41" t="n"/>
       <c r="D16" s="30">
         <f>IF($B16="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B16,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5220,8 +5346,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="n"/>
-      <c r="B17" s="40" t="n"/>
+      <c r="A17" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 17(256GB)</t>
+        </is>
+      </c>
       <c r="C17" s="41" t="n"/>
       <c r="D17" s="30">
         <f>IF($B17="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B17,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5245,8 +5377,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="n"/>
-      <c r="B18" s="40" t="n"/>
+      <c r="A18" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 17(256GB)</t>
+        </is>
+      </c>
       <c r="C18" s="41" t="n"/>
       <c r="D18" s="30">
         <f>IF($B18="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B18,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5270,8 +5408,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="n"/>
-      <c r="B19" s="40" t="n"/>
+      <c r="A19" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro(256GB)</t>
+        </is>
+      </c>
       <c r="C19" s="41" t="n"/>
       <c r="D19" s="30">
         <f>IF($B19="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B19,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5295,8 +5439,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="n"/>
-      <c r="B20" s="40" t="n"/>
+      <c r="A20" s="39" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S26(256GB)</t>
+        </is>
+      </c>
       <c r="C20" s="41" t="n"/>
       <c r="D20" s="30">
         <f>IF($B20="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B20,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5320,8 +5470,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="n"/>
-      <c r="B21" s="40" t="n"/>
+      <c r="A21" s="39" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 17(256GB)</t>
+        </is>
+      </c>
       <c r="C21" s="41" t="n"/>
       <c r="D21" s="30">
         <f>IF($B21="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B21,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5345,8 +5501,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="n"/>
-      <c r="B22" s="40" t="n"/>
+      <c r="A22" s="39" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro(256GB)</t>
+        </is>
+      </c>
       <c r="C22" s="41" t="n"/>
       <c r="D22" s="30">
         <f>IF($B22="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B22,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5370,8 +5532,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="n"/>
-      <c r="B23" s="40" t="n"/>
+      <c r="A23" s="39" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>motorola edge 60s pro</t>
+        </is>
+      </c>
       <c r="C23" s="41" t="n"/>
       <c r="D23" s="30">
         <f>IF($B23="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B23,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5395,8 +5563,14 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="n"/>
-      <c r="B24" s="40" t="n"/>
+      <c r="A24" s="39" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro(256GB)</t>
+        </is>
+      </c>
       <c r="C24" s="41" t="n"/>
       <c r="D24" s="30">
         <f>IF($B24="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B24,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5420,8 +5594,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="n"/>
-      <c r="B25" s="40" t="n"/>
+      <c r="A25" s="39" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro(256GB)</t>
+        </is>
+      </c>
       <c r="C25" s="41" t="n"/>
       <c r="D25" s="30">
         <f>IF($B25="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B25,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>
@@ -5445,8 +5625,14 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="n"/>
-      <c r="B26" s="40" t="n"/>
+      <c r="A26" s="39" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A57 5G</t>
+        </is>
+      </c>
       <c r="C26" s="41" t="n"/>
       <c r="D26" s="30">
         <f>IF($B26="","",IFERROR(INDEX(機種マスタ!$A$4:$A$203,MATCH($B26,機種マスタ!$B$4:$B$203,0)),"未登録"))</f>

--- a/進捗確認.xlsx
+++ b/進捗確認.xlsx
@@ -4856,7 +4856,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>販売日と機種名(プルダウン)を選ぶだけで、その機種の戦略Ptが自動加算されます。台数は空欄なら1台として計算します。販売日が空欄の行は日別に反映されません(赤く表示)。販売日は▼から選択(今日の日付は Ctrl+; でも入力可)。</t>
+          <t>販売日と機種名(プルダウン)を選ぶだけで、その機種の(機種Pt+戦略Pt)×台数が自動加算されます(機種Ptの点数は機種マスタのK〜L列で変更可)。戦略Ptが空欄の機種は加算されません。台数は空欄なら1台として計算します。販売日が空欄の行は日別に反映されません(赤く表示)。販売日は▼から選択(今日の日付は Ctrl+; でも入力可)。</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4900,8 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>加算Pt</t>
+          <t>加算Pt
+(機種Pt+戦略Pt)×台数</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
@@ -4940,7 +4941,7 @@
         <v/>
       </c>
       <c r="H4" s="30">
-        <f>IF($B4="","",F4*G4)</f>
+        <f>IF($B4="","",IF(F4&gt;0,(F4+IFERROR(VLOOKUP(E4,機種マスタ!$K$4:$L$6,2,FALSE),0))*G4,0))</f>
         <v/>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -4981,7 +4982,7 @@
         <v/>
       </c>
       <c r="H5" s="30">
-        <f>IF($B5="","",F5*G5)</f>
+        <f>IF($B5="","",IF(F5&gt;0,(F5+IFERROR(VLOOKUP(E5,機種マスタ!$K$4:$L$6,2,FALSE),0))*G5,0))</f>
         <v/>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -5021,7 +5022,7 @@
         <v/>
       </c>
       <c r="H6" s="30">
-        <f>IF($B6="","",F6*G6)</f>
+        <f>IF($B6="","",IF(F6&gt;0,(F6+IFERROR(VLOOKUP(E6,機種マスタ!$K$4:$L$6,2,FALSE),0))*G6,0))</f>
         <v/>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -5062,7 +5063,7 @@
         <v/>
       </c>
       <c r="H7" s="30">
-        <f>IF($B7="","",F7*G7)</f>
+        <f>IF($B7="","",IF(F7&gt;0,(F7+IFERROR(VLOOKUP(E7,機種マスタ!$K$4:$L$6,2,FALSE),0))*G7,0))</f>
         <v/>
       </c>
     </row>
@@ -5093,7 +5094,7 @@
         <v/>
       </c>
       <c r="H8" s="30">
-        <f>IF($B8="","",F8*G8)</f>
+        <f>IF($B8="","",IF(F8&gt;0,(F8+IFERROR(VLOOKUP(E8,機種マスタ!$K$4:$L$6,2,FALSE),0))*G8,0))</f>
         <v/>
       </c>
     </row>
@@ -5124,7 +5125,7 @@
         <v/>
       </c>
       <c r="H9" s="30">
-        <f>IF($B9="","",F9*G9)</f>
+        <f>IF($B9="","",IF(F9&gt;0,(F9+IFERROR(VLOOKUP(E9,機種マスタ!$K$4:$L$6,2,FALSE),0))*G9,0))</f>
         <v/>
       </c>
     </row>
@@ -5155,7 +5156,7 @@
         <v/>
       </c>
       <c r="H10" s="30">
-        <f>IF($B10="","",F10*G10)</f>
+        <f>IF($B10="","",IF(F10&gt;0,(F10+IFERROR(VLOOKUP(E10,機種マスタ!$K$4:$L$6,2,FALSE),0))*G10,0))</f>
         <v/>
       </c>
     </row>
@@ -5186,7 +5187,7 @@
         <v/>
       </c>
       <c r="H11" s="30">
-        <f>IF($B11="","",F11*G11)</f>
+        <f>IF($B11="","",IF(F11&gt;0,(F11+IFERROR(VLOOKUP(E11,機種マスタ!$K$4:$L$6,2,FALSE),0))*G11,0))</f>
         <v/>
       </c>
     </row>
@@ -5217,7 +5218,7 @@
         <v/>
       </c>
       <c r="H12" s="30">
-        <f>IF($B12="","",F12*G12)</f>
+        <f>IF($B12="","",IF(F12&gt;0,(F12+IFERROR(VLOOKUP(E12,機種マスタ!$K$4:$L$6,2,FALSE),0))*G12,0))</f>
         <v/>
       </c>
     </row>
@@ -5248,7 +5249,7 @@
         <v/>
       </c>
       <c r="H13" s="30">
-        <f>IF($B13="","",F13*G13)</f>
+        <f>IF($B13="","",IF(F13&gt;0,(F13+IFERROR(VLOOKUP(E13,機種マスタ!$K$4:$L$6,2,FALSE),0))*G13,0))</f>
         <v/>
       </c>
     </row>
@@ -5279,7 +5280,7 @@
         <v/>
       </c>
       <c r="H14" s="30">
-        <f>IF($B14="","",F14*G14)</f>
+        <f>IF($B14="","",IF(F14&gt;0,(F14+IFERROR(VLOOKUP(E14,機種マスタ!$K$4:$L$6,2,FALSE),0))*G14,0))</f>
         <v/>
       </c>
     </row>
@@ -5310,7 +5311,7 @@
         <v/>
       </c>
       <c r="H15" s="30">
-        <f>IF($B15="","",F15*G15)</f>
+        <f>IF($B15="","",IF(F15&gt;0,(F15+IFERROR(VLOOKUP(E15,機種マスタ!$K$4:$L$6,2,FALSE),0))*G15,0))</f>
         <v/>
       </c>
     </row>
@@ -5341,7 +5342,7 @@
         <v/>
       </c>
       <c r="H16" s="30">
-        <f>IF($B16="","",F16*G16)</f>
+        <f>IF($B16="","",IF(F16&gt;0,(F16+IFERROR(VLOOKUP(E16,機種マスタ!$K$4:$L$6,2,FALSE),0))*G16,0))</f>
         <v/>
       </c>
     </row>
@@ -5372,7 +5373,7 @@
         <v/>
       </c>
       <c r="H17" s="30">
-        <f>IF($B17="","",F17*G17)</f>
+        <f>IF($B17="","",IF(F17&gt;0,(F17+IFERROR(VLOOKUP(E17,機種マスタ!$K$4:$L$6,2,FALSE),0))*G17,0))</f>
         <v/>
       </c>
     </row>
@@ -5403,7 +5404,7 @@
         <v/>
       </c>
       <c r="H18" s="30">
-        <f>IF($B18="","",F18*G18)</f>
+        <f>IF($B18="","",IF(F18&gt;0,(F18+IFERROR(VLOOKUP(E18,機種マスタ!$K$4:$L$6,2,FALSE),0))*G18,0))</f>
         <v/>
       </c>
     </row>
@@ -5434,7 +5435,7 @@
         <v/>
       </c>
       <c r="H19" s="30">
-        <f>IF($B19="","",F19*G19)</f>
+        <f>IF($B19="","",IF(F19&gt;0,(F19+IFERROR(VLOOKUP(E19,機種マスタ!$K$4:$L$6,2,FALSE),0))*G19,0))</f>
         <v/>
       </c>
     </row>
@@ -5465,7 +5466,7 @@
         <v/>
       </c>
       <c r="H20" s="30">
-        <f>IF($B20="","",F20*G20)</f>
+        <f>IF($B20="","",IF(F20&gt;0,(F20+IFERROR(VLOOKUP(E20,機種マスタ!$K$4:$L$6,2,FALSE),0))*G20,0))</f>
         <v/>
       </c>
     </row>
@@ -5496,7 +5497,7 @@
         <v/>
       </c>
       <c r="H21" s="30">
-        <f>IF($B21="","",F21*G21)</f>
+        <f>IF($B21="","",IF(F21&gt;0,(F21+IFERROR(VLOOKUP(E21,機種マスタ!$K$4:$L$6,2,FALSE),0))*G21,0))</f>
         <v/>
       </c>
     </row>
@@ -5527,7 +5528,7 @@
         <v/>
       </c>
       <c r="H22" s="30">
-        <f>IF($B22="","",F22*G22)</f>
+        <f>IF($B22="","",IF(F22&gt;0,(F22+IFERROR(VLOOKUP(E22,機種マスタ!$K$4:$L$6,2,FALSE),0))*G22,0))</f>
         <v/>
       </c>
     </row>
@@ -5558,7 +5559,7 @@
         <v/>
       </c>
       <c r="H23" s="30">
-        <f>IF($B23="","",F23*G23)</f>
+        <f>IF($B23="","",IF(F23&gt;0,(F23+IFERROR(VLOOKUP(E23,機種マスタ!$K$4:$L$6,2,FALSE),0))*G23,0))</f>
         <v/>
       </c>
     </row>
@@ -5589,7 +5590,7 @@
         <v/>
       </c>
       <c r="H24" s="30">
-        <f>IF($B24="","",F24*G24)</f>
+        <f>IF($B24="","",IF(F24&gt;0,(F24+IFERROR(VLOOKUP(E24,機種マスタ!$K$4:$L$6,2,FALSE),0))*G24,0))</f>
         <v/>
       </c>
     </row>
@@ -5620,7 +5621,7 @@
         <v/>
       </c>
       <c r="H25" s="30">
-        <f>IF($B25="","",F25*G25)</f>
+        <f>IF($B25="","",IF(F25&gt;0,(F25+IFERROR(VLOOKUP(E25,機種マスタ!$K$4:$L$6,2,FALSE),0))*G25,0))</f>
         <v/>
       </c>
     </row>
@@ -5651,7 +5652,7 @@
         <v/>
       </c>
       <c r="H26" s="30">
-        <f>IF($B26="","",F26*G26)</f>
+        <f>IF($B26="","",IF(F26&gt;0,(F26+IFERROR(VLOOKUP(E26,機種マスタ!$K$4:$L$6,2,FALSE),0))*G26,0))</f>
         <v/>
       </c>
     </row>
@@ -5676,7 +5677,7 @@
         <v/>
       </c>
       <c r="H27" s="30">
-        <f>IF($B27="","",F27*G27)</f>
+        <f>IF($B27="","",IF(F27&gt;0,(F27+IFERROR(VLOOKUP(E27,機種マスタ!$K$4:$L$6,2,FALSE),0))*G27,0))</f>
         <v/>
       </c>
     </row>
@@ -5701,7 +5702,7 @@
         <v/>
       </c>
       <c r="H28" s="30">
-        <f>IF($B28="","",F28*G28)</f>
+        <f>IF($B28="","",IF(F28&gt;0,(F28+IFERROR(VLOOKUP(E28,機種マスタ!$K$4:$L$6,2,FALSE),0))*G28,0))</f>
         <v/>
       </c>
     </row>
@@ -5726,7 +5727,7 @@
         <v/>
       </c>
       <c r="H29" s="30">
-        <f>IF($B29="","",F29*G29)</f>
+        <f>IF($B29="","",IF(F29&gt;0,(F29+IFERROR(VLOOKUP(E29,機種マスタ!$K$4:$L$6,2,FALSE),0))*G29,0))</f>
         <v/>
       </c>
     </row>
@@ -5751,7 +5752,7 @@
         <v/>
       </c>
       <c r="H30" s="30">
-        <f>IF($B30="","",F30*G30)</f>
+        <f>IF($B30="","",IF(F30&gt;0,(F30+IFERROR(VLOOKUP(E30,機種マスタ!$K$4:$L$6,2,FALSE),0))*G30,0))</f>
         <v/>
       </c>
     </row>
@@ -5776,7 +5777,7 @@
         <v/>
       </c>
       <c r="H31" s="30">
-        <f>IF($B31="","",F31*G31)</f>
+        <f>IF($B31="","",IF(F31&gt;0,(F31+IFERROR(VLOOKUP(E31,機種マスタ!$K$4:$L$6,2,FALSE),0))*G31,0))</f>
         <v/>
       </c>
     </row>
@@ -5801,7 +5802,7 @@
         <v/>
       </c>
       <c r="H32" s="30">
-        <f>IF($B32="","",F32*G32)</f>
+        <f>IF($B32="","",IF(F32&gt;0,(F32+IFERROR(VLOOKUP(E32,機種マスタ!$K$4:$L$6,2,FALSE),0))*G32,0))</f>
         <v/>
       </c>
     </row>
@@ -5826,7 +5827,7 @@
         <v/>
       </c>
       <c r="H33" s="30">
-        <f>IF($B33="","",F33*G33)</f>
+        <f>IF($B33="","",IF(F33&gt;0,(F33+IFERROR(VLOOKUP(E33,機種マスタ!$K$4:$L$6,2,FALSE),0))*G33,0))</f>
         <v/>
       </c>
     </row>
@@ -5851,7 +5852,7 @@
         <v/>
       </c>
       <c r="H34" s="30">
-        <f>IF($B34="","",F34*G34)</f>
+        <f>IF($B34="","",IF(F34&gt;0,(F34+IFERROR(VLOOKUP(E34,機種マスタ!$K$4:$L$6,2,FALSE),0))*G34,0))</f>
         <v/>
       </c>
     </row>
@@ -5876,7 +5877,7 @@
         <v/>
       </c>
       <c r="H35" s="30">
-        <f>IF($B35="","",F35*G35)</f>
+        <f>IF($B35="","",IF(F35&gt;0,(F35+IFERROR(VLOOKUP(E35,機種マスタ!$K$4:$L$6,2,FALSE),0))*G35,0))</f>
         <v/>
       </c>
     </row>
@@ -5901,7 +5902,7 @@
         <v/>
       </c>
       <c r="H36" s="30">
-        <f>IF($B36="","",F36*G36)</f>
+        <f>IF($B36="","",IF(F36&gt;0,(F36+IFERROR(VLOOKUP(E36,機種マスタ!$K$4:$L$6,2,FALSE),0))*G36,0))</f>
         <v/>
       </c>
     </row>
@@ -5926,7 +5927,7 @@
         <v/>
       </c>
       <c r="H37" s="30">
-        <f>IF($B37="","",F37*G37)</f>
+        <f>IF($B37="","",IF(F37&gt;0,(F37+IFERROR(VLOOKUP(E37,機種マスタ!$K$4:$L$6,2,FALSE),0))*G37,0))</f>
         <v/>
       </c>
     </row>
@@ -5951,7 +5952,7 @@
         <v/>
       </c>
       <c r="H38" s="30">
-        <f>IF($B38="","",F38*G38)</f>
+        <f>IF($B38="","",IF(F38&gt;0,(F38+IFERROR(VLOOKUP(E38,機種マスタ!$K$4:$L$6,2,FALSE),0))*G38,0))</f>
         <v/>
       </c>
     </row>
@@ -5976,7 +5977,7 @@
         <v/>
       </c>
       <c r="H39" s="30">
-        <f>IF($B39="","",F39*G39)</f>
+        <f>IF($B39="","",IF(F39&gt;0,(F39+IFERROR(VLOOKUP(E39,機種マスタ!$K$4:$L$6,2,FALSE),0))*G39,0))</f>
         <v/>
       </c>
     </row>
@@ -6001,7 +6002,7 @@
         <v/>
       </c>
       <c r="H40" s="30">
-        <f>IF($B40="","",F40*G40)</f>
+        <f>IF($B40="","",IF(F40&gt;0,(F40+IFERROR(VLOOKUP(E40,機種マスタ!$K$4:$L$6,2,FALSE),0))*G40,0))</f>
         <v/>
       </c>
     </row>
@@ -6026,7 +6027,7 @@
         <v/>
       </c>
       <c r="H41" s="30">
-        <f>IF($B41="","",F41*G41)</f>
+        <f>IF($B41="","",IF(F41&gt;0,(F41+IFERROR(VLOOKUP(E41,機種マスタ!$K$4:$L$6,2,FALSE),0))*G41,0))</f>
         <v/>
       </c>
     </row>
@@ -6051,7 +6052,7 @@
         <v/>
       </c>
       <c r="H42" s="30">
-        <f>IF($B42="","",F42*G42)</f>
+        <f>IF($B42="","",IF(F42&gt;0,(F42+IFERROR(VLOOKUP(E42,機種マスタ!$K$4:$L$6,2,FALSE),0))*G42,0))</f>
         <v/>
       </c>
     </row>
@@ -6076,7 +6077,7 @@
         <v/>
       </c>
       <c r="H43" s="30">
-        <f>IF($B43="","",F43*G43)</f>
+        <f>IF($B43="","",IF(F43&gt;0,(F43+IFERROR(VLOOKUP(E43,機種マスタ!$K$4:$L$6,2,FALSE),0))*G43,0))</f>
         <v/>
       </c>
     </row>
@@ -6101,7 +6102,7 @@
         <v/>
       </c>
       <c r="H44" s="30">
-        <f>IF($B44="","",F44*G44)</f>
+        <f>IF($B44="","",IF(F44&gt;0,(F44+IFERROR(VLOOKUP(E44,機種マスタ!$K$4:$L$6,2,FALSE),0))*G44,0))</f>
         <v/>
       </c>
     </row>
@@ -6126,7 +6127,7 @@
         <v/>
       </c>
       <c r="H45" s="30">
-        <f>IF($B45="","",F45*G45)</f>
+        <f>IF($B45="","",IF(F45&gt;0,(F45+IFERROR(VLOOKUP(E45,機種マスタ!$K$4:$L$6,2,FALSE),0))*G45,0))</f>
         <v/>
       </c>
     </row>
@@ -6151,7 +6152,7 @@
         <v/>
       </c>
       <c r="H46" s="30">
-        <f>IF($B46="","",F46*G46)</f>
+        <f>IF($B46="","",IF(F46&gt;0,(F46+IFERROR(VLOOKUP(E46,機種マスタ!$K$4:$L$6,2,FALSE),0))*G46,0))</f>
         <v/>
       </c>
     </row>
@@ -6176,7 +6177,7 @@
         <v/>
       </c>
       <c r="H47" s="30">
-        <f>IF($B47="","",F47*G47)</f>
+        <f>IF($B47="","",IF(F47&gt;0,(F47+IFERROR(VLOOKUP(E47,機種マスタ!$K$4:$L$6,2,FALSE),0))*G47,0))</f>
         <v/>
       </c>
     </row>
@@ -6201,7 +6202,7 @@
         <v/>
       </c>
       <c r="H48" s="30">
-        <f>IF($B48="","",F48*G48)</f>
+        <f>IF($B48="","",IF(F48&gt;0,(F48+IFERROR(VLOOKUP(E48,機種マスタ!$K$4:$L$6,2,FALSE),0))*G48,0))</f>
         <v/>
       </c>
     </row>
@@ -6226,7 +6227,7 @@
         <v/>
       </c>
       <c r="H49" s="30">
-        <f>IF($B49="","",F49*G49)</f>
+        <f>IF($B49="","",IF(F49&gt;0,(F49+IFERROR(VLOOKUP(E49,機種マスタ!$K$4:$L$6,2,FALSE),0))*G49,0))</f>
         <v/>
       </c>
     </row>
@@ -6251,7 +6252,7 @@
         <v/>
       </c>
       <c r="H50" s="30">
-        <f>IF($B50="","",F50*G50)</f>
+        <f>IF($B50="","",IF(F50&gt;0,(F50+IFERROR(VLOOKUP(E50,機種マスタ!$K$4:$L$6,2,FALSE),0))*G50,0))</f>
         <v/>
       </c>
     </row>
@@ -6276,7 +6277,7 @@
         <v/>
       </c>
       <c r="H51" s="30">
-        <f>IF($B51="","",F51*G51)</f>
+        <f>IF($B51="","",IF(F51&gt;0,(F51+IFERROR(VLOOKUP(E51,機種マスタ!$K$4:$L$6,2,FALSE),0))*G51,0))</f>
         <v/>
       </c>
     </row>
@@ -6301,7 +6302,7 @@
         <v/>
       </c>
       <c r="H52" s="30">
-        <f>IF($B52="","",F52*G52)</f>
+        <f>IF($B52="","",IF(F52&gt;0,(F52+IFERROR(VLOOKUP(E52,機種マスタ!$K$4:$L$6,2,FALSE),0))*G52,0))</f>
         <v/>
       </c>
     </row>
@@ -6326,7 +6327,7 @@
         <v/>
       </c>
       <c r="H53" s="30">
-        <f>IF($B53="","",F53*G53)</f>
+        <f>IF($B53="","",IF(F53&gt;0,(F53+IFERROR(VLOOKUP(E53,機種マスタ!$K$4:$L$6,2,FALSE),0))*G53,0))</f>
         <v/>
       </c>
     </row>
@@ -6351,7 +6352,7 @@
         <v/>
       </c>
       <c r="H54" s="30">
-        <f>IF($B54="","",F54*G54)</f>
+        <f>IF($B54="","",IF(F54&gt;0,(F54+IFERROR(VLOOKUP(E54,機種マスタ!$K$4:$L$6,2,FALSE),0))*G54,0))</f>
         <v/>
       </c>
     </row>
@@ -6376,7 +6377,7 @@
         <v/>
       </c>
       <c r="H55" s="30">
-        <f>IF($B55="","",F55*G55)</f>
+        <f>IF($B55="","",IF(F55&gt;0,(F55+IFERROR(VLOOKUP(E55,機種マスタ!$K$4:$L$6,2,FALSE),0))*G55,0))</f>
         <v/>
       </c>
     </row>
@@ -6401,7 +6402,7 @@
         <v/>
       </c>
       <c r="H56" s="30">
-        <f>IF($B56="","",F56*G56)</f>
+        <f>IF($B56="","",IF(F56&gt;0,(F56+IFERROR(VLOOKUP(E56,機種マスタ!$K$4:$L$6,2,FALSE),0))*G56,0))</f>
         <v/>
       </c>
     </row>
@@ -6426,7 +6427,7 @@
         <v/>
       </c>
       <c r="H57" s="30">
-        <f>IF($B57="","",F57*G57)</f>
+        <f>IF($B57="","",IF(F57&gt;0,(F57+IFERROR(VLOOKUP(E57,機種マスタ!$K$4:$L$6,2,FALSE),0))*G57,0))</f>
         <v/>
       </c>
     </row>
@@ -6451,7 +6452,7 @@
         <v/>
       </c>
       <c r="H58" s="30">
-        <f>IF($B58="","",F58*G58)</f>
+        <f>IF($B58="","",IF(F58&gt;0,(F58+IFERROR(VLOOKUP(E58,機種マスタ!$K$4:$L$6,2,FALSE),0))*G58,0))</f>
         <v/>
       </c>
     </row>
@@ -6476,7 +6477,7 @@
         <v/>
       </c>
       <c r="H59" s="30">
-        <f>IF($B59="","",F59*G59)</f>
+        <f>IF($B59="","",IF(F59&gt;0,(F59+IFERROR(VLOOKUP(E59,機種マスタ!$K$4:$L$6,2,FALSE),0))*G59,0))</f>
         <v/>
       </c>
     </row>
@@ -6501,7 +6502,7 @@
         <v/>
       </c>
       <c r="H60" s="30">
-        <f>IF($B60="","",F60*G60)</f>
+        <f>IF($B60="","",IF(F60&gt;0,(F60+IFERROR(VLOOKUP(E60,機種マスタ!$K$4:$L$6,2,FALSE),0))*G60,0))</f>
         <v/>
       </c>
     </row>
@@ -6526,7 +6527,7 @@
         <v/>
       </c>
       <c r="H61" s="30">
-        <f>IF($B61="","",F61*G61)</f>
+        <f>IF($B61="","",IF(F61&gt;0,(F61+IFERROR(VLOOKUP(E61,機種マスタ!$K$4:$L$6,2,FALSE),0))*G61,0))</f>
         <v/>
       </c>
     </row>
@@ -6551,7 +6552,7 @@
         <v/>
       </c>
       <c r="H62" s="30">
-        <f>IF($B62="","",F62*G62)</f>
+        <f>IF($B62="","",IF(F62&gt;0,(F62+IFERROR(VLOOKUP(E62,機種マスタ!$K$4:$L$6,2,FALSE),0))*G62,0))</f>
         <v/>
       </c>
     </row>
@@ -6576,7 +6577,7 @@
         <v/>
       </c>
       <c r="H63" s="30">
-        <f>IF($B63="","",F63*G63)</f>
+        <f>IF($B63="","",IF(F63&gt;0,(F63+IFERROR(VLOOKUP(E63,機種マスタ!$K$4:$L$6,2,FALSE),0))*G63,0))</f>
         <v/>
       </c>
     </row>
@@ -6601,7 +6602,7 @@
         <v/>
       </c>
       <c r="H64" s="30">
-        <f>IF($B64="","",F64*G64)</f>
+        <f>IF($B64="","",IF(F64&gt;0,(F64+IFERROR(VLOOKUP(E64,機種マスタ!$K$4:$L$6,2,FALSE),0))*G64,0))</f>
         <v/>
       </c>
     </row>
@@ -6626,7 +6627,7 @@
         <v/>
       </c>
       <c r="H65" s="30">
-        <f>IF($B65="","",F65*G65)</f>
+        <f>IF($B65="","",IF(F65&gt;0,(F65+IFERROR(VLOOKUP(E65,機種マスタ!$K$4:$L$6,2,FALSE),0))*G65,0))</f>
         <v/>
       </c>
     </row>
@@ -6651,7 +6652,7 @@
         <v/>
       </c>
       <c r="H66" s="30">
-        <f>IF($B66="","",F66*G66)</f>
+        <f>IF($B66="","",IF(F66&gt;0,(F66+IFERROR(VLOOKUP(E66,機種マスタ!$K$4:$L$6,2,FALSE),0))*G66,0))</f>
         <v/>
       </c>
     </row>
@@ -6676,7 +6677,7 @@
         <v/>
       </c>
       <c r="H67" s="30">
-        <f>IF($B67="","",F67*G67)</f>
+        <f>IF($B67="","",IF(F67&gt;0,(F67+IFERROR(VLOOKUP(E67,機種マスタ!$K$4:$L$6,2,FALSE),0))*G67,0))</f>
         <v/>
       </c>
     </row>
@@ -6701,7 +6702,7 @@
         <v/>
       </c>
       <c r="H68" s="30">
-        <f>IF($B68="","",F68*G68)</f>
+        <f>IF($B68="","",IF(F68&gt;0,(F68+IFERROR(VLOOKUP(E68,機種マスタ!$K$4:$L$6,2,FALSE),0))*G68,0))</f>
         <v/>
       </c>
     </row>
@@ -6726,7 +6727,7 @@
         <v/>
       </c>
       <c r="H69" s="30">
-        <f>IF($B69="","",F69*G69)</f>
+        <f>IF($B69="","",IF(F69&gt;0,(F69+IFERROR(VLOOKUP(E69,機種マスタ!$K$4:$L$6,2,FALSE),0))*G69,0))</f>
         <v/>
       </c>
     </row>
@@ -6751,7 +6752,7 @@
         <v/>
       </c>
       <c r="H70" s="30">
-        <f>IF($B70="","",F70*G70)</f>
+        <f>IF($B70="","",IF(F70&gt;0,(F70+IFERROR(VLOOKUP(E70,機種マスタ!$K$4:$L$6,2,FALSE),0))*G70,0))</f>
         <v/>
       </c>
     </row>
@@ -6776,7 +6777,7 @@
         <v/>
       </c>
       <c r="H71" s="30">
-        <f>IF($B71="","",F71*G71)</f>
+        <f>IF($B71="","",IF(F71&gt;0,(F71+IFERROR(VLOOKUP(E71,機種マスタ!$K$4:$L$6,2,FALSE),0))*G71,0))</f>
         <v/>
       </c>
     </row>
@@ -6801,7 +6802,7 @@
         <v/>
       </c>
       <c r="H72" s="30">
-        <f>IF($B72="","",F72*G72)</f>
+        <f>IF($B72="","",IF(F72&gt;0,(F72+IFERROR(VLOOKUP(E72,機種マスタ!$K$4:$L$6,2,FALSE),0))*G72,0))</f>
         <v/>
       </c>
     </row>
@@ -6826,7 +6827,7 @@
         <v/>
       </c>
       <c r="H73" s="30">
-        <f>IF($B73="","",F73*G73)</f>
+        <f>IF($B73="","",IF(F73&gt;0,(F73+IFERROR(VLOOKUP(E73,機種マスタ!$K$4:$L$6,2,FALSE),0))*G73,0))</f>
         <v/>
       </c>
     </row>
@@ -6851,7 +6852,7 @@
         <v/>
       </c>
       <c r="H74" s="30">
-        <f>IF($B74="","",F74*G74)</f>
+        <f>IF($B74="","",IF(F74&gt;0,(F74+IFERROR(VLOOKUP(E74,機種マスタ!$K$4:$L$6,2,FALSE),0))*G74,0))</f>
         <v/>
       </c>
     </row>
@@ -6876,7 +6877,7 @@
         <v/>
       </c>
       <c r="H75" s="30">
-        <f>IF($B75="","",F75*G75)</f>
+        <f>IF($B75="","",IF(F75&gt;0,(F75+IFERROR(VLOOKUP(E75,機種マスタ!$K$4:$L$6,2,FALSE),0))*G75,0))</f>
         <v/>
       </c>
     </row>
@@ -6901,7 +6902,7 @@
         <v/>
       </c>
       <c r="H76" s="30">
-        <f>IF($B76="","",F76*G76)</f>
+        <f>IF($B76="","",IF(F76&gt;0,(F76+IFERROR(VLOOKUP(E76,機種マスタ!$K$4:$L$6,2,FALSE),0))*G76,0))</f>
         <v/>
       </c>
     </row>
@@ -6926,7 +6927,7 @@
         <v/>
       </c>
       <c r="H77" s="30">
-        <f>IF($B77="","",F77*G77)</f>
+        <f>IF($B77="","",IF(F77&gt;0,(F77+IFERROR(VLOOKUP(E77,機種マスタ!$K$4:$L$6,2,FALSE),0))*G77,0))</f>
         <v/>
       </c>
     </row>
@@ -6951,7 +6952,7 @@
         <v/>
       </c>
       <c r="H78" s="30">
-        <f>IF($B78="","",F78*G78)</f>
+        <f>IF($B78="","",IF(F78&gt;0,(F78+IFERROR(VLOOKUP(E78,機種マスタ!$K$4:$L$6,2,FALSE),0))*G78,0))</f>
         <v/>
       </c>
     </row>
@@ -6976,7 +6977,7 @@
         <v/>
       </c>
       <c r="H79" s="30">
-        <f>IF($B79="","",F79*G79)</f>
+        <f>IF($B79="","",IF(F79&gt;0,(F79+IFERROR(VLOOKUP(E79,機種マスタ!$K$4:$L$6,2,FALSE),0))*G79,0))</f>
         <v/>
       </c>
     </row>
@@ -7001,7 +7002,7 @@
         <v/>
       </c>
       <c r="H80" s="30">
-        <f>IF($B80="","",F80*G80)</f>
+        <f>IF($B80="","",IF(F80&gt;0,(F80+IFERROR(VLOOKUP(E80,機種マスタ!$K$4:$L$6,2,FALSE),0))*G80,0))</f>
         <v/>
       </c>
     </row>
@@ -7026,7 +7027,7 @@
         <v/>
       </c>
       <c r="H81" s="30">
-        <f>IF($B81="","",F81*G81)</f>
+        <f>IF($B81="","",IF(F81&gt;0,(F81+IFERROR(VLOOKUP(E81,機種マスタ!$K$4:$L$6,2,FALSE),0))*G81,0))</f>
         <v/>
       </c>
     </row>
@@ -7051,7 +7052,7 @@
         <v/>
       </c>
       <c r="H82" s="30">
-        <f>IF($B82="","",F82*G82)</f>
+        <f>IF($B82="","",IF(F82&gt;0,(F82+IFERROR(VLOOKUP(E82,機種マスタ!$K$4:$L$6,2,FALSE),0))*G82,0))</f>
         <v/>
       </c>
     </row>
@@ -7076,7 +7077,7 @@
         <v/>
       </c>
       <c r="H83" s="30">
-        <f>IF($B83="","",F83*G83)</f>
+        <f>IF($B83="","",IF(F83&gt;0,(F83+IFERROR(VLOOKUP(E83,機種マスタ!$K$4:$L$6,2,FALSE),0))*G83,0))</f>
         <v/>
       </c>
     </row>
@@ -7101,7 +7102,7 @@
         <v/>
       </c>
       <c r="H84" s="30">
-        <f>IF($B84="","",F84*G84)</f>
+        <f>IF($B84="","",IF(F84&gt;0,(F84+IFERROR(VLOOKUP(E84,機種マスタ!$K$4:$L$6,2,FALSE),0))*G84,0))</f>
         <v/>
       </c>
     </row>
@@ -7126,7 +7127,7 @@
         <v/>
       </c>
       <c r="H85" s="30">
-        <f>IF($B85="","",F85*G85)</f>
+        <f>IF($B85="","",IF(F85&gt;0,(F85+IFERROR(VLOOKUP(E85,機種マスタ!$K$4:$L$6,2,FALSE),0))*G85,0))</f>
         <v/>
       </c>
     </row>
@@ -7151,7 +7152,7 @@
         <v/>
       </c>
       <c r="H86" s="30">
-        <f>IF($B86="","",F86*G86)</f>
+        <f>IF($B86="","",IF(F86&gt;0,(F86+IFERROR(VLOOKUP(E86,機種マスタ!$K$4:$L$6,2,FALSE),0))*G86,0))</f>
         <v/>
       </c>
     </row>
@@ -7176,7 +7177,7 @@
         <v/>
       </c>
       <c r="H87" s="30">
-        <f>IF($B87="","",F87*G87)</f>
+        <f>IF($B87="","",IF(F87&gt;0,(F87+IFERROR(VLOOKUP(E87,機種マスタ!$K$4:$L$6,2,FALSE),0))*G87,0))</f>
         <v/>
       </c>
     </row>
@@ -7201,7 +7202,7 @@
         <v/>
       </c>
       <c r="H88" s="30">
-        <f>IF($B88="","",F88*G88)</f>
+        <f>IF($B88="","",IF(F88&gt;0,(F88+IFERROR(VLOOKUP(E88,機種マスタ!$K$4:$L$6,2,FALSE),0))*G88,0))</f>
         <v/>
       </c>
     </row>
@@ -7226,7 +7227,7 @@
         <v/>
       </c>
       <c r="H89" s="30">
-        <f>IF($B89="","",F89*G89)</f>
+        <f>IF($B89="","",IF(F89&gt;0,(F89+IFERROR(VLOOKUP(E89,機種マスタ!$K$4:$L$6,2,FALSE),0))*G89,0))</f>
         <v/>
       </c>
     </row>
@@ -7251,7 +7252,7 @@
         <v/>
       </c>
       <c r="H90" s="30">
-        <f>IF($B90="","",F90*G90)</f>
+        <f>IF($B90="","",IF(F90&gt;0,(F90+IFERROR(VLOOKUP(E90,機種マスタ!$K$4:$L$6,2,FALSE),0))*G90,0))</f>
         <v/>
       </c>
     </row>
@@ -7276,7 +7277,7 @@
         <v/>
       </c>
       <c r="H91" s="30">
-        <f>IF($B91="","",F91*G91)</f>
+        <f>IF($B91="","",IF(F91&gt;0,(F91+IFERROR(VLOOKUP(E91,機種マスタ!$K$4:$L$6,2,FALSE),0))*G91,0))</f>
         <v/>
       </c>
     </row>
@@ -7301,7 +7302,7 @@
         <v/>
       </c>
       <c r="H92" s="30">
-        <f>IF($B92="","",F92*G92)</f>
+        <f>IF($B92="","",IF(F92&gt;0,(F92+IFERROR(VLOOKUP(E92,機種マスタ!$K$4:$L$6,2,FALSE),0))*G92,0))</f>
         <v/>
       </c>
     </row>
@@ -7326,7 +7327,7 @@
         <v/>
       </c>
       <c r="H93" s="30">
-        <f>IF($B93="","",F93*G93)</f>
+        <f>IF($B93="","",IF(F93&gt;0,(F93+IFERROR(VLOOKUP(E93,機種マスタ!$K$4:$L$6,2,FALSE),0))*G93,0))</f>
         <v/>
       </c>
     </row>
@@ -7351,7 +7352,7 @@
         <v/>
       </c>
       <c r="H94" s="30">
-        <f>IF($B94="","",F94*G94)</f>
+        <f>IF($B94="","",IF(F94&gt;0,(F94+IFERROR(VLOOKUP(E94,機種マスタ!$K$4:$L$6,2,FALSE),0))*G94,0))</f>
         <v/>
       </c>
     </row>
@@ -7376,7 +7377,7 @@
         <v/>
       </c>
       <c r="H95" s="30">
-        <f>IF($B95="","",F95*G95)</f>
+        <f>IF($B95="","",IF(F95&gt;0,(F95+IFERROR(VLOOKUP(E95,機種マスタ!$K$4:$L$6,2,FALSE),0))*G95,0))</f>
         <v/>
       </c>
     </row>
@@ -7401,7 +7402,7 @@
         <v/>
       </c>
       <c r="H96" s="30">
-        <f>IF($B96="","",F96*G96)</f>
+        <f>IF($B96="","",IF(F96&gt;0,(F96+IFERROR(VLOOKUP(E96,機種マスタ!$K$4:$L$6,2,FALSE),0))*G96,0))</f>
         <v/>
       </c>
     </row>
@@ -7426,7 +7427,7 @@
         <v/>
       </c>
       <c r="H97" s="30">
-        <f>IF($B97="","",F97*G97)</f>
+        <f>IF($B97="","",IF(F97&gt;0,(F97+IFERROR(VLOOKUP(E97,機種マスタ!$K$4:$L$6,2,FALSE),0))*G97,0))</f>
         <v/>
       </c>
     </row>
@@ -7451,7 +7452,7 @@
         <v/>
       </c>
       <c r="H98" s="30">
-        <f>IF($B98="","",F98*G98)</f>
+        <f>IF($B98="","",IF(F98&gt;0,(F98+IFERROR(VLOOKUP(E98,機種マスタ!$K$4:$L$6,2,FALSE),0))*G98,0))</f>
         <v/>
       </c>
     </row>
@@ -7476,7 +7477,7 @@
         <v/>
       </c>
       <c r="H99" s="30">
-        <f>IF($B99="","",F99*G99)</f>
+        <f>IF($B99="","",IF(F99&gt;0,(F99+IFERROR(VLOOKUP(E99,機種マスタ!$K$4:$L$6,2,FALSE),0))*G99,0))</f>
         <v/>
       </c>
     </row>
@@ -7501,7 +7502,7 @@
         <v/>
       </c>
       <c r="H100" s="30">
-        <f>IF($B100="","",F100*G100)</f>
+        <f>IF($B100="","",IF(F100&gt;0,(F100+IFERROR(VLOOKUP(E100,機種マスタ!$K$4:$L$6,2,FALSE),0))*G100,0))</f>
         <v/>
       </c>
     </row>
@@ -7526,7 +7527,7 @@
         <v/>
       </c>
       <c r="H101" s="30">
-        <f>IF($B101="","",F101*G101)</f>
+        <f>IF($B101="","",IF(F101&gt;0,(F101+IFERROR(VLOOKUP(E101,機種マスタ!$K$4:$L$6,2,FALSE),0))*G101,0))</f>
         <v/>
       </c>
     </row>
@@ -7551,7 +7552,7 @@
         <v/>
       </c>
       <c r="H102" s="30">
-        <f>IF($B102="","",F102*G102)</f>
+        <f>IF($B102="","",IF(F102&gt;0,(F102+IFERROR(VLOOKUP(E102,機種マスタ!$K$4:$L$6,2,FALSE),0))*G102,0))</f>
         <v/>
       </c>
     </row>
@@ -7576,7 +7577,7 @@
         <v/>
       </c>
       <c r="H103" s="30">
-        <f>IF($B103="","",F103*G103)</f>
+        <f>IF($B103="","",IF(F103&gt;0,(F103+IFERROR(VLOOKUP(E103,機種マスタ!$K$4:$L$6,2,FALSE),0))*G103,0))</f>
         <v/>
       </c>
     </row>
@@ -7601,7 +7602,7 @@
         <v/>
       </c>
       <c r="H104" s="30">
-        <f>IF($B104="","",F104*G104)</f>
+        <f>IF($B104="","",IF(F104&gt;0,(F104+IFERROR(VLOOKUP(E104,機種マスタ!$K$4:$L$6,2,FALSE),0))*G104,0))</f>
         <v/>
       </c>
     </row>
@@ -7626,7 +7627,7 @@
         <v/>
       </c>
       <c r="H105" s="30">
-        <f>IF($B105="","",F105*G105)</f>
+        <f>IF($B105="","",IF(F105&gt;0,(F105+IFERROR(VLOOKUP(E105,機種マスタ!$K$4:$L$6,2,FALSE),0))*G105,0))</f>
         <v/>
       </c>
     </row>
@@ -7651,7 +7652,7 @@
         <v/>
       </c>
       <c r="H106" s="30">
-        <f>IF($B106="","",F106*G106)</f>
+        <f>IF($B106="","",IF(F106&gt;0,(F106+IFERROR(VLOOKUP(E106,機種マスタ!$K$4:$L$6,2,FALSE),0))*G106,0))</f>
         <v/>
       </c>
     </row>
@@ -7676,7 +7677,7 @@
         <v/>
       </c>
       <c r="H107" s="30">
-        <f>IF($B107="","",F107*G107)</f>
+        <f>IF($B107="","",IF(F107&gt;0,(F107+IFERROR(VLOOKUP(E107,機種マスタ!$K$4:$L$6,2,FALSE),0))*G107,0))</f>
         <v/>
       </c>
     </row>
@@ -7701,7 +7702,7 @@
         <v/>
       </c>
       <c r="H108" s="30">
-        <f>IF($B108="","",F108*G108)</f>
+        <f>IF($B108="","",IF(F108&gt;0,(F108+IFERROR(VLOOKUP(E108,機種マスタ!$K$4:$L$6,2,FALSE),0))*G108,0))</f>
         <v/>
       </c>
     </row>
@@ -7726,7 +7727,7 @@
         <v/>
       </c>
       <c r="H109" s="30">
-        <f>IF($B109="","",F109*G109)</f>
+        <f>IF($B109="","",IF(F109&gt;0,(F109+IFERROR(VLOOKUP(E109,機種マスタ!$K$4:$L$6,2,FALSE),0))*G109,0))</f>
         <v/>
       </c>
     </row>
@@ -7751,7 +7752,7 @@
         <v/>
       </c>
       <c r="H110" s="30">
-        <f>IF($B110="","",F110*G110)</f>
+        <f>IF($B110="","",IF(F110&gt;0,(F110+IFERROR(VLOOKUP(E110,機種マスタ!$K$4:$L$6,2,FALSE),0))*G110,0))</f>
         <v/>
       </c>
     </row>
@@ -7776,7 +7777,7 @@
         <v/>
       </c>
       <c r="H111" s="30">
-        <f>IF($B111="","",F111*G111)</f>
+        <f>IF($B111="","",IF(F111&gt;0,(F111+IFERROR(VLOOKUP(E111,機種マスタ!$K$4:$L$6,2,FALSE),0))*G111,0))</f>
         <v/>
       </c>
     </row>
@@ -7801,7 +7802,7 @@
         <v/>
       </c>
       <c r="H112" s="30">
-        <f>IF($B112="","",F112*G112)</f>
+        <f>IF($B112="","",IF(F112&gt;0,(F112+IFERROR(VLOOKUP(E112,機種マスタ!$K$4:$L$6,2,FALSE),0))*G112,0))</f>
         <v/>
       </c>
     </row>
@@ -7826,7 +7827,7 @@
         <v/>
       </c>
       <c r="H113" s="30">
-        <f>IF($B113="","",F113*G113)</f>
+        <f>IF($B113="","",IF(F113&gt;0,(F113+IFERROR(VLOOKUP(E113,機種マスタ!$K$4:$L$6,2,FALSE),0))*G113,0))</f>
         <v/>
       </c>
     </row>
@@ -7851,7 +7852,7 @@
         <v/>
       </c>
       <c r="H114" s="30">
-        <f>IF($B114="","",F114*G114)</f>
+        <f>IF($B114="","",IF(F114&gt;0,(F114+IFERROR(VLOOKUP(E114,機種マスタ!$K$4:$L$6,2,FALSE),0))*G114,0))</f>
         <v/>
       </c>
     </row>
@@ -7876,7 +7877,7 @@
         <v/>
       </c>
       <c r="H115" s="30">
-        <f>IF($B115="","",F115*G115)</f>
+        <f>IF($B115="","",IF(F115&gt;0,(F115+IFERROR(VLOOKUP(E115,機種マスタ!$K$4:$L$6,2,FALSE),0))*G115,0))</f>
         <v/>
       </c>
     </row>
@@ -7901,7 +7902,7 @@
         <v/>
       </c>
       <c r="H116" s="30">
-        <f>IF($B116="","",F116*G116)</f>
+        <f>IF($B116="","",IF(F116&gt;0,(F116+IFERROR(VLOOKUP(E116,機種マスタ!$K$4:$L$6,2,FALSE),0))*G116,0))</f>
         <v/>
       </c>
     </row>
@@ -7926,7 +7927,7 @@
         <v/>
       </c>
       <c r="H117" s="30">
-        <f>IF($B117="","",F117*G117)</f>
+        <f>IF($B117="","",IF(F117&gt;0,(F117+IFERROR(VLOOKUP(E117,機種マスタ!$K$4:$L$6,2,FALSE),0))*G117,0))</f>
         <v/>
       </c>
     </row>
@@ -7951,7 +7952,7 @@
         <v/>
       </c>
       <c r="H118" s="30">
-        <f>IF($B118="","",F118*G118)</f>
+        <f>IF($B118="","",IF(F118&gt;0,(F118+IFERROR(VLOOKUP(E118,機種マスタ!$K$4:$L$6,2,FALSE),0))*G118,0))</f>
         <v/>
       </c>
     </row>
@@ -7976,7 +7977,7 @@
         <v/>
       </c>
       <c r="H119" s="30">
-        <f>IF($B119="","",F119*G119)</f>
+        <f>IF($B119="","",IF(F119&gt;0,(F119+IFERROR(VLOOKUP(E119,機種マスタ!$K$4:$L$6,2,FALSE),0))*G119,0))</f>
         <v/>
       </c>
     </row>
@@ -8001,7 +8002,7 @@
         <v/>
       </c>
       <c r="H120" s="30">
-        <f>IF($B120="","",F120*G120)</f>
+        <f>IF($B120="","",IF(F120&gt;0,(F120+IFERROR(VLOOKUP(E120,機種マスタ!$K$4:$L$6,2,FALSE),0))*G120,0))</f>
         <v/>
       </c>
     </row>
@@ -8026,7 +8027,7 @@
         <v/>
       </c>
       <c r="H121" s="30">
-        <f>IF($B121="","",F121*G121)</f>
+        <f>IF($B121="","",IF(F121&gt;0,(F121+IFERROR(VLOOKUP(E121,機種マスタ!$K$4:$L$6,2,FALSE),0))*G121,0))</f>
         <v/>
       </c>
     </row>
@@ -8051,7 +8052,7 @@
         <v/>
       </c>
       <c r="H122" s="30">
-        <f>IF($B122="","",F122*G122)</f>
+        <f>IF($B122="","",IF(F122&gt;0,(F122+IFERROR(VLOOKUP(E122,機種マスタ!$K$4:$L$6,2,FALSE),0))*G122,0))</f>
         <v/>
       </c>
     </row>
@@ -8076,7 +8077,7 @@
         <v/>
       </c>
       <c r="H123" s="30">
-        <f>IF($B123="","",F123*G123)</f>
+        <f>IF($B123="","",IF(F123&gt;0,(F123+IFERROR(VLOOKUP(E123,機種マスタ!$K$4:$L$6,2,FALSE),0))*G123,0))</f>
         <v/>
       </c>
     </row>
@@ -8101,7 +8102,7 @@
         <v/>
       </c>
       <c r="H124" s="30">
-        <f>IF($B124="","",F124*G124)</f>
+        <f>IF($B124="","",IF(F124&gt;0,(F124+IFERROR(VLOOKUP(E124,機種マスタ!$K$4:$L$6,2,FALSE),0))*G124,0))</f>
         <v/>
       </c>
     </row>
@@ -8126,7 +8127,7 @@
         <v/>
       </c>
       <c r="H125" s="30">
-        <f>IF($B125="","",F125*G125)</f>
+        <f>IF($B125="","",IF(F125&gt;0,(F125+IFERROR(VLOOKUP(E125,機種マスタ!$K$4:$L$6,2,FALSE),0))*G125,0))</f>
         <v/>
       </c>
     </row>
@@ -8151,7 +8152,7 @@
         <v/>
       </c>
       <c r="H126" s="30">
-        <f>IF($B126="","",F126*G126)</f>
+        <f>IF($B126="","",IF(F126&gt;0,(F126+IFERROR(VLOOKUP(E126,機種マスタ!$K$4:$L$6,2,FALSE),0))*G126,0))</f>
         <v/>
       </c>
     </row>
@@ -8176,7 +8177,7 @@
         <v/>
       </c>
       <c r="H127" s="30">
-        <f>IF($B127="","",F127*G127)</f>
+        <f>IF($B127="","",IF(F127&gt;0,(F127+IFERROR(VLOOKUP(E127,機種マスタ!$K$4:$L$6,2,FALSE),0))*G127,0))</f>
         <v/>
       </c>
     </row>
@@ -8201,7 +8202,7 @@
         <v/>
       </c>
       <c r="H128" s="30">
-        <f>IF($B128="","",F128*G128)</f>
+        <f>IF($B128="","",IF(F128&gt;0,(F128+IFERROR(VLOOKUP(E128,機種マスタ!$K$4:$L$6,2,FALSE),0))*G128,0))</f>
         <v/>
       </c>
     </row>
@@ -8226,7 +8227,7 @@
         <v/>
       </c>
       <c r="H129" s="30">
-        <f>IF($B129="","",F129*G129)</f>
+        <f>IF($B129="","",IF(F129&gt;0,(F129+IFERROR(VLOOKUP(E129,機種マスタ!$K$4:$L$6,2,FALSE),0))*G129,0))</f>
         <v/>
       </c>
     </row>
@@ -8251,7 +8252,7 @@
         <v/>
       </c>
       <c r="H130" s="30">
-        <f>IF($B130="","",F130*G130)</f>
+        <f>IF($B130="","",IF(F130&gt;0,(F130+IFERROR(VLOOKUP(E130,機種マスタ!$K$4:$L$6,2,FALSE),0))*G130,0))</f>
         <v/>
       </c>
     </row>
@@ -8276,7 +8277,7 @@
         <v/>
       </c>
       <c r="H131" s="30">
-        <f>IF($B131="","",F131*G131)</f>
+        <f>IF($B131="","",IF(F131&gt;0,(F131+IFERROR(VLOOKUP(E131,機種マスタ!$K$4:$L$6,2,FALSE),0))*G131,0))</f>
         <v/>
       </c>
     </row>
@@ -8301,7 +8302,7 @@
         <v/>
       </c>
       <c r="H132" s="30">
-        <f>IF($B132="","",F132*G132)</f>
+        <f>IF($B132="","",IF(F132&gt;0,(F132+IFERROR(VLOOKUP(E132,機種マスタ!$K$4:$L$6,2,FALSE),0))*G132,0))</f>
         <v/>
       </c>
     </row>
@@ -8326,7 +8327,7 @@
         <v/>
       </c>
       <c r="H133" s="30">
-        <f>IF($B133="","",F133*G133)</f>
+        <f>IF($B133="","",IF(F133&gt;0,(F133+IFERROR(VLOOKUP(E133,機種マスタ!$K$4:$L$6,2,FALSE),0))*G133,0))</f>
         <v/>
       </c>
     </row>
@@ -8351,7 +8352,7 @@
         <v/>
       </c>
       <c r="H134" s="30">
-        <f>IF($B134="","",F134*G134)</f>
+        <f>IF($B134="","",IF(F134&gt;0,(F134+IFERROR(VLOOKUP(E134,機種マスタ!$K$4:$L$6,2,FALSE),0))*G134,0))</f>
         <v/>
       </c>
     </row>
@@ -8376,7 +8377,7 @@
         <v/>
       </c>
       <c r="H135" s="30">
-        <f>IF($B135="","",F135*G135)</f>
+        <f>IF($B135="","",IF(F135&gt;0,(F135+IFERROR(VLOOKUP(E135,機種マスタ!$K$4:$L$6,2,FALSE),0))*G135,0))</f>
         <v/>
       </c>
     </row>
@@ -8401,7 +8402,7 @@
         <v/>
       </c>
       <c r="H136" s="30">
-        <f>IF($B136="","",F136*G136)</f>
+        <f>IF($B136="","",IF(F136&gt;0,(F136+IFERROR(VLOOKUP(E136,機種マスタ!$K$4:$L$6,2,FALSE),0))*G136,0))</f>
         <v/>
       </c>
     </row>
@@ -8426,7 +8427,7 @@
         <v/>
       </c>
       <c r="H137" s="30">
-        <f>IF($B137="","",F137*G137)</f>
+        <f>IF($B137="","",IF(F137&gt;0,(F137+IFERROR(VLOOKUP(E137,機種マスタ!$K$4:$L$6,2,FALSE),0))*G137,0))</f>
         <v/>
       </c>
     </row>
@@ -8451,7 +8452,7 @@
         <v/>
       </c>
       <c r="H138" s="30">
-        <f>IF($B138="","",F138*G138)</f>
+        <f>IF($B138="","",IF(F138&gt;0,(F138+IFERROR(VLOOKUP(E138,機種マスタ!$K$4:$L$6,2,FALSE),0))*G138,0))</f>
         <v/>
       </c>
     </row>
@@ -8476,7 +8477,7 @@
         <v/>
       </c>
       <c r="H139" s="30">
-        <f>IF($B139="","",F139*G139)</f>
+        <f>IF($B139="","",IF(F139&gt;0,(F139+IFERROR(VLOOKUP(E139,機種マスタ!$K$4:$L$6,2,FALSE),0))*G139,0))</f>
         <v/>
       </c>
     </row>
@@ -8501,7 +8502,7 @@
         <v/>
       </c>
       <c r="H140" s="30">
-        <f>IF($B140="","",F140*G140)</f>
+        <f>IF($B140="","",IF(F140&gt;0,(F140+IFERROR(VLOOKUP(E140,機種マスタ!$K$4:$L$6,2,FALSE),0))*G140,0))</f>
         <v/>
       </c>
     </row>
@@ -8526,7 +8527,7 @@
         <v/>
       </c>
       <c r="H141" s="30">
-        <f>IF($B141="","",F141*G141)</f>
+        <f>IF($B141="","",IF(F141&gt;0,(F141+IFERROR(VLOOKUP(E141,機種マスタ!$K$4:$L$6,2,FALSE),0))*G141,0))</f>
         <v/>
       </c>
     </row>
@@ -8551,7 +8552,7 @@
         <v/>
       </c>
       <c r="H142" s="30">
-        <f>IF($B142="","",F142*G142)</f>
+        <f>IF($B142="","",IF(F142&gt;0,(F142+IFERROR(VLOOKUP(E142,機種マスタ!$K$4:$L$6,2,FALSE),0))*G142,0))</f>
         <v/>
       </c>
     </row>
@@ -8576,7 +8577,7 @@
         <v/>
       </c>
       <c r="H143" s="30">
-        <f>IF($B143="","",F143*G143)</f>
+        <f>IF($B143="","",IF(F143&gt;0,(F143+IFERROR(VLOOKUP(E143,機種マスタ!$K$4:$L$6,2,FALSE),0))*G143,0))</f>
         <v/>
       </c>
     </row>
@@ -8601,7 +8602,7 @@
         <v/>
       </c>
       <c r="H144" s="30">
-        <f>IF($B144="","",F144*G144)</f>
+        <f>IF($B144="","",IF(F144&gt;0,(F144+IFERROR(VLOOKUP(E144,機種マスタ!$K$4:$L$6,2,FALSE),0))*G144,0))</f>
         <v/>
       </c>
     </row>
@@ -8626,7 +8627,7 @@
         <v/>
       </c>
       <c r="H145" s="30">
-        <f>IF($B145="","",F145*G145)</f>
+        <f>IF($B145="","",IF(F145&gt;0,(F145+IFERROR(VLOOKUP(E145,機種マスタ!$K$4:$L$6,2,FALSE),0))*G145,0))</f>
         <v/>
       </c>
     </row>
@@ -8651,7 +8652,7 @@
         <v/>
       </c>
       <c r="H146" s="30">
-        <f>IF($B146="","",F146*G146)</f>
+        <f>IF($B146="","",IF(F146&gt;0,(F146+IFERROR(VLOOKUP(E146,機種マスタ!$K$4:$L$6,2,FALSE),0))*G146,0))</f>
         <v/>
       </c>
     </row>
@@ -8676,7 +8677,7 @@
         <v/>
       </c>
       <c r="H147" s="30">
-        <f>IF($B147="","",F147*G147)</f>
+        <f>IF($B147="","",IF(F147&gt;0,(F147+IFERROR(VLOOKUP(E147,機種マスタ!$K$4:$L$6,2,FALSE),0))*G147,0))</f>
         <v/>
       </c>
     </row>
@@ -8701,7 +8702,7 @@
         <v/>
       </c>
       <c r="H148" s="30">
-        <f>IF($B148="","",F148*G148)</f>
+        <f>IF($B148="","",IF(F148&gt;0,(F148+IFERROR(VLOOKUP(E148,機種マスタ!$K$4:$L$6,2,FALSE),0))*G148,0))</f>
         <v/>
       </c>
     </row>
@@ -8726,7 +8727,7 @@
         <v/>
       </c>
       <c r="H149" s="30">
-        <f>IF($B149="","",F149*G149)</f>
+        <f>IF($B149="","",IF(F149&gt;0,(F149+IFERROR(VLOOKUP(E149,機種マスタ!$K$4:$L$6,2,FALSE),0))*G149,0))</f>
         <v/>
       </c>
     </row>
@@ -8751,7 +8752,7 @@
         <v/>
       </c>
       <c r="H150" s="30">
-        <f>IF($B150="","",F150*G150)</f>
+        <f>IF($B150="","",IF(F150&gt;0,(F150+IFERROR(VLOOKUP(E150,機種マスタ!$K$4:$L$6,2,FALSE),0))*G150,0))</f>
         <v/>
       </c>
     </row>
@@ -8776,7 +8777,7 @@
         <v/>
       </c>
       <c r="H151" s="30">
-        <f>IF($B151="","",F151*G151)</f>
+        <f>IF($B151="","",IF(F151&gt;0,(F151+IFERROR(VLOOKUP(E151,機種マスタ!$K$4:$L$6,2,FALSE),0))*G151,0))</f>
         <v/>
       </c>
     </row>
@@ -8801,7 +8802,7 @@
         <v/>
       </c>
       <c r="H152" s="30">
-        <f>IF($B152="","",F152*G152)</f>
+        <f>IF($B152="","",IF(F152&gt;0,(F152+IFERROR(VLOOKUP(E152,機種マスタ!$K$4:$L$6,2,FALSE),0))*G152,0))</f>
         <v/>
       </c>
     </row>
@@ -8826,7 +8827,7 @@
         <v/>
       </c>
       <c r="H153" s="30">
-        <f>IF($B153="","",F153*G153)</f>
+        <f>IF($B153="","",IF(F153&gt;0,(F153+IFERROR(VLOOKUP(E153,機種マスタ!$K$4:$L$6,2,FALSE),0))*G153,0))</f>
         <v/>
       </c>
     </row>
@@ -8851,7 +8852,7 @@
         <v/>
       </c>
       <c r="H154" s="30">
-        <f>IF($B154="","",F154*G154)</f>
+        <f>IF($B154="","",IF(F154&gt;0,(F154+IFERROR(VLOOKUP(E154,機種マスタ!$K$4:$L$6,2,FALSE),0))*G154,0))</f>
         <v/>
       </c>
     </row>
@@ -8876,7 +8877,7 @@
         <v/>
       </c>
       <c r="H155" s="30">
-        <f>IF($B155="","",F155*G155)</f>
+        <f>IF($B155="","",IF(F155&gt;0,(F155+IFERROR(VLOOKUP(E155,機種マスタ!$K$4:$L$6,2,FALSE),0))*G155,0))</f>
         <v/>
       </c>
     </row>
@@ -8901,7 +8902,7 @@
         <v/>
       </c>
       <c r="H156" s="30">
-        <f>IF($B156="","",F156*G156)</f>
+        <f>IF($B156="","",IF(F156&gt;0,(F156+IFERROR(VLOOKUP(E156,機種マスタ!$K$4:$L$6,2,FALSE),0))*G156,0))</f>
         <v/>
       </c>
     </row>
@@ -8926,7 +8927,7 @@
         <v/>
       </c>
       <c r="H157" s="30">
-        <f>IF($B157="","",F157*G157)</f>
+        <f>IF($B157="","",IF(F157&gt;0,(F157+IFERROR(VLOOKUP(E157,機種マスタ!$K$4:$L$6,2,FALSE),0))*G157,0))</f>
         <v/>
       </c>
     </row>
@@ -8951,7 +8952,7 @@
         <v/>
       </c>
       <c r="H158" s="30">
-        <f>IF($B158="","",F158*G158)</f>
+        <f>IF($B158="","",IF(F158&gt;0,(F158+IFERROR(VLOOKUP(E158,機種マスタ!$K$4:$L$6,2,FALSE),0))*G158,0))</f>
         <v/>
       </c>
     </row>
@@ -8976,7 +8977,7 @@
         <v/>
       </c>
       <c r="H159" s="30">
-        <f>IF($B159="","",F159*G159)</f>
+        <f>IF($B159="","",IF(F159&gt;0,(F159+IFERROR(VLOOKUP(E159,機種マスタ!$K$4:$L$6,2,FALSE),0))*G159,0))</f>
         <v/>
       </c>
     </row>
@@ -9001,7 +9002,7 @@
         <v/>
       </c>
       <c r="H160" s="30">
-        <f>IF($B160="","",F160*G160)</f>
+        <f>IF($B160="","",IF(F160&gt;0,(F160+IFERROR(VLOOKUP(E160,機種マスタ!$K$4:$L$6,2,FALSE),0))*G160,0))</f>
         <v/>
       </c>
     </row>
@@ -9026,7 +9027,7 @@
         <v/>
       </c>
       <c r="H161" s="30">
-        <f>IF($B161="","",F161*G161)</f>
+        <f>IF($B161="","",IF(F161&gt;0,(F161+IFERROR(VLOOKUP(E161,機種マスタ!$K$4:$L$6,2,FALSE),0))*G161,0))</f>
         <v/>
       </c>
     </row>
@@ -9051,7 +9052,7 @@
         <v/>
       </c>
       <c r="H162" s="30">
-        <f>IF($B162="","",F162*G162)</f>
+        <f>IF($B162="","",IF(F162&gt;0,(F162+IFERROR(VLOOKUP(E162,機種マスタ!$K$4:$L$6,2,FALSE),0))*G162,0))</f>
         <v/>
       </c>
     </row>
@@ -9076,7 +9077,7 @@
         <v/>
       </c>
       <c r="H163" s="30">
-        <f>IF($B163="","",F163*G163)</f>
+        <f>IF($B163="","",IF(F163&gt;0,(F163+IFERROR(VLOOKUP(E163,機種マスタ!$K$4:$L$6,2,FALSE),0))*G163,0))</f>
         <v/>
       </c>
     </row>
@@ -9101,7 +9102,7 @@
         <v/>
       </c>
       <c r="H164" s="30">
-        <f>IF($B164="","",F164*G164)</f>
+        <f>IF($B164="","",IF(F164&gt;0,(F164+IFERROR(VLOOKUP(E164,機種マスタ!$K$4:$L$6,2,FALSE),0))*G164,0))</f>
         <v/>
       </c>
     </row>
@@ -9126,7 +9127,7 @@
         <v/>
       </c>
       <c r="H165" s="30">
-        <f>IF($B165="","",F165*G165)</f>
+        <f>IF($B165="","",IF(F165&gt;0,(F165+IFERROR(VLOOKUP(E165,機種マスタ!$K$4:$L$6,2,FALSE),0))*G165,0))</f>
         <v/>
       </c>
     </row>
@@ -9151,7 +9152,7 @@
         <v/>
       </c>
       <c r="H166" s="30">
-        <f>IF($B166="","",F166*G166)</f>
+        <f>IF($B166="","",IF(F166&gt;0,(F166+IFERROR(VLOOKUP(E166,機種マスタ!$K$4:$L$6,2,FALSE),0))*G166,0))</f>
         <v/>
       </c>
     </row>
@@ -9176,7 +9177,7 @@
         <v/>
       </c>
       <c r="H167" s="30">
-        <f>IF($B167="","",F167*G167)</f>
+        <f>IF($B167="","",IF(F167&gt;0,(F167+IFERROR(VLOOKUP(E167,機種マスタ!$K$4:$L$6,2,FALSE),0))*G167,0))</f>
         <v/>
       </c>
     </row>
@@ -9201,7 +9202,7 @@
         <v/>
       </c>
       <c r="H168" s="30">
-        <f>IF($B168="","",F168*G168)</f>
+        <f>IF($B168="","",IF(F168&gt;0,(F168+IFERROR(VLOOKUP(E168,機種マスタ!$K$4:$L$6,2,FALSE),0))*G168,0))</f>
         <v/>
       </c>
     </row>
@@ -9226,7 +9227,7 @@
         <v/>
       </c>
       <c r="H169" s="30">
-        <f>IF($B169="","",F169*G169)</f>
+        <f>IF($B169="","",IF(F169&gt;0,(F169+IFERROR(VLOOKUP(E169,機種マスタ!$K$4:$L$6,2,FALSE),0))*G169,0))</f>
         <v/>
       </c>
     </row>
@@ -9251,7 +9252,7 @@
         <v/>
       </c>
       <c r="H170" s="30">
-        <f>IF($B170="","",F170*G170)</f>
+        <f>IF($B170="","",IF(F170&gt;0,(F170+IFERROR(VLOOKUP(E170,機種マスタ!$K$4:$L$6,2,FALSE),0))*G170,0))</f>
         <v/>
       </c>
     </row>
@@ -9276,7 +9277,7 @@
         <v/>
       </c>
       <c r="H171" s="30">
-        <f>IF($B171="","",F171*G171)</f>
+        <f>IF($B171="","",IF(F171&gt;0,(F171+IFERROR(VLOOKUP(E171,機種マスタ!$K$4:$L$6,2,FALSE),0))*G171,0))</f>
         <v/>
       </c>
     </row>
@@ -9301,7 +9302,7 @@
         <v/>
       </c>
       <c r="H172" s="30">
-        <f>IF($B172="","",F172*G172)</f>
+        <f>IF($B172="","",IF(F172&gt;0,(F172+IFERROR(VLOOKUP(E172,機種マスタ!$K$4:$L$6,2,FALSE),0))*G172,0))</f>
         <v/>
       </c>
     </row>
@@ -9326,7 +9327,7 @@
         <v/>
       </c>
       <c r="H173" s="30">
-        <f>IF($B173="","",F173*G173)</f>
+        <f>IF($B173="","",IF(F173&gt;0,(F173+IFERROR(VLOOKUP(E173,機種マスタ!$K$4:$L$6,2,FALSE),0))*G173,0))</f>
         <v/>
       </c>
     </row>
@@ -9351,7 +9352,7 @@
         <v/>
       </c>
       <c r="H174" s="30">
-        <f>IF($B174="","",F174*G174)</f>
+        <f>IF($B174="","",IF(F174&gt;0,(F174+IFERROR(VLOOKUP(E174,機種マスタ!$K$4:$L$6,2,FALSE),0))*G174,0))</f>
         <v/>
       </c>
     </row>
@@ -9376,7 +9377,7 @@
         <v/>
       </c>
       <c r="H175" s="30">
-        <f>IF($B175="","",F175*G175)</f>
+        <f>IF($B175="","",IF(F175&gt;0,(F175+IFERROR(VLOOKUP(E175,機種マスタ!$K$4:$L$6,2,FALSE),0))*G175,0))</f>
         <v/>
       </c>
     </row>
@@ -9401,7 +9402,7 @@
         <v/>
       </c>
       <c r="H176" s="30">
-        <f>IF($B176="","",F176*G176)</f>
+        <f>IF($B176="","",IF(F176&gt;0,(F176+IFERROR(VLOOKUP(E176,機種マスタ!$K$4:$L$6,2,FALSE),0))*G176,0))</f>
         <v/>
       </c>
     </row>
@@ -9426,7 +9427,7 @@
         <v/>
       </c>
       <c r="H177" s="30">
-        <f>IF($B177="","",F177*G177)</f>
+        <f>IF($B177="","",IF(F177&gt;0,(F177+IFERROR(VLOOKUP(E177,機種マスタ!$K$4:$L$6,2,FALSE),0))*G177,0))</f>
         <v/>
       </c>
     </row>
@@ -9451,7 +9452,7 @@
         <v/>
       </c>
       <c r="H178" s="30">
-        <f>IF($B178="","",F178*G178)</f>
+        <f>IF($B178="","",IF(F178&gt;0,(F178+IFERROR(VLOOKUP(E178,機種マスタ!$K$4:$L$6,2,FALSE),0))*G178,0))</f>
         <v/>
       </c>
     </row>
@@ -9476,7 +9477,7 @@
         <v/>
       </c>
       <c r="H179" s="30">
-        <f>IF($B179="","",F179*G179)</f>
+        <f>IF($B179="","",IF(F179&gt;0,(F179+IFERROR(VLOOKUP(E179,機種マスタ!$K$4:$L$6,2,FALSE),0))*G179,0))</f>
         <v/>
       </c>
     </row>
@@ -9501,7 +9502,7 @@
         <v/>
       </c>
       <c r="H180" s="30">
-        <f>IF($B180="","",F180*G180)</f>
+        <f>IF($B180="","",IF(F180&gt;0,(F180+IFERROR(VLOOKUP(E180,機種マスタ!$K$4:$L$6,2,FALSE),0))*G180,0))</f>
         <v/>
       </c>
     </row>
@@ -9526,7 +9527,7 @@
         <v/>
       </c>
       <c r="H181" s="30">
-        <f>IF($B181="","",F181*G181)</f>
+        <f>IF($B181="","",IF(F181&gt;0,(F181+IFERROR(VLOOKUP(E181,機種マスタ!$K$4:$L$6,2,FALSE),0))*G181,0))</f>
         <v/>
       </c>
     </row>
@@ -9551,7 +9552,7 @@
         <v/>
       </c>
       <c r="H182" s="30">
-        <f>IF($B182="","",F182*G182)</f>
+        <f>IF($B182="","",IF(F182&gt;0,(F182+IFERROR(VLOOKUP(E182,機種マスタ!$K$4:$L$6,2,FALSE),0))*G182,0))</f>
         <v/>
       </c>
     </row>
@@ -9576,7 +9577,7 @@
         <v/>
       </c>
       <c r="H183" s="30">
-        <f>IF($B183="","",F183*G183)</f>
+        <f>IF($B183="","",IF(F183&gt;0,(F183+IFERROR(VLOOKUP(E183,機種マスタ!$K$4:$L$6,2,FALSE),0))*G183,0))</f>
         <v/>
       </c>
     </row>
@@ -9601,7 +9602,7 @@
         <v/>
       </c>
       <c r="H184" s="30">
-        <f>IF($B184="","",F184*G184)</f>
+        <f>IF($B184="","",IF(F184&gt;0,(F184+IFERROR(VLOOKUP(E184,機種マスタ!$K$4:$L$6,2,FALSE),0))*G184,0))</f>
         <v/>
       </c>
     </row>
@@ -9626,7 +9627,7 @@
         <v/>
       </c>
       <c r="H185" s="30">
-        <f>IF($B185="","",F185*G185)</f>
+        <f>IF($B185="","",IF(F185&gt;0,(F185+IFERROR(VLOOKUP(E185,機種マスタ!$K$4:$L$6,2,FALSE),0))*G185,0))</f>
         <v/>
       </c>
     </row>
@@ -9651,7 +9652,7 @@
         <v/>
       </c>
       <c r="H186" s="30">
-        <f>IF($B186="","",F186*G186)</f>
+        <f>IF($B186="","",IF(F186&gt;0,(F186+IFERROR(VLOOKUP(E186,機種マスタ!$K$4:$L$6,2,FALSE),0))*G186,0))</f>
         <v/>
       </c>
     </row>
@@ -9676,7 +9677,7 @@
         <v/>
       </c>
       <c r="H187" s="30">
-        <f>IF($B187="","",F187*G187)</f>
+        <f>IF($B187="","",IF(F187&gt;0,(F187+IFERROR(VLOOKUP(E187,機種マスタ!$K$4:$L$6,2,FALSE),0))*G187,0))</f>
         <v/>
       </c>
     </row>
@@ -9701,7 +9702,7 @@
         <v/>
       </c>
       <c r="H188" s="30">
-        <f>IF($B188="","",F188*G188)</f>
+        <f>IF($B188="","",IF(F188&gt;0,(F188+IFERROR(VLOOKUP(E188,機種マスタ!$K$4:$L$6,2,FALSE),0))*G188,0))</f>
         <v/>
       </c>
     </row>
@@ -9726,7 +9727,7 @@
         <v/>
       </c>
       <c r="H189" s="30">
-        <f>IF($B189="","",F189*G189)</f>
+        <f>IF($B189="","",IF(F189&gt;0,(F189+IFERROR(VLOOKUP(E189,機種マスタ!$K$4:$L$6,2,FALSE),0))*G189,0))</f>
         <v/>
       </c>
     </row>
@@ -9751,7 +9752,7 @@
         <v/>
       </c>
       <c r="H190" s="30">
-        <f>IF($B190="","",F190*G190)</f>
+        <f>IF($B190="","",IF(F190&gt;0,(F190+IFERROR(VLOOKUP(E190,機種マスタ!$K$4:$L$6,2,FALSE),0))*G190,0))</f>
         <v/>
       </c>
     </row>
@@ -9776,7 +9777,7 @@
         <v/>
       </c>
       <c r="H191" s="30">
-        <f>IF($B191="","",F191*G191)</f>
+        <f>IF($B191="","",IF(F191&gt;0,(F191+IFERROR(VLOOKUP(E191,機種マスタ!$K$4:$L$6,2,FALSE),0))*G191,0))</f>
         <v/>
       </c>
     </row>
@@ -9801,7 +9802,7 @@
         <v/>
       </c>
       <c r="H192" s="30">
-        <f>IF($B192="","",F192*G192)</f>
+        <f>IF($B192="","",IF(F192&gt;0,(F192+IFERROR(VLOOKUP(E192,機種マスタ!$K$4:$L$6,2,FALSE),0))*G192,0))</f>
         <v/>
       </c>
     </row>
@@ -9826,7 +9827,7 @@
         <v/>
       </c>
       <c r="H193" s="30">
-        <f>IF($B193="","",F193*G193)</f>
+        <f>IF($B193="","",IF(F193&gt;0,(F193+IFERROR(VLOOKUP(E193,機種マスタ!$K$4:$L$6,2,FALSE),0))*G193,0))</f>
         <v/>
       </c>
     </row>
@@ -9851,7 +9852,7 @@
         <v/>
       </c>
       <c r="H194" s="30">
-        <f>IF($B194="","",F194*G194)</f>
+        <f>IF($B194="","",IF(F194&gt;0,(F194+IFERROR(VLOOKUP(E194,機種マスタ!$K$4:$L$6,2,FALSE),0))*G194,0))</f>
         <v/>
       </c>
     </row>
@@ -9876,7 +9877,7 @@
         <v/>
       </c>
       <c r="H195" s="30">
-        <f>IF($B195="","",F195*G195)</f>
+        <f>IF($B195="","",IF(F195&gt;0,(F195+IFERROR(VLOOKUP(E195,機種マスタ!$K$4:$L$6,2,FALSE),0))*G195,0))</f>
         <v/>
       </c>
     </row>
@@ -9901,7 +9902,7 @@
         <v/>
       </c>
       <c r="H196" s="30">
-        <f>IF($B196="","",F196*G196)</f>
+        <f>IF($B196="","",IF(F196&gt;0,(F196+IFERROR(VLOOKUP(E196,機種マスタ!$K$4:$L$6,2,FALSE),0))*G196,0))</f>
         <v/>
       </c>
     </row>
@@ -9926,7 +9927,7 @@
         <v/>
       </c>
       <c r="H197" s="30">
-        <f>IF($B197="","",F197*G197)</f>
+        <f>IF($B197="","",IF(F197&gt;0,(F197+IFERROR(VLOOKUP(E197,機種マスタ!$K$4:$L$6,2,FALSE),0))*G197,0))</f>
         <v/>
       </c>
     </row>
@@ -9951,7 +9952,7 @@
         <v/>
       </c>
       <c r="H198" s="30">
-        <f>IF($B198="","",F198*G198)</f>
+        <f>IF($B198="","",IF(F198&gt;0,(F198+IFERROR(VLOOKUP(E198,機種マスタ!$K$4:$L$6,2,FALSE),0))*G198,0))</f>
         <v/>
       </c>
     </row>
@@ -9976,7 +9977,7 @@
         <v/>
       </c>
       <c r="H199" s="30">
-        <f>IF($B199="","",F199*G199)</f>
+        <f>IF($B199="","",IF(F199&gt;0,(F199+IFERROR(VLOOKUP(E199,機種マスタ!$K$4:$L$6,2,FALSE),0))*G199,0))</f>
         <v/>
       </c>
     </row>
@@ -10001,7 +10002,7 @@
         <v/>
       </c>
       <c r="H200" s="30">
-        <f>IF($B200="","",F200*G200)</f>
+        <f>IF($B200="","",IF(F200&gt;0,(F200+IFERROR(VLOOKUP(E200,機種マスタ!$K$4:$L$6,2,FALSE),0))*G200,0))</f>
         <v/>
       </c>
     </row>
@@ -10026,7 +10027,7 @@
         <v/>
       </c>
       <c r="H201" s="30">
-        <f>IF($B201="","",F201*G201)</f>
+        <f>IF($B201="","",IF(F201&gt;0,(F201+IFERROR(VLOOKUP(E201,機種マスタ!$K$4:$L$6,2,FALSE),0))*G201,0))</f>
         <v/>
       </c>
     </row>
@@ -10051,7 +10052,7 @@
         <v/>
       </c>
       <c r="H202" s="30">
-        <f>IF($B202="","",F202*G202)</f>
+        <f>IF($B202="","",IF(F202&gt;0,(F202+IFERROR(VLOOKUP(E202,機種マスタ!$K$4:$L$6,2,FALSE),0))*G202,0))</f>
         <v/>
       </c>
     </row>
@@ -10076,7 +10077,7 @@
         <v/>
       </c>
       <c r="H203" s="30">
-        <f>IF($B203="","",F203*G203)</f>
+        <f>IF($B203="","",IF(F203&gt;0,(F203+IFERROR(VLOOKUP(E203,機種マスタ!$K$4:$L$6,2,FALSE),0))*G203,0))</f>
         <v/>
       </c>
     </row>
@@ -10101,7 +10102,7 @@
         <v/>
       </c>
       <c r="H204" s="30">
-        <f>IF($B204="","",F204*G204)</f>
+        <f>IF($B204="","",IF(F204&gt;0,(F204+IFERROR(VLOOKUP(E204,機種マスタ!$K$4:$L$6,2,FALSE),0))*G204,0))</f>
         <v/>
       </c>
     </row>
@@ -10126,7 +10127,7 @@
         <v/>
       </c>
       <c r="H205" s="30">
-        <f>IF($B205="","",F205*G205)</f>
+        <f>IF($B205="","",IF(F205&gt;0,(F205+IFERROR(VLOOKUP(E205,機種マスタ!$K$4:$L$6,2,FALSE),0))*G205,0))</f>
         <v/>
       </c>
     </row>
@@ -10151,7 +10152,7 @@
         <v/>
       </c>
       <c r="H206" s="30">
-        <f>IF($B206="","",F206*G206)</f>
+        <f>IF($B206="","",IF(F206&gt;0,(F206+IFERROR(VLOOKUP(E206,機種マスタ!$K$4:$L$6,2,FALSE),0))*G206,0))</f>
         <v/>
       </c>
     </row>
@@ -10176,7 +10177,7 @@
         <v/>
       </c>
       <c r="H207" s="30">
-        <f>IF($B207="","",F207*G207)</f>
+        <f>IF($B207="","",IF(F207&gt;0,(F207+IFERROR(VLOOKUP(E207,機種マスタ!$K$4:$L$6,2,FALSE),0))*G207,0))</f>
         <v/>
       </c>
     </row>
@@ -10201,7 +10202,7 @@
         <v/>
       </c>
       <c r="H208" s="30">
-        <f>IF($B208="","",F208*G208)</f>
+        <f>IF($B208="","",IF(F208&gt;0,(F208+IFERROR(VLOOKUP(E208,機種マスタ!$K$4:$L$6,2,FALSE),0))*G208,0))</f>
         <v/>
       </c>
     </row>
@@ -10226,7 +10227,7 @@
         <v/>
       </c>
       <c r="H209" s="30">
-        <f>IF($B209="","",F209*G209)</f>
+        <f>IF($B209="","",IF(F209&gt;0,(F209+IFERROR(VLOOKUP(E209,機種マスタ!$K$4:$L$6,2,FALSE),0))*G209,0))</f>
         <v/>
       </c>
     </row>
@@ -10251,7 +10252,7 @@
         <v/>
       </c>
       <c r="H210" s="30">
-        <f>IF($B210="","",F210*G210)</f>
+        <f>IF($B210="","",IF(F210&gt;0,(F210+IFERROR(VLOOKUP(E210,機種マスタ!$K$4:$L$6,2,FALSE),0))*G210,0))</f>
         <v/>
       </c>
     </row>
@@ -10276,7 +10277,7 @@
         <v/>
       </c>
       <c r="H211" s="30">
-        <f>IF($B211="","",F211*G211)</f>
+        <f>IF($B211="","",IF(F211&gt;0,(F211+IFERROR(VLOOKUP(E211,機種マスタ!$K$4:$L$6,2,FALSE),0))*G211,0))</f>
         <v/>
       </c>
     </row>
@@ -10301,7 +10302,7 @@
         <v/>
       </c>
       <c r="H212" s="30">
-        <f>IF($B212="","",F212*G212)</f>
+        <f>IF($B212="","",IF(F212&gt;0,(F212+IFERROR(VLOOKUP(E212,機種マスタ!$K$4:$L$6,2,FALSE),0))*G212,0))</f>
         <v/>
       </c>
     </row>
@@ -10326,7 +10327,7 @@
         <v/>
       </c>
       <c r="H213" s="30">
-        <f>IF($B213="","",F213*G213)</f>
+        <f>IF($B213="","",IF(F213&gt;0,(F213+IFERROR(VLOOKUP(E213,機種マスタ!$K$4:$L$6,2,FALSE),0))*G213,0))</f>
         <v/>
       </c>
     </row>
@@ -10351,7 +10352,7 @@
         <v/>
       </c>
       <c r="H214" s="30">
-        <f>IF($B214="","",F214*G214)</f>
+        <f>IF($B214="","",IF(F214&gt;0,(F214+IFERROR(VLOOKUP(E214,機種マスタ!$K$4:$L$6,2,FALSE),0))*G214,0))</f>
         <v/>
       </c>
     </row>
@@ -10376,7 +10377,7 @@
         <v/>
       </c>
       <c r="H215" s="30">
-        <f>IF($B215="","",F215*G215)</f>
+        <f>IF($B215="","",IF(F215&gt;0,(F215+IFERROR(VLOOKUP(E215,機種マスタ!$K$4:$L$6,2,FALSE),0))*G215,0))</f>
         <v/>
       </c>
     </row>
@@ -10401,7 +10402,7 @@
         <v/>
       </c>
       <c r="H216" s="30">
-        <f>IF($B216="","",F216*G216)</f>
+        <f>IF($B216="","",IF(F216&gt;0,(F216+IFERROR(VLOOKUP(E216,機種マスタ!$K$4:$L$6,2,FALSE),0))*G216,0))</f>
         <v/>
       </c>
     </row>
@@ -10426,7 +10427,7 @@
         <v/>
       </c>
       <c r="H217" s="30">
-        <f>IF($B217="","",F217*G217)</f>
+        <f>IF($B217="","",IF(F217&gt;0,(F217+IFERROR(VLOOKUP(E217,機種マスタ!$K$4:$L$6,2,FALSE),0))*G217,0))</f>
         <v/>
       </c>
     </row>
@@ -10451,7 +10452,7 @@
         <v/>
       </c>
       <c r="H218" s="30">
-        <f>IF($B218="","",F218*G218)</f>
+        <f>IF($B218="","",IF(F218&gt;0,(F218+IFERROR(VLOOKUP(E218,機種マスタ!$K$4:$L$6,2,FALSE),0))*G218,0))</f>
         <v/>
       </c>
     </row>
@@ -10476,7 +10477,7 @@
         <v/>
       </c>
       <c r="H219" s="30">
-        <f>IF($B219="","",F219*G219)</f>
+        <f>IF($B219="","",IF(F219&gt;0,(F219+IFERROR(VLOOKUP(E219,機種マスタ!$K$4:$L$6,2,FALSE),0))*G219,0))</f>
         <v/>
       </c>
     </row>
@@ -10501,7 +10502,7 @@
         <v/>
       </c>
       <c r="H220" s="30">
-        <f>IF($B220="","",F220*G220)</f>
+        <f>IF($B220="","",IF(F220&gt;0,(F220+IFERROR(VLOOKUP(E220,機種マスタ!$K$4:$L$6,2,FALSE),0))*G220,0))</f>
         <v/>
       </c>
     </row>
@@ -10526,7 +10527,7 @@
         <v/>
       </c>
       <c r="H221" s="30">
-        <f>IF($B221="","",F221*G221)</f>
+        <f>IF($B221="","",IF(F221&gt;0,(F221+IFERROR(VLOOKUP(E221,機種マスタ!$K$4:$L$6,2,FALSE),0))*G221,0))</f>
         <v/>
       </c>
     </row>
@@ -10551,7 +10552,7 @@
         <v/>
       </c>
       <c r="H222" s="30">
-        <f>IF($B222="","",F222*G222)</f>
+        <f>IF($B222="","",IF(F222&gt;0,(F222+IFERROR(VLOOKUP(E222,機種マスタ!$K$4:$L$6,2,FALSE),0))*G222,0))</f>
         <v/>
       </c>
     </row>
@@ -10576,7 +10577,7 @@
         <v/>
       </c>
       <c r="H223" s="30">
-        <f>IF($B223="","",F223*G223)</f>
+        <f>IF($B223="","",IF(F223&gt;0,(F223+IFERROR(VLOOKUP(E223,機種マスタ!$K$4:$L$6,2,FALSE),0))*G223,0))</f>
         <v/>
       </c>
     </row>
@@ -10601,7 +10602,7 @@
         <v/>
       </c>
       <c r="H224" s="30">
-        <f>IF($B224="","",F224*G224)</f>
+        <f>IF($B224="","",IF(F224&gt;0,(F224+IFERROR(VLOOKUP(E224,機種マスタ!$K$4:$L$6,2,FALSE),0))*G224,0))</f>
         <v/>
       </c>
     </row>
@@ -10626,7 +10627,7 @@
         <v/>
       </c>
       <c r="H225" s="30">
-        <f>IF($B225="","",F225*G225)</f>
+        <f>IF($B225="","",IF(F225&gt;0,(F225+IFERROR(VLOOKUP(E225,機種マスタ!$K$4:$L$6,2,FALSE),0))*G225,0))</f>
         <v/>
       </c>
     </row>
@@ -10651,7 +10652,7 @@
         <v/>
       </c>
       <c r="H226" s="30">
-        <f>IF($B226="","",F226*G226)</f>
+        <f>IF($B226="","",IF(F226&gt;0,(F226+IFERROR(VLOOKUP(E226,機種マスタ!$K$4:$L$6,2,FALSE),0))*G226,0))</f>
         <v/>
       </c>
     </row>
@@ -10676,7 +10677,7 @@
         <v/>
       </c>
       <c r="H227" s="30">
-        <f>IF($B227="","",F227*G227)</f>
+        <f>IF($B227="","",IF(F227&gt;0,(F227+IFERROR(VLOOKUP(E227,機種マスタ!$K$4:$L$6,2,FALSE),0))*G227,0))</f>
         <v/>
       </c>
     </row>
@@ -10701,7 +10702,7 @@
         <v/>
       </c>
       <c r="H228" s="30">
-        <f>IF($B228="","",F228*G228)</f>
+        <f>IF($B228="","",IF(F228&gt;0,(F228+IFERROR(VLOOKUP(E228,機種マスタ!$K$4:$L$6,2,FALSE),0))*G228,0))</f>
         <v/>
       </c>
     </row>
@@ -10726,7 +10727,7 @@
         <v/>
       </c>
       <c r="H229" s="30">
-        <f>IF($B229="","",F229*G229)</f>
+        <f>IF($B229="","",IF(F229&gt;0,(F229+IFERROR(VLOOKUP(E229,機種マスタ!$K$4:$L$6,2,FALSE),0))*G229,0))</f>
         <v/>
       </c>
     </row>
@@ -10751,7 +10752,7 @@
         <v/>
       </c>
       <c r="H230" s="30">
-        <f>IF($B230="","",F230*G230)</f>
+        <f>IF($B230="","",IF(F230&gt;0,(F230+IFERROR(VLOOKUP(E230,機種マスタ!$K$4:$L$6,2,FALSE),0))*G230,0))</f>
         <v/>
       </c>
     </row>
@@ -10776,7 +10777,7 @@
         <v/>
       </c>
       <c r="H231" s="30">
-        <f>IF($B231="","",F231*G231)</f>
+        <f>IF($B231="","",IF(F231&gt;0,(F231+IFERROR(VLOOKUP(E231,機種マスタ!$K$4:$L$6,2,FALSE),0))*G231,0))</f>
         <v/>
       </c>
     </row>
@@ -10801,7 +10802,7 @@
         <v/>
       </c>
       <c r="H232" s="30">
-        <f>IF($B232="","",F232*G232)</f>
+        <f>IF($B232="","",IF(F232&gt;0,(F232+IFERROR(VLOOKUP(E232,機種マスタ!$K$4:$L$6,2,FALSE),0))*G232,0))</f>
         <v/>
       </c>
     </row>
@@ -10826,7 +10827,7 @@
         <v/>
       </c>
       <c r="H233" s="30">
-        <f>IF($B233="","",F233*G233)</f>
+        <f>IF($B233="","",IF(F233&gt;0,(F233+IFERROR(VLOOKUP(E233,機種マスタ!$K$4:$L$6,2,FALSE),0))*G233,0))</f>
         <v/>
       </c>
     </row>
@@ -10851,7 +10852,7 @@
         <v/>
       </c>
       <c r="H234" s="30">
-        <f>IF($B234="","",F234*G234)</f>
+        <f>IF($B234="","",IF(F234&gt;0,(F234+IFERROR(VLOOKUP(E234,機種マスタ!$K$4:$L$6,2,FALSE),0))*G234,0))</f>
         <v/>
       </c>
     </row>
@@ -10876,7 +10877,7 @@
         <v/>
       </c>
       <c r="H235" s="30">
-        <f>IF($B235="","",F235*G235)</f>
+        <f>IF($B235="","",IF(F235&gt;0,(F235+IFERROR(VLOOKUP(E235,機種マスタ!$K$4:$L$6,2,FALSE),0))*G235,0))</f>
         <v/>
       </c>
     </row>
@@ -10901,7 +10902,7 @@
         <v/>
       </c>
       <c r="H236" s="30">
-        <f>IF($B236="","",F236*G236)</f>
+        <f>IF($B236="","",IF(F236&gt;0,(F236+IFERROR(VLOOKUP(E236,機種マスタ!$K$4:$L$6,2,FALSE),0))*G236,0))</f>
         <v/>
       </c>
     </row>
@@ -10926,7 +10927,7 @@
         <v/>
       </c>
       <c r="H237" s="30">
-        <f>IF($B237="","",F237*G237)</f>
+        <f>IF($B237="","",IF(F237&gt;0,(F237+IFERROR(VLOOKUP(E237,機種マスタ!$K$4:$L$6,2,FALSE),0))*G237,0))</f>
         <v/>
       </c>
     </row>
@@ -10951,7 +10952,7 @@
         <v/>
       </c>
       <c r="H238" s="30">
-        <f>IF($B238="","",F238*G238)</f>
+        <f>IF($B238="","",IF(F238&gt;0,(F238+IFERROR(VLOOKUP(E238,機種マスタ!$K$4:$L$6,2,FALSE),0))*G238,0))</f>
         <v/>
       </c>
     </row>
@@ -10976,7 +10977,7 @@
         <v/>
       </c>
       <c r="H239" s="30">
-        <f>IF($B239="","",F239*G239)</f>
+        <f>IF($B239="","",IF(F239&gt;0,(F239+IFERROR(VLOOKUP(E239,機種マスタ!$K$4:$L$6,2,FALSE),0))*G239,0))</f>
         <v/>
       </c>
     </row>
@@ -11001,7 +11002,7 @@
         <v/>
       </c>
       <c r="H240" s="30">
-        <f>IF($B240="","",F240*G240)</f>
+        <f>IF($B240="","",IF(F240&gt;0,(F240+IFERROR(VLOOKUP(E240,機種マスタ!$K$4:$L$6,2,FALSE),0))*G240,0))</f>
         <v/>
       </c>
     </row>
@@ -11026,7 +11027,7 @@
         <v/>
       </c>
       <c r="H241" s="30">
-        <f>IF($B241="","",F241*G241)</f>
+        <f>IF($B241="","",IF(F241&gt;0,(F241+IFERROR(VLOOKUP(E241,機種マスタ!$K$4:$L$6,2,FALSE),0))*G241,0))</f>
         <v/>
       </c>
     </row>
@@ -11051,7 +11052,7 @@
         <v/>
       </c>
       <c r="H242" s="30">
-        <f>IF($B242="","",F242*G242)</f>
+        <f>IF($B242="","",IF(F242&gt;0,(F242+IFERROR(VLOOKUP(E242,機種マスタ!$K$4:$L$6,2,FALSE),0))*G242,0))</f>
         <v/>
       </c>
     </row>
@@ -11076,7 +11077,7 @@
         <v/>
       </c>
       <c r="H243" s="30">
-        <f>IF($B243="","",F243*G243)</f>
+        <f>IF($B243="","",IF(F243&gt;0,(F243+IFERROR(VLOOKUP(E243,機種マスタ!$K$4:$L$6,2,FALSE),0))*G243,0))</f>
         <v/>
       </c>
     </row>
@@ -11101,7 +11102,7 @@
         <v/>
       </c>
       <c r="H244" s="30">
-        <f>IF($B244="","",F244*G244)</f>
+        <f>IF($B244="","",IF(F244&gt;0,(F244+IFERROR(VLOOKUP(E244,機種マスタ!$K$4:$L$6,2,FALSE),0))*G244,0))</f>
         <v/>
       </c>
     </row>
@@ -11126,7 +11127,7 @@
         <v/>
       </c>
       <c r="H245" s="30">
-        <f>IF($B245="","",F245*G245)</f>
+        <f>IF($B245="","",IF(F245&gt;0,(F245+IFERROR(VLOOKUP(E245,機種マスタ!$K$4:$L$6,2,FALSE),0))*G245,0))</f>
         <v/>
       </c>
     </row>
@@ -11151,7 +11152,7 @@
         <v/>
       </c>
       <c r="H246" s="30">
-        <f>IF($B246="","",F246*G246)</f>
+        <f>IF($B246="","",IF(F246&gt;0,(F246+IFERROR(VLOOKUP(E246,機種マスタ!$K$4:$L$6,2,FALSE),0))*G246,0))</f>
         <v/>
       </c>
     </row>
@@ -11176,7 +11177,7 @@
         <v/>
       </c>
       <c r="H247" s="30">
-        <f>IF($B247="","",F247*G247)</f>
+        <f>IF($B247="","",IF(F247&gt;0,(F247+IFERROR(VLOOKUP(E247,機種マスタ!$K$4:$L$6,2,FALSE),0))*G247,0))</f>
         <v/>
       </c>
     </row>
@@ -11201,7 +11202,7 @@
         <v/>
       </c>
       <c r="H248" s="30">
-        <f>IF($B248="","",F248*G248)</f>
+        <f>IF($B248="","",IF(F248&gt;0,(F248+IFERROR(VLOOKUP(E248,機種マスタ!$K$4:$L$6,2,FALSE),0))*G248,0))</f>
         <v/>
       </c>
     </row>
@@ -11226,7 +11227,7 @@
         <v/>
       </c>
       <c r="H249" s="30">
-        <f>IF($B249="","",F249*G249)</f>
+        <f>IF($B249="","",IF(F249&gt;0,(F249+IFERROR(VLOOKUP(E249,機種マスタ!$K$4:$L$6,2,FALSE),0))*G249,0))</f>
         <v/>
       </c>
     </row>
@@ -11251,7 +11252,7 @@
         <v/>
       </c>
       <c r="H250" s="30">
-        <f>IF($B250="","",F250*G250)</f>
+        <f>IF($B250="","",IF(F250&gt;0,(F250+IFERROR(VLOOKUP(E250,機種マスタ!$K$4:$L$6,2,FALSE),0))*G250,0))</f>
         <v/>
       </c>
     </row>
@@ -11276,7 +11277,7 @@
         <v/>
       </c>
       <c r="H251" s="30">
-        <f>IF($B251="","",F251*G251)</f>
+        <f>IF($B251="","",IF(F251&gt;0,(F251+IFERROR(VLOOKUP(E251,機種マスタ!$K$4:$L$6,2,FALSE),0))*G251,0))</f>
         <v/>
       </c>
     </row>
@@ -11301,7 +11302,7 @@
         <v/>
       </c>
       <c r="H252" s="30">
-        <f>IF($B252="","",F252*G252)</f>
+        <f>IF($B252="","",IF(F252&gt;0,(F252+IFERROR(VLOOKUP(E252,機種マスタ!$K$4:$L$6,2,FALSE),0))*G252,0))</f>
         <v/>
       </c>
     </row>
@@ -11326,7 +11327,7 @@
         <v/>
       </c>
       <c r="H253" s="30">
-        <f>IF($B253="","",F253*G253)</f>
+        <f>IF($B253="","",IF(F253&gt;0,(F253+IFERROR(VLOOKUP(E253,機種マスタ!$K$4:$L$6,2,FALSE),0))*G253,0))</f>
         <v/>
       </c>
     </row>
@@ -11351,7 +11352,7 @@
         <v/>
       </c>
       <c r="H254" s="30">
-        <f>IF($B254="","",F254*G254)</f>
+        <f>IF($B254="","",IF(F254&gt;0,(F254+IFERROR(VLOOKUP(E254,機種マスタ!$K$4:$L$6,2,FALSE),0))*G254,0))</f>
         <v/>
       </c>
     </row>
@@ -11376,7 +11377,7 @@
         <v/>
       </c>
       <c r="H255" s="30">
-        <f>IF($B255="","",F255*G255)</f>
+        <f>IF($B255="","",IF(F255&gt;0,(F255+IFERROR(VLOOKUP(E255,機種マスタ!$K$4:$L$6,2,FALSE),0))*G255,0))</f>
         <v/>
       </c>
     </row>
@@ -11401,7 +11402,7 @@
         <v/>
       </c>
       <c r="H256" s="30">
-        <f>IF($B256="","",F256*G256)</f>
+        <f>IF($B256="","",IF(F256&gt;0,(F256+IFERROR(VLOOKUP(E256,機種マスタ!$K$4:$L$6,2,FALSE),0))*G256,0))</f>
         <v/>
       </c>
     </row>
@@ -11426,7 +11427,7 @@
         <v/>
       </c>
       <c r="H257" s="30">
-        <f>IF($B257="","",F257*G257)</f>
+        <f>IF($B257="","",IF(F257&gt;0,(F257+IFERROR(VLOOKUP(E257,機種マスタ!$K$4:$L$6,2,FALSE),0))*G257,0))</f>
         <v/>
       </c>
     </row>
@@ -11451,7 +11452,7 @@
         <v/>
       </c>
       <c r="H258" s="30">
-        <f>IF($B258="","",F258*G258)</f>
+        <f>IF($B258="","",IF(F258&gt;0,(F258+IFERROR(VLOOKUP(E258,機種マスタ!$K$4:$L$6,2,FALSE),0))*G258,0))</f>
         <v/>
       </c>
     </row>
@@ -11476,7 +11477,7 @@
         <v/>
       </c>
       <c r="H259" s="30">
-        <f>IF($B259="","",F259*G259)</f>
+        <f>IF($B259="","",IF(F259&gt;0,(F259+IFERROR(VLOOKUP(E259,機種マスタ!$K$4:$L$6,2,FALSE),0))*G259,0))</f>
         <v/>
       </c>
     </row>
@@ -11501,7 +11502,7 @@
         <v/>
       </c>
       <c r="H260" s="30">
-        <f>IF($B260="","",F260*G260)</f>
+        <f>IF($B260="","",IF(F260&gt;0,(F260+IFERROR(VLOOKUP(E260,機種マスタ!$K$4:$L$6,2,FALSE),0))*G260,0))</f>
         <v/>
       </c>
     </row>
@@ -11526,7 +11527,7 @@
         <v/>
       </c>
       <c r="H261" s="30">
-        <f>IF($B261="","",F261*G261)</f>
+        <f>IF($B261="","",IF(F261&gt;0,(F261+IFERROR(VLOOKUP(E261,機種マスタ!$K$4:$L$6,2,FALSE),0))*G261,0))</f>
         <v/>
       </c>
     </row>
@@ -11551,7 +11552,7 @@
         <v/>
       </c>
       <c r="H262" s="30">
-        <f>IF($B262="","",F262*G262)</f>
+        <f>IF($B262="","",IF(F262&gt;0,(F262+IFERROR(VLOOKUP(E262,機種マスタ!$K$4:$L$6,2,FALSE),0))*G262,0))</f>
         <v/>
       </c>
     </row>
@@ -11576,7 +11577,7 @@
         <v/>
       </c>
       <c r="H263" s="30">
-        <f>IF($B263="","",F263*G263)</f>
+        <f>IF($B263="","",IF(F263&gt;0,(F263+IFERROR(VLOOKUP(E263,機種マスタ!$K$4:$L$6,2,FALSE),0))*G263,0))</f>
         <v/>
       </c>
     </row>
@@ -11601,7 +11602,7 @@
         <v/>
       </c>
       <c r="H264" s="30">
-        <f>IF($B264="","",F264*G264)</f>
+        <f>IF($B264="","",IF(F264&gt;0,(F264+IFERROR(VLOOKUP(E264,機種マスタ!$K$4:$L$6,2,FALSE),0))*G264,0))</f>
         <v/>
       </c>
     </row>
@@ -11626,7 +11627,7 @@
         <v/>
       </c>
       <c r="H265" s="30">
-        <f>IF($B265="","",F265*G265)</f>
+        <f>IF($B265="","",IF(F265&gt;0,(F265+IFERROR(VLOOKUP(E265,機種マスタ!$K$4:$L$6,2,FALSE),0))*G265,0))</f>
         <v/>
       </c>
     </row>
@@ -11651,7 +11652,7 @@
         <v/>
       </c>
       <c r="H266" s="30">
-        <f>IF($B266="","",F266*G266)</f>
+        <f>IF($B266="","",IF(F266&gt;0,(F266+IFERROR(VLOOKUP(E266,機種マスタ!$K$4:$L$6,2,FALSE),0))*G266,0))</f>
         <v/>
       </c>
     </row>
@@ -11676,7 +11677,7 @@
         <v/>
       </c>
       <c r="H267" s="30">
-        <f>IF($B267="","",F267*G267)</f>
+        <f>IF($B267="","",IF(F267&gt;0,(F267+IFERROR(VLOOKUP(E267,機種マスタ!$K$4:$L$6,2,FALSE),0))*G267,0))</f>
         <v/>
       </c>
     </row>
@@ -11701,7 +11702,7 @@
         <v/>
       </c>
       <c r="H268" s="30">
-        <f>IF($B268="","",F268*G268)</f>
+        <f>IF($B268="","",IF(F268&gt;0,(F268+IFERROR(VLOOKUP(E268,機種マスタ!$K$4:$L$6,2,FALSE),0))*G268,0))</f>
         <v/>
       </c>
     </row>
@@ -11726,7 +11727,7 @@
         <v/>
       </c>
       <c r="H269" s="30">
-        <f>IF($B269="","",F269*G269)</f>
+        <f>IF($B269="","",IF(F269&gt;0,(F269+IFERROR(VLOOKUP(E269,機種マスタ!$K$4:$L$6,2,FALSE),0))*G269,0))</f>
         <v/>
       </c>
     </row>
@@ -11751,7 +11752,7 @@
         <v/>
       </c>
       <c r="H270" s="30">
-        <f>IF($B270="","",F270*G270)</f>
+        <f>IF($B270="","",IF(F270&gt;0,(F270+IFERROR(VLOOKUP(E270,機種マスタ!$K$4:$L$6,2,FALSE),0))*G270,0))</f>
         <v/>
       </c>
     </row>
@@ -11776,7 +11777,7 @@
         <v/>
       </c>
       <c r="H271" s="30">
-        <f>IF($B271="","",F271*G271)</f>
+        <f>IF($B271="","",IF(F271&gt;0,(F271+IFERROR(VLOOKUP(E271,機種マスタ!$K$4:$L$6,2,FALSE),0))*G271,0))</f>
         <v/>
       </c>
     </row>
@@ -11801,7 +11802,7 @@
         <v/>
       </c>
       <c r="H272" s="30">
-        <f>IF($B272="","",F272*G272)</f>
+        <f>IF($B272="","",IF(F272&gt;0,(F272+IFERROR(VLOOKUP(E272,機種マスタ!$K$4:$L$6,2,FALSE),0))*G272,0))</f>
         <v/>
       </c>
     </row>
@@ -11826,7 +11827,7 @@
         <v/>
       </c>
       <c r="H273" s="30">
-        <f>IF($B273="","",F273*G273)</f>
+        <f>IF($B273="","",IF(F273&gt;0,(F273+IFERROR(VLOOKUP(E273,機種マスタ!$K$4:$L$6,2,FALSE),0))*G273,0))</f>
         <v/>
       </c>
     </row>
@@ -11851,7 +11852,7 @@
         <v/>
       </c>
       <c r="H274" s="30">
-        <f>IF($B274="","",F274*G274)</f>
+        <f>IF($B274="","",IF(F274&gt;0,(F274+IFERROR(VLOOKUP(E274,機種マスタ!$K$4:$L$6,2,FALSE),0))*G274,0))</f>
         <v/>
       </c>
     </row>
@@ -11876,7 +11877,7 @@
         <v/>
       </c>
       <c r="H275" s="30">
-        <f>IF($B275="","",F275*G275)</f>
+        <f>IF($B275="","",IF(F275&gt;0,(F275+IFERROR(VLOOKUP(E275,機種マスタ!$K$4:$L$6,2,FALSE),0))*G275,0))</f>
         <v/>
       </c>
     </row>
@@ -11901,7 +11902,7 @@
         <v/>
       </c>
       <c r="H276" s="30">
-        <f>IF($B276="","",F276*G276)</f>
+        <f>IF($B276="","",IF(F276&gt;0,(F276+IFERROR(VLOOKUP(E276,機種マスタ!$K$4:$L$6,2,FALSE),0))*G276,0))</f>
         <v/>
       </c>
     </row>
@@ -11926,7 +11927,7 @@
         <v/>
       </c>
       <c r="H277" s="30">
-        <f>IF($B277="","",F277*G277)</f>
+        <f>IF($B277="","",IF(F277&gt;0,(F277+IFERROR(VLOOKUP(E277,機種マスタ!$K$4:$L$6,2,FALSE),0))*G277,0))</f>
         <v/>
       </c>
     </row>
@@ -11951,7 +11952,7 @@
         <v/>
       </c>
       <c r="H278" s="30">
-        <f>IF($B278="","",F278*G278)</f>
+        <f>IF($B278="","",IF(F278&gt;0,(F278+IFERROR(VLOOKUP(E278,機種マスタ!$K$4:$L$6,2,FALSE),0))*G278,0))</f>
         <v/>
       </c>
     </row>
@@ -11976,7 +11977,7 @@
         <v/>
       </c>
       <c r="H279" s="30">
-        <f>IF($B279="","",F279*G279)</f>
+        <f>IF($B279="","",IF(F279&gt;0,(F279+IFERROR(VLOOKUP(E279,機種マスタ!$K$4:$L$6,2,FALSE),0))*G279,0))</f>
         <v/>
       </c>
     </row>
@@ -12001,7 +12002,7 @@
         <v/>
       </c>
       <c r="H280" s="30">
-        <f>IF($B280="","",F280*G280)</f>
+        <f>IF($B280="","",IF(F280&gt;0,(F280+IFERROR(VLOOKUP(E280,機種マスタ!$K$4:$L$6,2,FALSE),0))*G280,0))</f>
         <v/>
       </c>
     </row>
@@ -12026,7 +12027,7 @@
         <v/>
       </c>
       <c r="H281" s="30">
-        <f>IF($B281="","",F281*G281)</f>
+        <f>IF($B281="","",IF(F281&gt;0,(F281+IFERROR(VLOOKUP(E281,機種マスタ!$K$4:$L$6,2,FALSE),0))*G281,0))</f>
         <v/>
       </c>
     </row>
@@ -12051,7 +12052,7 @@
         <v/>
       </c>
       <c r="H282" s="30">
-        <f>IF($B282="","",F282*G282)</f>
+        <f>IF($B282="","",IF(F282&gt;0,(F282+IFERROR(VLOOKUP(E282,機種マスタ!$K$4:$L$6,2,FALSE),0))*G282,0))</f>
         <v/>
       </c>
     </row>
@@ -12076,7 +12077,7 @@
         <v/>
       </c>
       <c r="H283" s="30">
-        <f>IF($B283="","",F283*G283)</f>
+        <f>IF($B283="","",IF(F283&gt;0,(F283+IFERROR(VLOOKUP(E283,機種マスタ!$K$4:$L$6,2,FALSE),0))*G283,0))</f>
         <v/>
       </c>
     </row>
@@ -12101,7 +12102,7 @@
         <v/>
       </c>
       <c r="H284" s="30">
-        <f>IF($B284="","",F284*G284)</f>
+        <f>IF($B284="","",IF(F284&gt;0,(F284+IFERROR(VLOOKUP(E284,機種マスタ!$K$4:$L$6,2,FALSE),0))*G284,0))</f>
         <v/>
       </c>
     </row>
@@ -12126,7 +12127,7 @@
         <v/>
       </c>
       <c r="H285" s="30">
-        <f>IF($B285="","",F285*G285)</f>
+        <f>IF($B285="","",IF(F285&gt;0,(F285+IFERROR(VLOOKUP(E285,機種マスタ!$K$4:$L$6,2,FALSE),0))*G285,0))</f>
         <v/>
       </c>
     </row>
@@ -12151,7 +12152,7 @@
         <v/>
       </c>
       <c r="H286" s="30">
-        <f>IF($B286="","",F286*G286)</f>
+        <f>IF($B286="","",IF(F286&gt;0,(F286+IFERROR(VLOOKUP(E286,機種マスタ!$K$4:$L$6,2,FALSE),0))*G286,0))</f>
         <v/>
       </c>
     </row>
@@ -12176,7 +12177,7 @@
         <v/>
       </c>
       <c r="H287" s="30">
-        <f>IF($B287="","",F287*G287)</f>
+        <f>IF($B287="","",IF(F287&gt;0,(F287+IFERROR(VLOOKUP(E287,機種マスタ!$K$4:$L$6,2,FALSE),0))*G287,0))</f>
         <v/>
       </c>
     </row>
@@ -12201,7 +12202,7 @@
         <v/>
       </c>
       <c r="H288" s="30">
-        <f>IF($B288="","",F288*G288)</f>
+        <f>IF($B288="","",IF(F288&gt;0,(F288+IFERROR(VLOOKUP(E288,機種マスタ!$K$4:$L$6,2,FALSE),0))*G288,0))</f>
         <v/>
       </c>
     </row>
@@ -12226,7 +12227,7 @@
         <v/>
       </c>
       <c r="H289" s="30">
-        <f>IF($B289="","",F289*G289)</f>
+        <f>IF($B289="","",IF(F289&gt;0,(F289+IFERROR(VLOOKUP(E289,機種マスタ!$K$4:$L$6,2,FALSE),0))*G289,0))</f>
         <v/>
       </c>
     </row>
@@ -12251,7 +12252,7 @@
         <v/>
       </c>
       <c r="H290" s="30">
-        <f>IF($B290="","",F290*G290)</f>
+        <f>IF($B290="","",IF(F290&gt;0,(F290+IFERROR(VLOOKUP(E290,機種マスタ!$K$4:$L$6,2,FALSE),0))*G290,0))</f>
         <v/>
       </c>
     </row>
@@ -12276,7 +12277,7 @@
         <v/>
       </c>
       <c r="H291" s="30">
-        <f>IF($B291="","",F291*G291)</f>
+        <f>IF($B291="","",IF(F291&gt;0,(F291+IFERROR(VLOOKUP(E291,機種マスタ!$K$4:$L$6,2,FALSE),0))*G291,0))</f>
         <v/>
       </c>
     </row>
@@ -12301,7 +12302,7 @@
         <v/>
       </c>
       <c r="H292" s="30">
-        <f>IF($B292="","",F292*G292)</f>
+        <f>IF($B292="","",IF(F292&gt;0,(F292+IFERROR(VLOOKUP(E292,機種マスタ!$K$4:$L$6,2,FALSE),0))*G292,0))</f>
         <v/>
       </c>
     </row>
@@ -12326,7 +12327,7 @@
         <v/>
       </c>
       <c r="H293" s="30">
-        <f>IF($B293="","",F293*G293)</f>
+        <f>IF($B293="","",IF(F293&gt;0,(F293+IFERROR(VLOOKUP(E293,機種マスタ!$K$4:$L$6,2,FALSE),0))*G293,0))</f>
         <v/>
       </c>
     </row>
@@ -12351,7 +12352,7 @@
         <v/>
       </c>
       <c r="H294" s="30">
-        <f>IF($B294="","",F294*G294)</f>
+        <f>IF($B294="","",IF(F294&gt;0,(F294+IFERROR(VLOOKUP(E294,機種マスタ!$K$4:$L$6,2,FALSE),0))*G294,0))</f>
         <v/>
       </c>
     </row>
@@ -12376,7 +12377,7 @@
         <v/>
       </c>
       <c r="H295" s="30">
-        <f>IF($B295="","",F295*G295)</f>
+        <f>IF($B295="","",IF(F295&gt;0,(F295+IFERROR(VLOOKUP(E295,機種マスタ!$K$4:$L$6,2,FALSE),0))*G295,0))</f>
         <v/>
       </c>
     </row>
@@ -12401,7 +12402,7 @@
         <v/>
       </c>
       <c r="H296" s="30">
-        <f>IF($B296="","",F296*G296)</f>
+        <f>IF($B296="","",IF(F296&gt;0,(F296+IFERROR(VLOOKUP(E296,機種マスタ!$K$4:$L$6,2,FALSE),0))*G296,0))</f>
         <v/>
       </c>
     </row>
@@ -12426,7 +12427,7 @@
         <v/>
       </c>
       <c r="H297" s="30">
-        <f>IF($B297="","",F297*G297)</f>
+        <f>IF($B297="","",IF(F297&gt;0,(F297+IFERROR(VLOOKUP(E297,機種マスタ!$K$4:$L$6,2,FALSE),0))*G297,0))</f>
         <v/>
       </c>
     </row>
@@ -12451,7 +12452,7 @@
         <v/>
       </c>
       <c r="H298" s="30">
-        <f>IF($B298="","",F298*G298)</f>
+        <f>IF($B298="","",IF(F298&gt;0,(F298+IFERROR(VLOOKUP(E298,機種マスタ!$K$4:$L$6,2,FALSE),0))*G298,0))</f>
         <v/>
       </c>
     </row>
@@ -12476,7 +12477,7 @@
         <v/>
       </c>
       <c r="H299" s="30">
-        <f>IF($B299="","",F299*G299)</f>
+        <f>IF($B299="","",IF(F299&gt;0,(F299+IFERROR(VLOOKUP(E299,機種マスタ!$K$4:$L$6,2,FALSE),0))*G299,0))</f>
         <v/>
       </c>
     </row>
@@ -12501,7 +12502,7 @@
         <v/>
       </c>
       <c r="H300" s="30">
-        <f>IF($B300="","",F300*G300)</f>
+        <f>IF($B300="","",IF(F300&gt;0,(F300+IFERROR(VLOOKUP(E300,機種マスタ!$K$4:$L$6,2,FALSE),0))*G300,0))</f>
         <v/>
       </c>
     </row>
@@ -12526,7 +12527,7 @@
         <v/>
       </c>
       <c r="H301" s="30">
-        <f>IF($B301="","",F301*G301)</f>
+        <f>IF($B301="","",IF(F301&gt;0,(F301+IFERROR(VLOOKUP(E301,機種マスタ!$K$4:$L$6,2,FALSE),0))*G301,0))</f>
         <v/>
       </c>
     </row>
@@ -12551,7 +12552,7 @@
         <v/>
       </c>
       <c r="H302" s="30">
-        <f>IF($B302="","",F302*G302)</f>
+        <f>IF($B302="","",IF(F302&gt;0,(F302+IFERROR(VLOOKUP(E302,機種マスタ!$K$4:$L$6,2,FALSE),0))*G302,0))</f>
         <v/>
       </c>
     </row>
@@ -12576,7 +12577,7 @@
         <v/>
       </c>
       <c r="H303" s="30">
-        <f>IF($B303="","",F303*G303)</f>
+        <f>IF($B303="","",IF(F303&gt;0,(F303+IFERROR(VLOOKUP(E303,機種マスタ!$K$4:$L$6,2,FALSE),0))*G303,0))</f>
         <v/>
       </c>
     </row>
@@ -12601,7 +12602,7 @@
         <v/>
       </c>
       <c r="H304" s="30">
-        <f>IF($B304="","",F304*G304)</f>
+        <f>IF($B304="","",IF(F304&gt;0,(F304+IFERROR(VLOOKUP(E304,機種マスタ!$K$4:$L$6,2,FALSE),0))*G304,0))</f>
         <v/>
       </c>
     </row>
@@ -12626,7 +12627,7 @@
         <v/>
       </c>
       <c r="H305" s="30">
-        <f>IF($B305="","",F305*G305)</f>
+        <f>IF($B305="","",IF(F305&gt;0,(F305+IFERROR(VLOOKUP(E305,機種マスタ!$K$4:$L$6,2,FALSE),0))*G305,0))</f>
         <v/>
       </c>
     </row>
@@ -12651,7 +12652,7 @@
         <v/>
       </c>
       <c r="H306" s="30">
-        <f>IF($B306="","",F306*G306)</f>
+        <f>IF($B306="","",IF(F306&gt;0,(F306+IFERROR(VLOOKUP(E306,機種マスタ!$K$4:$L$6,2,FALSE),0))*G306,0))</f>
         <v/>
       </c>
     </row>
@@ -12676,7 +12677,7 @@
         <v/>
       </c>
       <c r="H307" s="30">
-        <f>IF($B307="","",F307*G307)</f>
+        <f>IF($B307="","",IF(F307&gt;0,(F307+IFERROR(VLOOKUP(E307,機種マスタ!$K$4:$L$6,2,FALSE),0))*G307,0))</f>
         <v/>
       </c>
     </row>
@@ -12701,7 +12702,7 @@
         <v/>
       </c>
       <c r="H308" s="30">
-        <f>IF($B308="","",F308*G308)</f>
+        <f>IF($B308="","",IF(F308&gt;0,(F308+IFERROR(VLOOKUP(E308,機種マスタ!$K$4:$L$6,2,FALSE),0))*G308,0))</f>
         <v/>
       </c>
     </row>
@@ -12726,7 +12727,7 @@
         <v/>
       </c>
       <c r="H309" s="30">
-        <f>IF($B309="","",F309*G309)</f>
+        <f>IF($B309="","",IF(F309&gt;0,(F309+IFERROR(VLOOKUP(E309,機種マスタ!$K$4:$L$6,2,FALSE),0))*G309,0))</f>
         <v/>
       </c>
     </row>
@@ -12751,7 +12752,7 @@
         <v/>
       </c>
       <c r="H310" s="30">
-        <f>IF($B310="","",F310*G310)</f>
+        <f>IF($B310="","",IF(F310&gt;0,(F310+IFERROR(VLOOKUP(E310,機種マスタ!$K$4:$L$6,2,FALSE),0))*G310,0))</f>
         <v/>
       </c>
     </row>
@@ -12776,7 +12777,7 @@
         <v/>
       </c>
       <c r="H311" s="30">
-        <f>IF($B311="","",F311*G311)</f>
+        <f>IF($B311="","",IF(F311&gt;0,(F311+IFERROR(VLOOKUP(E311,機種マスタ!$K$4:$L$6,2,FALSE),0))*G311,0))</f>
         <v/>
       </c>
     </row>
@@ -12801,7 +12802,7 @@
         <v/>
       </c>
       <c r="H312" s="30">
-        <f>IF($B312="","",F312*G312)</f>
+        <f>IF($B312="","",IF(F312&gt;0,(F312+IFERROR(VLOOKUP(E312,機種マスタ!$K$4:$L$6,2,FALSE),0))*G312,0))</f>
         <v/>
       </c>
     </row>
@@ -12826,7 +12827,7 @@
         <v/>
       </c>
       <c r="H313" s="30">
-        <f>IF($B313="","",F313*G313)</f>
+        <f>IF($B313="","",IF(F313&gt;0,(F313+IFERROR(VLOOKUP(E313,機種マスタ!$K$4:$L$6,2,FALSE),0))*G313,0))</f>
         <v/>
       </c>
     </row>
@@ -12851,7 +12852,7 @@
         <v/>
       </c>
       <c r="H314" s="30">
-        <f>IF($B314="","",F314*G314)</f>
+        <f>IF($B314="","",IF(F314&gt;0,(F314+IFERROR(VLOOKUP(E314,機種マスタ!$K$4:$L$6,2,FALSE),0))*G314,0))</f>
         <v/>
       </c>
     </row>
@@ -12876,7 +12877,7 @@
         <v/>
       </c>
       <c r="H315" s="30">
-        <f>IF($B315="","",F315*G315)</f>
+        <f>IF($B315="","",IF(F315&gt;0,(F315+IFERROR(VLOOKUP(E315,機種マスタ!$K$4:$L$6,2,FALSE),0))*G315,0))</f>
         <v/>
       </c>
     </row>
@@ -12901,7 +12902,7 @@
         <v/>
       </c>
       <c r="H316" s="30">
-        <f>IF($B316="","",F316*G316)</f>
+        <f>IF($B316="","",IF(F316&gt;0,(F316+IFERROR(VLOOKUP(E316,機種マスタ!$K$4:$L$6,2,FALSE),0))*G316,0))</f>
         <v/>
       </c>
     </row>
@@ -12926,7 +12927,7 @@
         <v/>
       </c>
       <c r="H317" s="30">
-        <f>IF($B317="","",F317*G317)</f>
+        <f>IF($B317="","",IF(F317&gt;0,(F317+IFERROR(VLOOKUP(E317,機種マスタ!$K$4:$L$6,2,FALSE),0))*G317,0))</f>
         <v/>
       </c>
     </row>
@@ -12951,7 +12952,7 @@
         <v/>
       </c>
       <c r="H318" s="30">
-        <f>IF($B318="","",F318*G318)</f>
+        <f>IF($B318="","",IF(F318&gt;0,(F318+IFERROR(VLOOKUP(E318,機種マスタ!$K$4:$L$6,2,FALSE),0))*G318,0))</f>
         <v/>
       </c>
     </row>
@@ -12976,7 +12977,7 @@
         <v/>
       </c>
       <c r="H319" s="30">
-        <f>IF($B319="","",F319*G319)</f>
+        <f>IF($B319="","",IF(F319&gt;0,(F319+IFERROR(VLOOKUP(E319,機種マスタ!$K$4:$L$6,2,FALSE),0))*G319,0))</f>
         <v/>
       </c>
     </row>
@@ -13001,7 +13002,7 @@
         <v/>
       </c>
       <c r="H320" s="30">
-        <f>IF($B320="","",F320*G320)</f>
+        <f>IF($B320="","",IF(F320&gt;0,(F320+IFERROR(VLOOKUP(E320,機種マスタ!$K$4:$L$6,2,FALSE),0))*G320,0))</f>
         <v/>
       </c>
     </row>
@@ -13026,7 +13027,7 @@
         <v/>
       </c>
       <c r="H321" s="30">
-        <f>IF($B321="","",F321*G321)</f>
+        <f>IF($B321="","",IF(F321&gt;0,(F321+IFERROR(VLOOKUP(E321,機種マスタ!$K$4:$L$6,2,FALSE),0))*G321,0))</f>
         <v/>
       </c>
     </row>
@@ -13051,7 +13052,7 @@
         <v/>
       </c>
       <c r="H322" s="30">
-        <f>IF($B322="","",F322*G322)</f>
+        <f>IF($B322="","",IF(F322&gt;0,(F322+IFERROR(VLOOKUP(E322,機種マスタ!$K$4:$L$6,2,FALSE),0))*G322,0))</f>
         <v/>
       </c>
     </row>
@@ -13076,7 +13077,7 @@
         <v/>
       </c>
       <c r="H323" s="30">
-        <f>IF($B323="","",F323*G323)</f>
+        <f>IF($B323="","",IF(F323&gt;0,(F323+IFERROR(VLOOKUP(E323,機種マスタ!$K$4:$L$6,2,FALSE),0))*G323,0))</f>
         <v/>
       </c>
     </row>
@@ -13101,7 +13102,7 @@
         <v/>
       </c>
       <c r="H324" s="30">
-        <f>IF($B324="","",F324*G324)</f>
+        <f>IF($B324="","",IF(F324&gt;0,(F324+IFERROR(VLOOKUP(E324,機種マスタ!$K$4:$L$6,2,FALSE),0))*G324,0))</f>
         <v/>
       </c>
     </row>
@@ -13126,7 +13127,7 @@
         <v/>
       </c>
       <c r="H325" s="30">
-        <f>IF($B325="","",F325*G325)</f>
+        <f>IF($B325="","",IF(F325&gt;0,(F325+IFERROR(VLOOKUP(E325,機種マスタ!$K$4:$L$6,2,FALSE),0))*G325,0))</f>
         <v/>
       </c>
     </row>
@@ -13151,7 +13152,7 @@
         <v/>
       </c>
       <c r="H326" s="30">
-        <f>IF($B326="","",F326*G326)</f>
+        <f>IF($B326="","",IF(F326&gt;0,(F326+IFERROR(VLOOKUP(E326,機種マスタ!$K$4:$L$6,2,FALSE),0))*G326,0))</f>
         <v/>
       </c>
     </row>
@@ -13176,7 +13177,7 @@
         <v/>
       </c>
       <c r="H327" s="30">
-        <f>IF($B327="","",F327*G327)</f>
+        <f>IF($B327="","",IF(F327&gt;0,(F327+IFERROR(VLOOKUP(E327,機種マスタ!$K$4:$L$6,2,FALSE),0))*G327,0))</f>
         <v/>
       </c>
     </row>
@@ -13201,7 +13202,7 @@
         <v/>
       </c>
       <c r="H328" s="30">
-        <f>IF($B328="","",F328*G328)</f>
+        <f>IF($B328="","",IF(F328&gt;0,(F328+IFERROR(VLOOKUP(E328,機種マスタ!$K$4:$L$6,2,FALSE),0))*G328,0))</f>
         <v/>
       </c>
     </row>
@@ -13226,7 +13227,7 @@
         <v/>
       </c>
       <c r="H329" s="30">
-        <f>IF($B329="","",F329*G329)</f>
+        <f>IF($B329="","",IF(F329&gt;0,(F329+IFERROR(VLOOKUP(E329,機種マスタ!$K$4:$L$6,2,FALSE),0))*G329,0))</f>
         <v/>
       </c>
     </row>
@@ -13251,7 +13252,7 @@
         <v/>
       </c>
       <c r="H330" s="30">
-        <f>IF($B330="","",F330*G330)</f>
+        <f>IF($B330="","",IF(F330&gt;0,(F330+IFERROR(VLOOKUP(E330,機種マスタ!$K$4:$L$6,2,FALSE),0))*G330,0))</f>
         <v/>
       </c>
     </row>
@@ -13276,7 +13277,7 @@
         <v/>
       </c>
       <c r="H331" s="30">
-        <f>IF($B331="","",F331*G331)</f>
+        <f>IF($B331="","",IF(F331&gt;0,(F331+IFERROR(VLOOKUP(E331,機種マスタ!$K$4:$L$6,2,FALSE),0))*G331,0))</f>
         <v/>
       </c>
     </row>
@@ -13301,7 +13302,7 @@
         <v/>
       </c>
       <c r="H332" s="30">
-        <f>IF($B332="","",F332*G332)</f>
+        <f>IF($B332="","",IF(F332&gt;0,(F332+IFERROR(VLOOKUP(E332,機種マスタ!$K$4:$L$6,2,FALSE),0))*G332,0))</f>
         <v/>
       </c>
     </row>
@@ -13326,7 +13327,7 @@
         <v/>
       </c>
       <c r="H333" s="30">
-        <f>IF($B333="","",F333*G333)</f>
+        <f>IF($B333="","",IF(F333&gt;0,(F333+IFERROR(VLOOKUP(E333,機種マスタ!$K$4:$L$6,2,FALSE),0))*G333,0))</f>
         <v/>
       </c>
     </row>
@@ -13351,7 +13352,7 @@
         <v/>
       </c>
       <c r="H334" s="30">
-        <f>IF($B334="","",F334*G334)</f>
+        <f>IF($B334="","",IF(F334&gt;0,(F334+IFERROR(VLOOKUP(E334,機種マスタ!$K$4:$L$6,2,FALSE),0))*G334,0))</f>
         <v/>
       </c>
     </row>
@@ -13376,7 +13377,7 @@
         <v/>
       </c>
       <c r="H335" s="30">
-        <f>IF($B335="","",F335*G335)</f>
+        <f>IF($B335="","",IF(F335&gt;0,(F335+IFERROR(VLOOKUP(E335,機種マスタ!$K$4:$L$6,2,FALSE),0))*G335,0))</f>
         <v/>
       </c>
     </row>
@@ -13401,7 +13402,7 @@
         <v/>
       </c>
       <c r="H336" s="30">
-        <f>IF($B336="","",F336*G336)</f>
+        <f>IF($B336="","",IF(F336&gt;0,(F336+IFERROR(VLOOKUP(E336,機種マスタ!$K$4:$L$6,2,FALSE),0))*G336,0))</f>
         <v/>
       </c>
     </row>
@@ -13426,7 +13427,7 @@
         <v/>
       </c>
       <c r="H337" s="30">
-        <f>IF($B337="","",F337*G337)</f>
+        <f>IF($B337="","",IF(F337&gt;0,(F337+IFERROR(VLOOKUP(E337,機種マスタ!$K$4:$L$6,2,FALSE),0))*G337,0))</f>
         <v/>
       </c>
     </row>
@@ -13451,7 +13452,7 @@
         <v/>
       </c>
       <c r="H338" s="30">
-        <f>IF($B338="","",F338*G338)</f>
+        <f>IF($B338="","",IF(F338&gt;0,(F338+IFERROR(VLOOKUP(E338,機種マスタ!$K$4:$L$6,2,FALSE),0))*G338,0))</f>
         <v/>
       </c>
     </row>
@@ -13476,7 +13477,7 @@
         <v/>
       </c>
       <c r="H339" s="30">
-        <f>IF($B339="","",F339*G339)</f>
+        <f>IF($B339="","",IF(F339&gt;0,(F339+IFERROR(VLOOKUP(E339,機種マスタ!$K$4:$L$6,2,FALSE),0))*G339,0))</f>
         <v/>
       </c>
     </row>
@@ -13501,7 +13502,7 @@
         <v/>
       </c>
       <c r="H340" s="30">
-        <f>IF($B340="","",F340*G340)</f>
+        <f>IF($B340="","",IF(F340&gt;0,(F340+IFERROR(VLOOKUP(E340,機種マスタ!$K$4:$L$6,2,FALSE),0))*G340,0))</f>
         <v/>
       </c>
     </row>
@@ -13526,7 +13527,7 @@
         <v/>
       </c>
       <c r="H341" s="30">
-        <f>IF($B341="","",F341*G341)</f>
+        <f>IF($B341="","",IF(F341&gt;0,(F341+IFERROR(VLOOKUP(E341,機種マスタ!$K$4:$L$6,2,FALSE),0))*G341,0))</f>
         <v/>
       </c>
     </row>
@@ -13551,7 +13552,7 @@
         <v/>
       </c>
       <c r="H342" s="30">
-        <f>IF($B342="","",F342*G342)</f>
+        <f>IF($B342="","",IF(F342&gt;0,(F342+IFERROR(VLOOKUP(E342,機種マスタ!$K$4:$L$6,2,FALSE),0))*G342,0))</f>
         <v/>
       </c>
     </row>
@@ -13576,7 +13577,7 @@
         <v/>
       </c>
       <c r="H343" s="30">
-        <f>IF($B343="","",F343*G343)</f>
+        <f>IF($B343="","",IF(F343&gt;0,(F343+IFERROR(VLOOKUP(E343,機種マスタ!$K$4:$L$6,2,FALSE),0))*G343,0))</f>
         <v/>
       </c>
     </row>
@@ -13601,7 +13602,7 @@
         <v/>
       </c>
       <c r="H344" s="30">
-        <f>IF($B344="","",F344*G344)</f>
+        <f>IF($B344="","",IF(F344&gt;0,(F344+IFERROR(VLOOKUP(E344,機種マスタ!$K$4:$L$6,2,FALSE),0))*G344,0))</f>
         <v/>
       </c>
     </row>
@@ -13626,7 +13627,7 @@
         <v/>
       </c>
       <c r="H345" s="30">
-        <f>IF($B345="","",F345*G345)</f>
+        <f>IF($B345="","",IF(F345&gt;0,(F345+IFERROR(VLOOKUP(E345,機種マスタ!$K$4:$L$6,2,FALSE),0))*G345,0))</f>
         <v/>
       </c>
     </row>
@@ -13651,7 +13652,7 @@
         <v/>
       </c>
       <c r="H346" s="30">
-        <f>IF($B346="","",F346*G346)</f>
+        <f>IF($B346="","",IF(F346&gt;0,(F346+IFERROR(VLOOKUP(E346,機種マスタ!$K$4:$L$6,2,FALSE),0))*G346,0))</f>
         <v/>
       </c>
     </row>
@@ -13676,7 +13677,7 @@
         <v/>
       </c>
       <c r="H347" s="30">
-        <f>IF($B347="","",F347*G347)</f>
+        <f>IF($B347="","",IF(F347&gt;0,(F347+IFERROR(VLOOKUP(E347,機種マスタ!$K$4:$L$6,2,FALSE),0))*G347,0))</f>
         <v/>
       </c>
     </row>
@@ -13701,7 +13702,7 @@
         <v/>
       </c>
       <c r="H348" s="30">
-        <f>IF($B348="","",F348*G348)</f>
+        <f>IF($B348="","",IF(F348&gt;0,(F348+IFERROR(VLOOKUP(E348,機種マスタ!$K$4:$L$6,2,FALSE),0))*G348,0))</f>
         <v/>
       </c>
     </row>
@@ -13726,7 +13727,7 @@
         <v/>
       </c>
       <c r="H349" s="30">
-        <f>IF($B349="","",F349*G349)</f>
+        <f>IF($B349="","",IF(F349&gt;0,(F349+IFERROR(VLOOKUP(E349,機種マスタ!$K$4:$L$6,2,FALSE),0))*G349,0))</f>
         <v/>
       </c>
     </row>
@@ -13751,7 +13752,7 @@
         <v/>
       </c>
       <c r="H350" s="30">
-        <f>IF($B350="","",F350*G350)</f>
+        <f>IF($B350="","",IF(F350&gt;0,(F350+IFERROR(VLOOKUP(E350,機種マスタ!$K$4:$L$6,2,FALSE),0))*G350,0))</f>
         <v/>
       </c>
     </row>
@@ -13776,7 +13777,7 @@
         <v/>
       </c>
       <c r="H351" s="30">
-        <f>IF($B351="","",F351*G351)</f>
+        <f>IF($B351="","",IF(F351&gt;0,(F351+IFERROR(VLOOKUP(E351,機種マスタ!$K$4:$L$6,2,FALSE),0))*G351,0))</f>
         <v/>
       </c>
     </row>
@@ -13801,7 +13802,7 @@
         <v/>
       </c>
       <c r="H352" s="30">
-        <f>IF($B352="","",F352*G352)</f>
+        <f>IF($B352="","",IF(F352&gt;0,(F352+IFERROR(VLOOKUP(E352,機種マスタ!$K$4:$L$6,2,FALSE),0))*G352,0))</f>
         <v/>
       </c>
     </row>
@@ -13826,7 +13827,7 @@
         <v/>
       </c>
       <c r="H353" s="30">
-        <f>IF($B353="","",F353*G353)</f>
+        <f>IF($B353="","",IF(F353&gt;0,(F353+IFERROR(VLOOKUP(E353,機種マスタ!$K$4:$L$6,2,FALSE),0))*G353,0))</f>
         <v/>
       </c>
     </row>
@@ -13851,7 +13852,7 @@
         <v/>
       </c>
       <c r="H354" s="30">
-        <f>IF($B354="","",F354*G354)</f>
+        <f>IF($B354="","",IF(F354&gt;0,(F354+IFERROR(VLOOKUP(E354,機種マスタ!$K$4:$L$6,2,FALSE),0))*G354,0))</f>
         <v/>
       </c>
     </row>
@@ -13876,7 +13877,7 @@
         <v/>
       </c>
       <c r="H355" s="30">
-        <f>IF($B355="","",F355*G355)</f>
+        <f>IF($B355="","",IF(F355&gt;0,(F355+IFERROR(VLOOKUP(E355,機種マスタ!$K$4:$L$6,2,FALSE),0))*G355,0))</f>
         <v/>
       </c>
     </row>
@@ -13901,7 +13902,7 @@
         <v/>
       </c>
       <c r="H356" s="30">
-        <f>IF($B356="","",F356*G356)</f>
+        <f>IF($B356="","",IF(F356&gt;0,(F356+IFERROR(VLOOKUP(E356,機種マスタ!$K$4:$L$6,2,FALSE),0))*G356,0))</f>
         <v/>
       </c>
     </row>
@@ -13926,7 +13927,7 @@
         <v/>
       </c>
       <c r="H357" s="30">
-        <f>IF($B357="","",F357*G357)</f>
+        <f>IF($B357="","",IF(F357&gt;0,(F357+IFERROR(VLOOKUP(E357,機種マスタ!$K$4:$L$6,2,FALSE),0))*G357,0))</f>
         <v/>
       </c>
     </row>
@@ -13951,7 +13952,7 @@
         <v/>
       </c>
       <c r="H358" s="30">
-        <f>IF($B358="","",F358*G358)</f>
+        <f>IF($B358="","",IF(F358&gt;0,(F358+IFERROR(VLOOKUP(E358,機種マスタ!$K$4:$L$6,2,FALSE),0))*G358,0))</f>
         <v/>
       </c>
     </row>
@@ -13976,7 +13977,7 @@
         <v/>
       </c>
       <c r="H359" s="30">
-        <f>IF($B359="","",F359*G359)</f>
+        <f>IF($B359="","",IF(F359&gt;0,(F359+IFERROR(VLOOKUP(E359,機種マスタ!$K$4:$L$6,2,FALSE),0))*G359,0))</f>
         <v/>
       </c>
     </row>
@@ -14001,7 +14002,7 @@
         <v/>
       </c>
       <c r="H360" s="30">
-        <f>IF($B360="","",F360*G360)</f>
+        <f>IF($B360="","",IF(F360&gt;0,(F360+IFERROR(VLOOKUP(E360,機種マスタ!$K$4:$L$6,2,FALSE),0))*G360,0))</f>
         <v/>
       </c>
     </row>
@@ -14026,7 +14027,7 @@
         <v/>
       </c>
       <c r="H361" s="30">
-        <f>IF($B361="","",F361*G361)</f>
+        <f>IF($B361="","",IF(F361&gt;0,(F361+IFERROR(VLOOKUP(E361,機種マスタ!$K$4:$L$6,2,FALSE),0))*G361,0))</f>
         <v/>
       </c>
     </row>
@@ -14051,7 +14052,7 @@
         <v/>
       </c>
       <c r="H362" s="30">
-        <f>IF($B362="","",F362*G362)</f>
+        <f>IF($B362="","",IF(F362&gt;0,(F362+IFERROR(VLOOKUP(E362,機種マスタ!$K$4:$L$6,2,FALSE),0))*G362,0))</f>
         <v/>
       </c>
     </row>
@@ -14076,7 +14077,7 @@
         <v/>
       </c>
       <c r="H363" s="30">
-        <f>IF($B363="","",F363*G363)</f>
+        <f>IF($B363="","",IF(F363&gt;0,(F363+IFERROR(VLOOKUP(E363,機種マスタ!$K$4:$L$6,2,FALSE),0))*G363,0))</f>
         <v/>
       </c>
     </row>
@@ -14101,7 +14102,7 @@
         <v/>
       </c>
       <c r="H364" s="30">
-        <f>IF($B364="","",F364*G364)</f>
+        <f>IF($B364="","",IF(F364&gt;0,(F364+IFERROR(VLOOKUP(E364,機種マスタ!$K$4:$L$6,2,FALSE),0))*G364,0))</f>
         <v/>
       </c>
     </row>
@@ -14126,7 +14127,7 @@
         <v/>
       </c>
       <c r="H365" s="30">
-        <f>IF($B365="","",F365*G365)</f>
+        <f>IF($B365="","",IF(F365&gt;0,(F365+IFERROR(VLOOKUP(E365,機種マスタ!$K$4:$L$6,2,FALSE),0))*G365,0))</f>
         <v/>
       </c>
     </row>
@@ -14151,7 +14152,7 @@
         <v/>
       </c>
       <c r="H366" s="30">
-        <f>IF($B366="","",F366*G366)</f>
+        <f>IF($B366="","",IF(F366&gt;0,(F366+IFERROR(VLOOKUP(E366,機種マスタ!$K$4:$L$6,2,FALSE),0))*G366,0))</f>
         <v/>
       </c>
     </row>
@@ -14176,7 +14177,7 @@
         <v/>
       </c>
       <c r="H367" s="30">
-        <f>IF($B367="","",F367*G367)</f>
+        <f>IF($B367="","",IF(F367&gt;0,(F367+IFERROR(VLOOKUP(E367,機種マスタ!$K$4:$L$6,2,FALSE),0))*G367,0))</f>
         <v/>
       </c>
     </row>
@@ -14201,7 +14202,7 @@
         <v/>
       </c>
       <c r="H368" s="30">
-        <f>IF($B368="","",F368*G368)</f>
+        <f>IF($B368="","",IF(F368&gt;0,(F368+IFERROR(VLOOKUP(E368,機種マスタ!$K$4:$L$6,2,FALSE),0))*G368,0))</f>
         <v/>
       </c>
     </row>
@@ -14226,7 +14227,7 @@
         <v/>
       </c>
       <c r="H369" s="30">
-        <f>IF($B369="","",F369*G369)</f>
+        <f>IF($B369="","",IF(F369&gt;0,(F369+IFERROR(VLOOKUP(E369,機種マスタ!$K$4:$L$6,2,FALSE),0))*G369,0))</f>
         <v/>
       </c>
     </row>
@@ -14251,7 +14252,7 @@
         <v/>
       </c>
       <c r="H370" s="30">
-        <f>IF($B370="","",F370*G370)</f>
+        <f>IF($B370="","",IF(F370&gt;0,(F370+IFERROR(VLOOKUP(E370,機種マスタ!$K$4:$L$6,2,FALSE),0))*G370,0))</f>
         <v/>
       </c>
     </row>
@@ -14276,7 +14277,7 @@
         <v/>
       </c>
       <c r="H371" s="30">
-        <f>IF($B371="","",F371*G371)</f>
+        <f>IF($B371="","",IF(F371&gt;0,(F371+IFERROR(VLOOKUP(E371,機種マスタ!$K$4:$L$6,2,FALSE),0))*G371,0))</f>
         <v/>
       </c>
     </row>
@@ -14301,7 +14302,7 @@
         <v/>
       </c>
       <c r="H372" s="30">
-        <f>IF($B372="","",F372*G372)</f>
+        <f>IF($B372="","",IF(F372&gt;0,(F372+IFERROR(VLOOKUP(E372,機種マスタ!$K$4:$L$6,2,FALSE),0))*G372,0))</f>
         <v/>
       </c>
     </row>
@@ -14326,7 +14327,7 @@
         <v/>
       </c>
       <c r="H373" s="30">
-        <f>IF($B373="","",F373*G373)</f>
+        <f>IF($B373="","",IF(F373&gt;0,(F373+IFERROR(VLOOKUP(E373,機種マスタ!$K$4:$L$6,2,FALSE),0))*G373,0))</f>
         <v/>
       </c>
     </row>
@@ -14351,7 +14352,7 @@
         <v/>
       </c>
       <c r="H374" s="30">
-        <f>IF($B374="","",F374*G374)</f>
+        <f>IF($B374="","",IF(F374&gt;0,(F374+IFERROR(VLOOKUP(E374,機種マスタ!$K$4:$L$6,2,FALSE),0))*G374,0))</f>
         <v/>
       </c>
     </row>
@@ -14376,7 +14377,7 @@
         <v/>
       </c>
       <c r="H375" s="30">
-        <f>IF($B375="","",F375*G375)</f>
+        <f>IF($B375="","",IF(F375&gt;0,(F375+IFERROR(VLOOKUP(E375,機種マスタ!$K$4:$L$6,2,FALSE),0))*G375,0))</f>
         <v/>
       </c>
     </row>
@@ -14401,7 +14402,7 @@
         <v/>
       </c>
       <c r="H376" s="30">
-        <f>IF($B376="","",F376*G376)</f>
+        <f>IF($B376="","",IF(F376&gt;0,(F376+IFERROR(VLOOKUP(E376,機種マスタ!$K$4:$L$6,2,FALSE),0))*G376,0))</f>
         <v/>
       </c>
     </row>
@@ -14426,7 +14427,7 @@
         <v/>
       </c>
       <c r="H377" s="30">
-        <f>IF($B377="","",F377*G377)</f>
+        <f>IF($B377="","",IF(F377&gt;0,(F377+IFERROR(VLOOKUP(E377,機種マスタ!$K$4:$L$6,2,FALSE),0))*G377,0))</f>
         <v/>
       </c>
     </row>
@@ -14451,7 +14452,7 @@
         <v/>
       </c>
       <c r="H378" s="30">
-        <f>IF($B378="","",F378*G378)</f>
+        <f>IF($B378="","",IF(F378&gt;0,(F378+IFERROR(VLOOKUP(E378,機種マスタ!$K$4:$L$6,2,FALSE),0))*G378,0))</f>
         <v/>
       </c>
     </row>
@@ -14476,7 +14477,7 @@
         <v/>
       </c>
       <c r="H379" s="30">
-        <f>IF($B379="","",F379*G379)</f>
+        <f>IF($B379="","",IF(F379&gt;0,(F379+IFERROR(VLOOKUP(E379,機種マスタ!$K$4:$L$6,2,FALSE),0))*G379,0))</f>
         <v/>
       </c>
     </row>
@@ -14501,7 +14502,7 @@
         <v/>
       </c>
       <c r="H380" s="30">
-        <f>IF($B380="","",F380*G380)</f>
+        <f>IF($B380="","",IF(F380&gt;0,(F380+IFERROR(VLOOKUP(E380,機種マスタ!$K$4:$L$6,2,FALSE),0))*G380,0))</f>
         <v/>
       </c>
     </row>
@@ -14526,7 +14527,7 @@
         <v/>
       </c>
       <c r="H381" s="30">
-        <f>IF($B381="","",F381*G381)</f>
+        <f>IF($B381="","",IF(F381&gt;0,(F381+IFERROR(VLOOKUP(E381,機種マスタ!$K$4:$L$6,2,FALSE),0))*G381,0))</f>
         <v/>
       </c>
     </row>
@@ -14551,7 +14552,7 @@
         <v/>
       </c>
       <c r="H382" s="30">
-        <f>IF($B382="","",F382*G382)</f>
+        <f>IF($B382="","",IF(F382&gt;0,(F382+IFERROR(VLOOKUP(E382,機種マスタ!$K$4:$L$6,2,FALSE),0))*G382,0))</f>
         <v/>
       </c>
     </row>
@@ -14576,7 +14577,7 @@
         <v/>
       </c>
       <c r="H383" s="30">
-        <f>IF($B383="","",F383*G383)</f>
+        <f>IF($B383="","",IF(F383&gt;0,(F383+IFERROR(VLOOKUP(E383,機種マスタ!$K$4:$L$6,2,FALSE),0))*G383,0))</f>
         <v/>
       </c>
     </row>
@@ -14601,7 +14602,7 @@
         <v/>
       </c>
       <c r="H384" s="30">
-        <f>IF($B384="","",F384*G384)</f>
+        <f>IF($B384="","",IF(F384&gt;0,(F384+IFERROR(VLOOKUP(E384,機種マスタ!$K$4:$L$6,2,FALSE),0))*G384,0))</f>
         <v/>
       </c>
     </row>
@@ -14626,7 +14627,7 @@
         <v/>
       </c>
       <c r="H385" s="30">
-        <f>IF($B385="","",F385*G385)</f>
+        <f>IF($B385="","",IF(F385&gt;0,(F385+IFERROR(VLOOKUP(E385,機種マスタ!$K$4:$L$6,2,FALSE),0))*G385,0))</f>
         <v/>
       </c>
     </row>
@@ -14651,7 +14652,7 @@
         <v/>
       </c>
       <c r="H386" s="30">
-        <f>IF($B386="","",F386*G386)</f>
+        <f>IF($B386="","",IF(F386&gt;0,(F386+IFERROR(VLOOKUP(E386,機種マスタ!$K$4:$L$6,2,FALSE),0))*G386,0))</f>
         <v/>
       </c>
     </row>
@@ -14676,7 +14677,7 @@
         <v/>
       </c>
       <c r="H387" s="30">
-        <f>IF($B387="","",F387*G387)</f>
+        <f>IF($B387="","",IF(F387&gt;0,(F387+IFERROR(VLOOKUP(E387,機種マスタ!$K$4:$L$6,2,FALSE),0))*G387,0))</f>
         <v/>
       </c>
     </row>
@@ -14701,7 +14702,7 @@
         <v/>
       </c>
       <c r="H388" s="30">
-        <f>IF($B388="","",F388*G388)</f>
+        <f>IF($B388="","",IF(F388&gt;0,(F388+IFERROR(VLOOKUP(E388,機種マスタ!$K$4:$L$6,2,FALSE),0))*G388,0))</f>
         <v/>
       </c>
     </row>
@@ -14726,7 +14727,7 @@
         <v/>
       </c>
       <c r="H389" s="30">
-        <f>IF($B389="","",F389*G389)</f>
+        <f>IF($B389="","",IF(F389&gt;0,(F389+IFERROR(VLOOKUP(E389,機種マスタ!$K$4:$L$6,2,FALSE),0))*G389,0))</f>
         <v/>
       </c>
     </row>
@@ -14751,7 +14752,7 @@
         <v/>
       </c>
       <c r="H390" s="30">
-        <f>IF($B390="","",F390*G390)</f>
+        <f>IF($B390="","",IF(F390&gt;0,(F390+IFERROR(VLOOKUP(E390,機種マスタ!$K$4:$L$6,2,FALSE),0))*G390,0))</f>
         <v/>
       </c>
     </row>
@@ -14776,7 +14777,7 @@
         <v/>
       </c>
       <c r="H391" s="30">
-        <f>IF($B391="","",F391*G391)</f>
+        <f>IF($B391="","",IF(F391&gt;0,(F391+IFERROR(VLOOKUP(E391,機種マスタ!$K$4:$L$6,2,FALSE),0))*G391,0))</f>
         <v/>
       </c>
     </row>
@@ -14801,7 +14802,7 @@
         <v/>
       </c>
       <c r="H392" s="30">
-        <f>IF($B392="","",F392*G392)</f>
+        <f>IF($B392="","",IF(F392&gt;0,(F392+IFERROR(VLOOKUP(E392,機種マスタ!$K$4:$L$6,2,FALSE),0))*G392,0))</f>
         <v/>
       </c>
     </row>
@@ -14826,7 +14827,7 @@
         <v/>
       </c>
       <c r="H393" s="30">
-        <f>IF($B393="","",F393*G393)</f>
+        <f>IF($B393="","",IF(F393&gt;0,(F393+IFERROR(VLOOKUP(E393,機種マスタ!$K$4:$L$6,2,FALSE),0))*G393,0))</f>
         <v/>
       </c>
     </row>
@@ -14851,7 +14852,7 @@
         <v/>
       </c>
       <c r="H394" s="30">
-        <f>IF($B394="","",F394*G394)</f>
+        <f>IF($B394="","",IF(F394&gt;0,(F394+IFERROR(VLOOKUP(E394,機種マスタ!$K$4:$L$6,2,FALSE),0))*G394,0))</f>
         <v/>
       </c>
     </row>
@@ -14876,7 +14877,7 @@
         <v/>
       </c>
       <c r="H395" s="30">
-        <f>IF($B395="","",F395*G395)</f>
+        <f>IF($B395="","",IF(F395&gt;0,(F395+IFERROR(VLOOKUP(E395,機種マスタ!$K$4:$L$6,2,FALSE),0))*G395,0))</f>
         <v/>
       </c>
     </row>
@@ -14901,7 +14902,7 @@
         <v/>
       </c>
       <c r="H396" s="30">
-        <f>IF($B396="","",F396*G396)</f>
+        <f>IF($B396="","",IF(F396&gt;0,(F396+IFERROR(VLOOKUP(E396,機種マスタ!$K$4:$L$6,2,FALSE),0))*G396,0))</f>
         <v/>
       </c>
     </row>
@@ -14926,7 +14927,7 @@
         <v/>
       </c>
       <c r="H397" s="30">
-        <f>IF($B397="","",F397*G397)</f>
+        <f>IF($B397="","",IF(F397&gt;0,(F397+IFERROR(VLOOKUP(E397,機種マスタ!$K$4:$L$6,2,FALSE),0))*G397,0))</f>
         <v/>
       </c>
     </row>
@@ -14951,7 +14952,7 @@
         <v/>
       </c>
       <c r="H398" s="30">
-        <f>IF($B398="","",F398*G398)</f>
+        <f>IF($B398="","",IF(F398&gt;0,(F398+IFERROR(VLOOKUP(E398,機種マスタ!$K$4:$L$6,2,FALSE),0))*G398,0))</f>
         <v/>
       </c>
     </row>
@@ -14976,7 +14977,7 @@
         <v/>
       </c>
       <c r="H399" s="30">
-        <f>IF($B399="","",F399*G399)</f>
+        <f>IF($B399="","",IF(F399&gt;0,(F399+IFERROR(VLOOKUP(E399,機種マスタ!$K$4:$L$6,2,FALSE),0))*G399,0))</f>
         <v/>
       </c>
     </row>
@@ -15001,7 +15002,7 @@
         <v/>
       </c>
       <c r="H400" s="30">
-        <f>IF($B400="","",F400*G400)</f>
+        <f>IF($B400="","",IF(F400&gt;0,(F400+IFERROR(VLOOKUP(E400,機種マスタ!$K$4:$L$6,2,FALSE),0))*G400,0))</f>
         <v/>
       </c>
     </row>
@@ -15026,7 +15027,7 @@
         <v/>
       </c>
       <c r="H401" s="30">
-        <f>IF($B401="","",F401*G401)</f>
+        <f>IF($B401="","",IF(F401&gt;0,(F401+IFERROR(VLOOKUP(E401,機種マスタ!$K$4:$L$6,2,FALSE),0))*G401,0))</f>
         <v/>
       </c>
     </row>
@@ -15051,7 +15052,7 @@
         <v/>
       </c>
       <c r="H402" s="30">
-        <f>IF($B402="","",F402*G402)</f>
+        <f>IF($B402="","",IF(F402&gt;0,(F402+IFERROR(VLOOKUP(E402,機種マスタ!$K$4:$L$6,2,FALSE),0))*G402,0))</f>
         <v/>
       </c>
     </row>
@@ -15076,7 +15077,7 @@
         <v/>
       </c>
       <c r="H403" s="30">
-        <f>IF($B403="","",F403*G403)</f>
+        <f>IF($B403="","",IF(F403&gt;0,(F403+IFERROR(VLOOKUP(E403,機種マスタ!$K$4:$L$6,2,FALSE),0))*G403,0))</f>
         <v/>
       </c>
     </row>
@@ -15101,7 +15102,7 @@
         <v/>
       </c>
       <c r="H404" s="30">
-        <f>IF($B404="","",F404*G404)</f>
+        <f>IF($B404="","",IF(F404&gt;0,(F404+IFERROR(VLOOKUP(E404,機種マスタ!$K$4:$L$6,2,FALSE),0))*G404,0))</f>
         <v/>
       </c>
     </row>
@@ -15126,7 +15127,7 @@
         <v/>
       </c>
       <c r="H405" s="30">
-        <f>IF($B405="","",F405*G405)</f>
+        <f>IF($B405="","",IF(F405&gt;0,(F405+IFERROR(VLOOKUP(E405,機種マスタ!$K$4:$L$6,2,FALSE),0))*G405,0))</f>
         <v/>
       </c>
     </row>
@@ -15151,7 +15152,7 @@
         <v/>
       </c>
       <c r="H406" s="30">
-        <f>IF($B406="","",F406*G406)</f>
+        <f>IF($B406="","",IF(F406&gt;0,(F406+IFERROR(VLOOKUP(E406,機種マスタ!$K$4:$L$6,2,FALSE),0))*G406,0))</f>
         <v/>
       </c>
     </row>
@@ -15176,7 +15177,7 @@
         <v/>
       </c>
       <c r="H407" s="30">
-        <f>IF($B407="","",F407*G407)</f>
+        <f>IF($B407="","",IF(F407&gt;0,(F407+IFERROR(VLOOKUP(E407,機種マスタ!$K$4:$L$6,2,FALSE),0))*G407,0))</f>
         <v/>
       </c>
     </row>
@@ -15201,7 +15202,7 @@
         <v/>
       </c>
       <c r="H408" s="30">
-        <f>IF($B408="","",F408*G408)</f>
+        <f>IF($B408="","",IF(F408&gt;0,(F408+IFERROR(VLOOKUP(E408,機種マスタ!$K$4:$L$6,2,FALSE),0))*G408,0))</f>
         <v/>
       </c>
     </row>
@@ -15226,7 +15227,7 @@
         <v/>
       </c>
       <c r="H409" s="30">
-        <f>IF($B409="","",F409*G409)</f>
+        <f>IF($B409="","",IF(F409&gt;0,(F409+IFERROR(VLOOKUP(E409,機種マスタ!$K$4:$L$6,2,FALSE),0))*G409,0))</f>
         <v/>
       </c>
     </row>
@@ -15251,7 +15252,7 @@
         <v/>
       </c>
       <c r="H410" s="30">
-        <f>IF($B410="","",F410*G410)</f>
+        <f>IF($B410="","",IF(F410&gt;0,(F410+IFERROR(VLOOKUP(E410,機種マスタ!$K$4:$L$6,2,FALSE),0))*G410,0))</f>
         <v/>
       </c>
     </row>
@@ -15276,7 +15277,7 @@
         <v/>
       </c>
       <c r="H411" s="30">
-        <f>IF($B411="","",F411*G411)</f>
+        <f>IF($B411="","",IF(F411&gt;0,(F411+IFERROR(VLOOKUP(E411,機種マスタ!$K$4:$L$6,2,FALSE),0))*G411,0))</f>
         <v/>
       </c>
     </row>
@@ -15301,7 +15302,7 @@
         <v/>
       </c>
       <c r="H412" s="30">
-        <f>IF($B412="","",F412*G412)</f>
+        <f>IF($B412="","",IF(F412&gt;0,(F412+IFERROR(VLOOKUP(E412,機種マスタ!$K$4:$L$6,2,FALSE),0))*G412,0))</f>
         <v/>
       </c>
     </row>
@@ -15326,7 +15327,7 @@
         <v/>
       </c>
       <c r="H413" s="30">
-        <f>IF($B413="","",F413*G413)</f>
+        <f>IF($B413="","",IF(F413&gt;0,(F413+IFERROR(VLOOKUP(E413,機種マスタ!$K$4:$L$6,2,FALSE),0))*G413,0))</f>
         <v/>
       </c>
     </row>
@@ -15351,7 +15352,7 @@
         <v/>
       </c>
       <c r="H414" s="30">
-        <f>IF($B414="","",F414*G414)</f>
+        <f>IF($B414="","",IF(F414&gt;0,(F414+IFERROR(VLOOKUP(E414,機種マスタ!$K$4:$L$6,2,FALSE),0))*G414,0))</f>
         <v/>
       </c>
     </row>
@@ -15376,7 +15377,7 @@
         <v/>
       </c>
       <c r="H415" s="30">
-        <f>IF($B415="","",F415*G415)</f>
+        <f>IF($B415="","",IF(F415&gt;0,(F415+IFERROR(VLOOKUP(E415,機種マスタ!$K$4:$L$6,2,FALSE),0))*G415,0))</f>
         <v/>
       </c>
     </row>
@@ -15401,7 +15402,7 @@
         <v/>
       </c>
       <c r="H416" s="30">
-        <f>IF($B416="","",F416*G416)</f>
+        <f>IF($B416="","",IF(F416&gt;0,(F416+IFERROR(VLOOKUP(E416,機種マスタ!$K$4:$L$6,2,FALSE),0))*G416,0))</f>
         <v/>
       </c>
     </row>
@@ -15426,7 +15427,7 @@
         <v/>
       </c>
       <c r="H417" s="30">
-        <f>IF($B417="","",F417*G417)</f>
+        <f>IF($B417="","",IF(F417&gt;0,(F417+IFERROR(VLOOKUP(E417,機種マスタ!$K$4:$L$6,2,FALSE),0))*G417,0))</f>
         <v/>
       </c>
     </row>
@@ -15451,7 +15452,7 @@
         <v/>
       </c>
       <c r="H418" s="30">
-        <f>IF($B418="","",F418*G418)</f>
+        <f>IF($B418="","",IF(F418&gt;0,(F418+IFERROR(VLOOKUP(E418,機種マスタ!$K$4:$L$6,2,FALSE),0))*G418,0))</f>
         <v/>
       </c>
     </row>
@@ -15476,7 +15477,7 @@
         <v/>
       </c>
       <c r="H419" s="30">
-        <f>IF($B419="","",F419*G419)</f>
+        <f>IF($B419="","",IF(F419&gt;0,(F419+IFERROR(VLOOKUP(E419,機種マスタ!$K$4:$L$6,2,FALSE),0))*G419,0))</f>
         <v/>
       </c>
     </row>
@@ -15501,7 +15502,7 @@
         <v/>
       </c>
       <c r="H420" s="30">
-        <f>IF($B420="","",F420*G420)</f>
+        <f>IF($B420="","",IF(F420&gt;0,(F420+IFERROR(VLOOKUP(E420,機種マスタ!$K$4:$L$6,2,FALSE),0))*G420,0))</f>
         <v/>
       </c>
     </row>
@@ -15526,7 +15527,7 @@
         <v/>
       </c>
       <c r="H421" s="30">
-        <f>IF($B421="","",F421*G421)</f>
+        <f>IF($B421="","",IF(F421&gt;0,(F421+IFERROR(VLOOKUP(E421,機種マスタ!$K$4:$L$6,2,FALSE),0))*G421,0))</f>
         <v/>
       </c>
     </row>
@@ -15551,7 +15552,7 @@
         <v/>
       </c>
       <c r="H422" s="30">
-        <f>IF($B422="","",F422*G422)</f>
+        <f>IF($B422="","",IF(F422&gt;0,(F422+IFERROR(VLOOKUP(E422,機種マスタ!$K$4:$L$6,2,FALSE),0))*G422,0))</f>
         <v/>
       </c>
     </row>
@@ -15576,7 +15577,7 @@
         <v/>
       </c>
       <c r="H423" s="30">
-        <f>IF($B423="","",F423*G423)</f>
+        <f>IF($B423="","",IF(F423&gt;0,(F423+IFERROR(VLOOKUP(E423,機種マスタ!$K$4:$L$6,2,FALSE),0))*G423,0))</f>
         <v/>
       </c>
     </row>
@@ -15601,7 +15602,7 @@
         <v/>
       </c>
       <c r="H424" s="30">
-        <f>IF($B424="","",F424*G424)</f>
+        <f>IF($B424="","",IF(F424&gt;0,(F424+IFERROR(VLOOKUP(E424,機種マスタ!$K$4:$L$6,2,FALSE),0))*G424,0))</f>
         <v/>
       </c>
     </row>
@@ -15626,7 +15627,7 @@
         <v/>
       </c>
       <c r="H425" s="30">
-        <f>IF($B425="","",F425*G425)</f>
+        <f>IF($B425="","",IF(F425&gt;0,(F425+IFERROR(VLOOKUP(E425,機種マスタ!$K$4:$L$6,2,FALSE),0))*G425,0))</f>
         <v/>
       </c>
     </row>
@@ -15651,7 +15652,7 @@
         <v/>
       </c>
       <c r="H426" s="30">
-        <f>IF($B426="","",F426*G426)</f>
+        <f>IF($B426="","",IF(F426&gt;0,(F426+IFERROR(VLOOKUP(E426,機種マスタ!$K$4:$L$6,2,FALSE),0))*G426,0))</f>
         <v/>
       </c>
     </row>
@@ -15676,7 +15677,7 @@
         <v/>
       </c>
       <c r="H427" s="30">
-        <f>IF($B427="","",F427*G427)</f>
+        <f>IF($B427="","",IF(F427&gt;0,(F427+IFERROR(VLOOKUP(E427,機種マスタ!$K$4:$L$6,2,FALSE),0))*G427,0))</f>
         <v/>
       </c>
     </row>
@@ -15701,7 +15702,7 @@
         <v/>
       </c>
       <c r="H428" s="30">
-        <f>IF($B428="","",F428*G428)</f>
+        <f>IF($B428="","",IF(F428&gt;0,(F428+IFERROR(VLOOKUP(E428,機種マスタ!$K$4:$L$6,2,FALSE),0))*G428,0))</f>
         <v/>
       </c>
     </row>
@@ -15726,7 +15727,7 @@
         <v/>
       </c>
       <c r="H429" s="30">
-        <f>IF($B429="","",F429*G429)</f>
+        <f>IF($B429="","",IF(F429&gt;0,(F429+IFERROR(VLOOKUP(E429,機種マスタ!$K$4:$L$6,2,FALSE),0))*G429,0))</f>
         <v/>
       </c>
     </row>
@@ -15751,7 +15752,7 @@
         <v/>
       </c>
       <c r="H430" s="30">
-        <f>IF($B430="","",F430*G430)</f>
+        <f>IF($B430="","",IF(F430&gt;0,(F430+IFERROR(VLOOKUP(E430,機種マスタ!$K$4:$L$6,2,FALSE),0))*G430,0))</f>
         <v/>
       </c>
     </row>
@@ -15776,7 +15777,7 @@
         <v/>
       </c>
       <c r="H431" s="30">
-        <f>IF($B431="","",F431*G431)</f>
+        <f>IF($B431="","",IF(F431&gt;0,(F431+IFERROR(VLOOKUP(E431,機種マスタ!$K$4:$L$6,2,FALSE),0))*G431,0))</f>
         <v/>
       </c>
     </row>
@@ -15801,7 +15802,7 @@
         <v/>
       </c>
       <c r="H432" s="30">
-        <f>IF($B432="","",F432*G432)</f>
+        <f>IF($B432="","",IF(F432&gt;0,(F432+IFERROR(VLOOKUP(E432,機種マスタ!$K$4:$L$6,2,FALSE),0))*G432,0))</f>
         <v/>
       </c>
     </row>
@@ -15826,7 +15827,7 @@
         <v/>
       </c>
       <c r="H433" s="30">
-        <f>IF($B433="","",F433*G433)</f>
+        <f>IF($B433="","",IF(F433&gt;0,(F433+IFERROR(VLOOKUP(E433,機種マスタ!$K$4:$L$6,2,FALSE),0))*G433,0))</f>
         <v/>
       </c>
     </row>
@@ -15851,7 +15852,7 @@
         <v/>
       </c>
       <c r="H434" s="30">
-        <f>IF($B434="","",F434*G434)</f>
+        <f>IF($B434="","",IF(F434&gt;0,(F434+IFERROR(VLOOKUP(E434,機種マスタ!$K$4:$L$6,2,FALSE),0))*G434,0))</f>
         <v/>
       </c>
     </row>
@@ -15876,7 +15877,7 @@
         <v/>
       </c>
       <c r="H435" s="30">
-        <f>IF($B435="","",F435*G435)</f>
+        <f>IF($B435="","",IF(F435&gt;0,(F435+IFERROR(VLOOKUP(E435,機種マスタ!$K$4:$L$6,2,FALSE),0))*G435,0))</f>
         <v/>
       </c>
     </row>
@@ -15901,7 +15902,7 @@
         <v/>
       </c>
       <c r="H436" s="30">
-        <f>IF($B436="","",F436*G436)</f>
+        <f>IF($B436="","",IF(F436&gt;0,(F436+IFERROR(VLOOKUP(E436,機種マスタ!$K$4:$L$6,2,FALSE),0))*G436,0))</f>
         <v/>
       </c>
     </row>
@@ -15926,7 +15927,7 @@
         <v/>
       </c>
       <c r="H437" s="30">
-        <f>IF($B437="","",F437*G437)</f>
+        <f>IF($B437="","",IF(F437&gt;0,(F437+IFERROR(VLOOKUP(E437,機種マスタ!$K$4:$L$6,2,FALSE),0))*G437,0))</f>
         <v/>
       </c>
     </row>
@@ -15951,7 +15952,7 @@
         <v/>
       </c>
       <c r="H438" s="30">
-        <f>IF($B438="","",F438*G438)</f>
+        <f>IF($B438="","",IF(F438&gt;0,(F438+IFERROR(VLOOKUP(E438,機種マスタ!$K$4:$L$6,2,FALSE),0))*G438,0))</f>
         <v/>
       </c>
     </row>
@@ -15976,7 +15977,7 @@
         <v/>
       </c>
       <c r="H439" s="30">
-        <f>IF($B439="","",F439*G439)</f>
+        <f>IF($B439="","",IF(F439&gt;0,(F439+IFERROR(VLOOKUP(E439,機種マスタ!$K$4:$L$6,2,FALSE),0))*G439,0))</f>
         <v/>
       </c>
     </row>
@@ -16001,7 +16002,7 @@
         <v/>
       </c>
       <c r="H440" s="30">
-        <f>IF($B440="","",F440*G440)</f>
+        <f>IF($B440="","",IF(F440&gt;0,(F440+IFERROR(VLOOKUP(E440,機種マスタ!$K$4:$L$6,2,FALSE),0))*G440,0))</f>
         <v/>
       </c>
     </row>
@@ -16026,7 +16027,7 @@
         <v/>
       </c>
       <c r="H441" s="30">
-        <f>IF($B441="","",F441*G441)</f>
+        <f>IF($B441="","",IF(F441&gt;0,(F441+IFERROR(VLOOKUP(E441,機種マスタ!$K$4:$L$6,2,FALSE),0))*G441,0))</f>
         <v/>
       </c>
     </row>
@@ -16051,7 +16052,7 @@
         <v/>
       </c>
       <c r="H442" s="30">
-        <f>IF($B442="","",F442*G442)</f>
+        <f>IF($B442="","",IF(F442&gt;0,(F442+IFERROR(VLOOKUP(E442,機種マスタ!$K$4:$L$6,2,FALSE),0))*G442,0))</f>
         <v/>
       </c>
     </row>
@@ -16076,7 +16077,7 @@
         <v/>
       </c>
       <c r="H443" s="30">
-        <f>IF($B443="","",F443*G443)</f>
+        <f>IF($B443="","",IF(F443&gt;0,(F443+IFERROR(VLOOKUP(E443,機種マスタ!$K$4:$L$6,2,FALSE),0))*G443,0))</f>
         <v/>
       </c>
     </row>
@@ -16101,7 +16102,7 @@
         <v/>
       </c>
       <c r="H444" s="30">
-        <f>IF($B444="","",F444*G444)</f>
+        <f>IF($B444="","",IF(F444&gt;0,(F444+IFERROR(VLOOKUP(E444,機種マスタ!$K$4:$L$6,2,FALSE),0))*G444,0))</f>
         <v/>
       </c>
     </row>
@@ -16126,7 +16127,7 @@
         <v/>
       </c>
       <c r="H445" s="30">
-        <f>IF($B445="","",F445*G445)</f>
+        <f>IF($B445="","",IF(F445&gt;0,(F445+IFERROR(VLOOKUP(E445,機種マスタ!$K$4:$L$6,2,FALSE),0))*G445,0))</f>
         <v/>
       </c>
     </row>
@@ -16151,7 +16152,7 @@
         <v/>
       </c>
       <c r="H446" s="30">
-        <f>IF($B446="","",F446*G446)</f>
+        <f>IF($B446="","",IF(F446&gt;0,(F446+IFERROR(VLOOKUP(E446,機種マスタ!$K$4:$L$6,2,FALSE),0))*G446,0))</f>
         <v/>
       </c>
     </row>
@@ -16176,7 +16177,7 @@
         <v/>
       </c>
       <c r="H447" s="30">
-        <f>IF($B447="","",F447*G447)</f>
+        <f>IF($B447="","",IF(F447&gt;0,(F447+IFERROR(VLOOKUP(E447,機種マスタ!$K$4:$L$6,2,FALSE),0))*G447,0))</f>
         <v/>
       </c>
     </row>
@@ -16201,7 +16202,7 @@
         <v/>
       </c>
       <c r="H448" s="30">
-        <f>IF($B448="","",F448*G448)</f>
+        <f>IF($B448="","",IF(F448&gt;0,(F448+IFERROR(VLOOKUP(E448,機種マスタ!$K$4:$L$6,2,FALSE),0))*G448,0))</f>
         <v/>
       </c>
     </row>
@@ -16226,7 +16227,7 @@
         <v/>
       </c>
       <c r="H449" s="30">
-        <f>IF($B449="","",F449*G449)</f>
+        <f>IF($B449="","",IF(F449&gt;0,(F449+IFERROR(VLOOKUP(E449,機種マスタ!$K$4:$L$6,2,FALSE),0))*G449,0))</f>
         <v/>
       </c>
     </row>
@@ -16251,7 +16252,7 @@
         <v/>
       </c>
       <c r="H450" s="30">
-        <f>IF($B450="","",F450*G450)</f>
+        <f>IF($B450="","",IF(F450&gt;0,(F450+IFERROR(VLOOKUP(E450,機種マスタ!$K$4:$L$6,2,FALSE),0))*G450,0))</f>
         <v/>
       </c>
     </row>
@@ -16276,7 +16277,7 @@
         <v/>
       </c>
       <c r="H451" s="30">
-        <f>IF($B451="","",F451*G451)</f>
+        <f>IF($B451="","",IF(F451&gt;0,(F451+IFERROR(VLOOKUP(E451,機種マスタ!$K$4:$L$6,2,FALSE),0))*G451,0))</f>
         <v/>
       </c>
     </row>
@@ -16301,7 +16302,7 @@
         <v/>
       </c>
       <c r="H452" s="30">
-        <f>IF($B452="","",F452*G452)</f>
+        <f>IF($B452="","",IF(F452&gt;0,(F452+IFERROR(VLOOKUP(E452,機種マスタ!$K$4:$L$6,2,FALSE),0))*G452,0))</f>
         <v/>
       </c>
     </row>
@@ -16326,7 +16327,7 @@
         <v/>
       </c>
       <c r="H453" s="30">
-        <f>IF($B453="","",F453*G453)</f>
+        <f>IF($B453="","",IF(F453&gt;0,(F453+IFERROR(VLOOKUP(E453,機種マスタ!$K$4:$L$6,2,FALSE),0))*G453,0))</f>
         <v/>
       </c>
     </row>
@@ -16351,7 +16352,7 @@
         <v/>
       </c>
       <c r="H454" s="30">
-        <f>IF($B454="","",F454*G454)</f>
+        <f>IF($B454="","",IF(F454&gt;0,(F454+IFERROR(VLOOKUP(E454,機種マスタ!$K$4:$L$6,2,FALSE),0))*G454,0))</f>
         <v/>
       </c>
     </row>
@@ -16376,7 +16377,7 @@
         <v/>
       </c>
       <c r="H455" s="30">
-        <f>IF($B455="","",F455*G455)</f>
+        <f>IF($B455="","",IF(F455&gt;0,(F455+IFERROR(VLOOKUP(E455,機種マスタ!$K$4:$L$6,2,FALSE),0))*G455,0))</f>
         <v/>
       </c>
     </row>
@@ -16401,7 +16402,7 @@
         <v/>
       </c>
       <c r="H456" s="30">
-        <f>IF($B456="","",F456*G456)</f>
+        <f>IF($B456="","",IF(F456&gt;0,(F456+IFERROR(VLOOKUP(E456,機種マスタ!$K$4:$L$6,2,FALSE),0))*G456,0))</f>
         <v/>
       </c>
     </row>
@@ -16426,7 +16427,7 @@
         <v/>
       </c>
       <c r="H457" s="30">
-        <f>IF($B457="","",F457*G457)</f>
+        <f>IF($B457="","",IF(F457&gt;0,(F457+IFERROR(VLOOKUP(E457,機種マスタ!$K$4:$L$6,2,FALSE),0))*G457,0))</f>
         <v/>
       </c>
     </row>
@@ -16451,7 +16452,7 @@
         <v/>
       </c>
       <c r="H458" s="30">
-        <f>IF($B458="","",F458*G458)</f>
+        <f>IF($B458="","",IF(F458&gt;0,(F458+IFERROR(VLOOKUP(E458,機種マスタ!$K$4:$L$6,2,FALSE),0))*G458,0))</f>
         <v/>
       </c>
     </row>
@@ -16476,7 +16477,7 @@
         <v/>
       </c>
       <c r="H459" s="30">
-        <f>IF($B459="","",F459*G459)</f>
+        <f>IF($B459="","",IF(F459&gt;0,(F459+IFERROR(VLOOKUP(E459,機種マスタ!$K$4:$L$6,2,FALSE),0))*G459,0))</f>
         <v/>
       </c>
     </row>
@@ -16501,7 +16502,7 @@
         <v/>
       </c>
       <c r="H460" s="30">
-        <f>IF($B460="","",F460*G460)</f>
+        <f>IF($B460="","",IF(F460&gt;0,(F460+IFERROR(VLOOKUP(E460,機種マスタ!$K$4:$L$6,2,FALSE),0))*G460,0))</f>
         <v/>
       </c>
     </row>
@@ -16526,7 +16527,7 @@
         <v/>
       </c>
       <c r="H461" s="30">
-        <f>IF($B461="","",F461*G461)</f>
+        <f>IF($B461="","",IF(F461&gt;0,(F461+IFERROR(VLOOKUP(E461,機種マスタ!$K$4:$L$6,2,FALSE),0))*G461,0))</f>
         <v/>
       </c>
     </row>
@@ -16551,7 +16552,7 @@
         <v/>
       </c>
       <c r="H462" s="30">
-        <f>IF($B462="","",F462*G462)</f>
+        <f>IF($B462="","",IF(F462&gt;0,(F462+IFERROR(VLOOKUP(E462,機種マスタ!$K$4:$L$6,2,FALSE),0))*G462,0))</f>
         <v/>
       </c>
     </row>
@@ -16576,7 +16577,7 @@
         <v/>
       </c>
       <c r="H463" s="30">
-        <f>IF($B463="","",F463*G463)</f>
+        <f>IF($B463="","",IF(F463&gt;0,(F463+IFERROR(VLOOKUP(E463,機種マスタ!$K$4:$L$6,2,FALSE),0))*G463,0))</f>
         <v/>
       </c>
     </row>
@@ -16601,7 +16602,7 @@
         <v/>
       </c>
       <c r="H464" s="30">
-        <f>IF($B464="","",F464*G464)</f>
+        <f>IF($B464="","",IF(F464&gt;0,(F464+IFERROR(VLOOKUP(E464,機種マスタ!$K$4:$L$6,2,FALSE),0))*G464,0))</f>
         <v/>
       </c>
     </row>
@@ -16626,7 +16627,7 @@
         <v/>
       </c>
       <c r="H465" s="30">
-        <f>IF($B465="","",F465*G465)</f>
+        <f>IF($B465="","",IF(F465&gt;0,(F465+IFERROR(VLOOKUP(E465,機種マスタ!$K$4:$L$6,2,FALSE),0))*G465,0))</f>
         <v/>
       </c>
     </row>
@@ -16651,7 +16652,7 @@
         <v/>
       </c>
       <c r="H466" s="30">
-        <f>IF($B466="","",F466*G466)</f>
+        <f>IF($B466="","",IF(F466&gt;0,(F466+IFERROR(VLOOKUP(E466,機種マスタ!$K$4:$L$6,2,FALSE),0))*G466,0))</f>
         <v/>
       </c>
     </row>
@@ -16676,7 +16677,7 @@
         <v/>
       </c>
       <c r="H467" s="30">
-        <f>IF($B467="","",F467*G467)</f>
+        <f>IF($B467="","",IF(F467&gt;0,(F467+IFERROR(VLOOKUP(E467,機種マスタ!$K$4:$L$6,2,FALSE),0))*G467,0))</f>
         <v/>
       </c>
     </row>
@@ -16701,7 +16702,7 @@
         <v/>
       </c>
       <c r="H468" s="30">
-        <f>IF($B468="","",F468*G468)</f>
+        <f>IF($B468="","",IF(F468&gt;0,(F468+IFERROR(VLOOKUP(E468,機種マスタ!$K$4:$L$6,2,FALSE),0))*G468,0))</f>
         <v/>
       </c>
     </row>
@@ -16726,7 +16727,7 @@
         <v/>
       </c>
       <c r="H469" s="30">
-        <f>IF($B469="","",F469*G469)</f>
+        <f>IF($B469="","",IF(F469&gt;0,(F469+IFERROR(VLOOKUP(E469,機種マスタ!$K$4:$L$6,2,FALSE),0))*G469,0))</f>
         <v/>
       </c>
     </row>
@@ -16751,7 +16752,7 @@
         <v/>
       </c>
       <c r="H470" s="30">
-        <f>IF($B470="","",F470*G470)</f>
+        <f>IF($B470="","",IF(F470&gt;0,(F470+IFERROR(VLOOKUP(E470,機種マスタ!$K$4:$L$6,2,FALSE),0))*G470,0))</f>
         <v/>
       </c>
     </row>
@@ -16776,7 +16777,7 @@
         <v/>
       </c>
       <c r="H471" s="30">
-        <f>IF($B471="","",F471*G471)</f>
+        <f>IF($B471="","",IF(F471&gt;0,(F471+IFERROR(VLOOKUP(E471,機種マスタ!$K$4:$L$6,2,FALSE),0))*G471,0))</f>
         <v/>
       </c>
     </row>
@@ -16801,7 +16802,7 @@
         <v/>
       </c>
       <c r="H472" s="30">
-        <f>IF($B472="","",F472*G472)</f>
+        <f>IF($B472="","",IF(F472&gt;0,(F472+IFERROR(VLOOKUP(E472,機種マスタ!$K$4:$L$6,2,FALSE),0))*G472,0))</f>
         <v/>
       </c>
     </row>
@@ -16826,7 +16827,7 @@
         <v/>
       </c>
       <c r="H473" s="30">
-        <f>IF($B473="","",F473*G473)</f>
+        <f>IF($B473="","",IF(F473&gt;0,(F473+IFERROR(VLOOKUP(E473,機種マスタ!$K$4:$L$6,2,FALSE),0))*G473,0))</f>
         <v/>
       </c>
     </row>
@@ -16851,7 +16852,7 @@
         <v/>
       </c>
       <c r="H474" s="30">
-        <f>IF($B474="","",F474*G474)</f>
+        <f>IF($B474="","",IF(F474&gt;0,(F474+IFERROR(VLOOKUP(E474,機種マスタ!$K$4:$L$6,2,FALSE),0))*G474,0))</f>
         <v/>
       </c>
     </row>
@@ -16876,7 +16877,7 @@
         <v/>
       </c>
       <c r="H475" s="30">
-        <f>IF($B475="","",F475*G475)</f>
+        <f>IF($B475="","",IF(F475&gt;0,(F475+IFERROR(VLOOKUP(E475,機種マスタ!$K$4:$L$6,2,FALSE),0))*G475,0))</f>
         <v/>
       </c>
     </row>
@@ -16901,7 +16902,7 @@
         <v/>
       </c>
       <c r="H476" s="30">
-        <f>IF($B476="","",F476*G476)</f>
+        <f>IF($B476="","",IF(F476&gt;0,(F476+IFERROR(VLOOKUP(E476,機種マスタ!$K$4:$L$6,2,FALSE),0))*G476,0))</f>
         <v/>
       </c>
     </row>
@@ -16926,7 +16927,7 @@
         <v/>
       </c>
       <c r="H477" s="30">
-        <f>IF($B477="","",F477*G477)</f>
+        <f>IF($B477="","",IF(F477&gt;0,(F477+IFERROR(VLOOKUP(E477,機種マスタ!$K$4:$L$6,2,FALSE),0))*G477,0))</f>
         <v/>
       </c>
     </row>
@@ -16951,7 +16952,7 @@
         <v/>
       </c>
       <c r="H478" s="30">
-        <f>IF($B478="","",F478*G478)</f>
+        <f>IF($B478="","",IF(F478&gt;0,(F478+IFERROR(VLOOKUP(E478,機種マスタ!$K$4:$L$6,2,FALSE),0))*G478,0))</f>
         <v/>
       </c>
     </row>
@@ -16976,7 +16977,7 @@
         <v/>
       </c>
       <c r="H479" s="30">
-        <f>IF($B479="","",F479*G479)</f>
+        <f>IF($B479="","",IF(F479&gt;0,(F479+IFERROR(VLOOKUP(E479,機種マスタ!$K$4:$L$6,2,FALSE),0))*G479,0))</f>
         <v/>
       </c>
     </row>
@@ -17001,7 +17002,7 @@
         <v/>
       </c>
       <c r="H480" s="30">
-        <f>IF($B480="","",F480*G480)</f>
+        <f>IF($B480="","",IF(F480&gt;0,(F480+IFERROR(VLOOKUP(E480,機種マスタ!$K$4:$L$6,2,FALSE),0))*G480,0))</f>
         <v/>
       </c>
     </row>
@@ -17026,7 +17027,7 @@
         <v/>
       </c>
       <c r="H481" s="30">
-        <f>IF($B481="","",F481*G481)</f>
+        <f>IF($B481="","",IF(F481&gt;0,(F481+IFERROR(VLOOKUP(E481,機種マスタ!$K$4:$L$6,2,FALSE),0))*G481,0))</f>
         <v/>
       </c>
     </row>
@@ -17051,7 +17052,7 @@
         <v/>
       </c>
       <c r="H482" s="30">
-        <f>IF($B482="","",F482*G482)</f>
+        <f>IF($B482="","",IF(F482&gt;0,(F482+IFERROR(VLOOKUP(E482,機種マスタ!$K$4:$L$6,2,FALSE),0))*G482,0))</f>
         <v/>
       </c>
     </row>
@@ -17076,7 +17077,7 @@
         <v/>
       </c>
       <c r="H483" s="30">
-        <f>IF($B483="","",F483*G483)</f>
+        <f>IF($B483="","",IF(F483&gt;0,(F483+IFERROR(VLOOKUP(E483,機種マスタ!$K$4:$L$6,2,FALSE),0))*G483,0))</f>
         <v/>
       </c>
     </row>
@@ -17101,7 +17102,7 @@
         <v/>
       </c>
       <c r="H484" s="30">
-        <f>IF($B484="","",F484*G484)</f>
+        <f>IF($B484="","",IF(F484&gt;0,(F484+IFERROR(VLOOKUP(E484,機種マスタ!$K$4:$L$6,2,FALSE),0))*G484,0))</f>
         <v/>
       </c>
     </row>
@@ -17126,7 +17127,7 @@
         <v/>
       </c>
       <c r="H485" s="30">
-        <f>IF($B485="","",F485*G485)</f>
+        <f>IF($B485="","",IF(F485&gt;0,(F485+IFERROR(VLOOKUP(E485,機種マスタ!$K$4:$L$6,2,FALSE),0))*G485,0))</f>
         <v/>
       </c>
     </row>
@@ -17151,7 +17152,7 @@
         <v/>
       </c>
       <c r="H486" s="30">
-        <f>IF($B486="","",F486*G486)</f>
+        <f>IF($B486="","",IF(F486&gt;0,(F486+IFERROR(VLOOKUP(E486,機種マスタ!$K$4:$L$6,2,FALSE),0))*G486,0))</f>
         <v/>
       </c>
     </row>
@@ -17176,7 +17177,7 @@
         <v/>
       </c>
       <c r="H487" s="30">
-        <f>IF($B487="","",F487*G487)</f>
+        <f>IF($B487="","",IF(F487&gt;0,(F487+IFERROR(VLOOKUP(E487,機種マスタ!$K$4:$L$6,2,FALSE),0))*G487,0))</f>
         <v/>
       </c>
     </row>
@@ -17201,7 +17202,7 @@
         <v/>
       </c>
       <c r="H488" s="30">
-        <f>IF($B488="","",F488*G488)</f>
+        <f>IF($B488="","",IF(F488&gt;0,(F488+IFERROR(VLOOKUP(E488,機種マスタ!$K$4:$L$6,2,FALSE),0))*G488,0))</f>
         <v/>
       </c>
     </row>
@@ -17226,7 +17227,7 @@
         <v/>
       </c>
       <c r="H489" s="30">
-        <f>IF($B489="","",F489*G489)</f>
+        <f>IF($B489="","",IF(F489&gt;0,(F489+IFERROR(VLOOKUP(E489,機種マスタ!$K$4:$L$6,2,FALSE),0))*G489,0))</f>
         <v/>
       </c>
     </row>
@@ -17251,7 +17252,7 @@
         <v/>
       </c>
       <c r="H490" s="30">
-        <f>IF($B490="","",F490*G490)</f>
+        <f>IF($B490="","",IF(F490&gt;0,(F490+IFERROR(VLOOKUP(E490,機種マスタ!$K$4:$L$6,2,FALSE),0))*G490,0))</f>
         <v/>
       </c>
     </row>
@@ -17276,7 +17277,7 @@
         <v/>
       </c>
       <c r="H491" s="30">
-        <f>IF($B491="","",F491*G491)</f>
+        <f>IF($B491="","",IF(F491&gt;0,(F491+IFERROR(VLOOKUP(E491,機種マスタ!$K$4:$L$6,2,FALSE),0))*G491,0))</f>
         <v/>
       </c>
     </row>
@@ -17301,7 +17302,7 @@
         <v/>
       </c>
       <c r="H492" s="30">
-        <f>IF($B492="","",F492*G492)</f>
+        <f>IF($B492="","",IF(F492&gt;0,(F492+IFERROR(VLOOKUP(E492,機種マスタ!$K$4:$L$6,2,FALSE),0))*G492,0))</f>
         <v/>
       </c>
     </row>
@@ -17326,7 +17327,7 @@
         <v/>
       </c>
       <c r="H493" s="30">
-        <f>IF($B493="","",F493*G493)</f>
+        <f>IF($B493="","",IF(F493&gt;0,(F493+IFERROR(VLOOKUP(E493,機種マスタ!$K$4:$L$6,2,FALSE),0))*G493,0))</f>
         <v/>
       </c>
     </row>
@@ -17351,7 +17352,7 @@
         <v/>
       </c>
       <c r="H494" s="30">
-        <f>IF($B494="","",F494*G494)</f>
+        <f>IF($B494="","",IF(F494&gt;0,(F494+IFERROR(VLOOKUP(E494,機種マスタ!$K$4:$L$6,2,FALSE),0))*G494,0))</f>
         <v/>
       </c>
     </row>
@@ -17376,7 +17377,7 @@
         <v/>
       </c>
       <c r="H495" s="30">
-        <f>IF($B495="","",F495*G495)</f>
+        <f>IF($B495="","",IF(F495&gt;0,(F495+IFERROR(VLOOKUP(E495,機種マスタ!$K$4:$L$6,2,FALSE),0))*G495,0))</f>
         <v/>
       </c>
     </row>
@@ -17401,7 +17402,7 @@
         <v/>
       </c>
       <c r="H496" s="30">
-        <f>IF($B496="","",F496*G496)</f>
+        <f>IF($B496="","",IF(F496&gt;0,(F496+IFERROR(VLOOKUP(E496,機種マスタ!$K$4:$L$6,2,FALSE),0))*G496,0))</f>
         <v/>
       </c>
     </row>
@@ -17426,7 +17427,7 @@
         <v/>
       </c>
       <c r="H497" s="30">
-        <f>IF($B497="","",F497*G497)</f>
+        <f>IF($B497="","",IF(F497&gt;0,(F497+IFERROR(VLOOKUP(E497,機種マスタ!$K$4:$L$6,2,FALSE),0))*G497,0))</f>
         <v/>
       </c>
     </row>
@@ -17451,7 +17452,7 @@
         <v/>
       </c>
       <c r="H498" s="30">
-        <f>IF($B498="","",F498*G498)</f>
+        <f>IF($B498="","",IF(F498&gt;0,(F498+IFERROR(VLOOKUP(E498,機種マスタ!$K$4:$L$6,2,FALSE),0))*G498,0))</f>
         <v/>
       </c>
     </row>
@@ -17476,7 +17477,7 @@
         <v/>
       </c>
       <c r="H499" s="30">
-        <f>IF($B499="","",F499*G499)</f>
+        <f>IF($B499="","",IF(F499&gt;0,(F499+IFERROR(VLOOKUP(E499,機種マスタ!$K$4:$L$6,2,FALSE),0))*G499,0))</f>
         <v/>
       </c>
     </row>
@@ -17501,7 +17502,7 @@
         <v/>
       </c>
       <c r="H500" s="30">
-        <f>IF($B500="","",F500*G500)</f>
+        <f>IF($B500="","",IF(F500&gt;0,(F500+IFERROR(VLOOKUP(E500,機種マスタ!$K$4:$L$6,2,FALSE),0))*G500,0))</f>
         <v/>
       </c>
     </row>
@@ -17526,7 +17527,7 @@
         <v/>
       </c>
       <c r="H501" s="30">
-        <f>IF($B501="","",F501*G501)</f>
+        <f>IF($B501="","",IF(F501&gt;0,(F501+IFERROR(VLOOKUP(E501,機種マスタ!$K$4:$L$6,2,FALSE),0))*G501,0))</f>
         <v/>
       </c>
     </row>
@@ -17551,7 +17552,7 @@
         <v/>
       </c>
       <c r="H502" s="30">
-        <f>IF($B502="","",F502*G502)</f>
+        <f>IF($B502="","",IF(F502&gt;0,(F502+IFERROR(VLOOKUP(E502,機種マスタ!$K$4:$L$6,2,FALSE),0))*G502,0))</f>
         <v/>
       </c>
     </row>
@@ -17576,7 +17577,7 @@
         <v/>
       </c>
       <c r="H503" s="30">
-        <f>IF($B503="","",F503*G503)</f>
+        <f>IF($B503="","",IF(F503&gt;0,(F503+IFERROR(VLOOKUP(E503,機種マスタ!$K$4:$L$6,2,FALSE),0))*G503,0))</f>
         <v/>
       </c>
     </row>
@@ -17621,7 +17622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I203"/>
+  <dimension ref="A1:L203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17633,6 +17634,7 @@
     <col width="2" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="11" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17645,7 +17647,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>画像の「SB機種」一覧を登録しています。機種の追加・戦略Ptの変更は黄色いセルを編集してください(戦略Ptが空欄の機種は加算されません)。</t>
+          <t>画像の「SB機種」一覧を登録しています。機種の追加・戦略Ptの変更は黄色いセルを編集してください(戦略Ptが空欄の機種は加算されません)。機種Ptの点数(H/M/L)はK〜L列で変更できます。</t>
         </is>
       </c>
     </row>
@@ -17690,6 +17692,16 @@
         <f>SUM(F4:F203)</f>
         <v/>
       </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>機種Pt</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>点数</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="41" t="inlineStr">
@@ -17718,6 +17730,14 @@
         <f>IF($B4="","",N($D4)*E4)</f>
         <v/>
       </c>
+      <c r="K4" s="41" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L4" s="41" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="41" t="inlineStr">
@@ -17746,6 +17766,14 @@
         <f>IF($B5="","",N($D5)*E5)</f>
         <v/>
       </c>
+      <c r="K5" s="41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L5" s="41" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="41" t="inlineStr">
@@ -17773,6 +17801,14 @@
       <c r="F6" s="30">
         <f>IF($B6="","",N($D6)*E6)</f>
         <v/>
+      </c>
+      <c r="K6" s="41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L6" s="41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">

--- a/進捗確認.xlsx
+++ b/進捗確認.xlsx
@@ -14,17 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="機種マスタ" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="グラフ用" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="SB機種一覧">OFFSET(機種マスタ!$B$4,0,0,MAX(1,COUNTA(機種マスタ!$B$4:$B$363)),1)</definedName>
-    <definedName name="YM機種一覧">OFFSET(機種マスタ!$J$4,0,0,MAX(1,COUNTA(機種マスタ!$J$4:$J$203)),1)</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="yyyy&quot;年&quot;m&quot;月&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;日&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -33,7 +30,6 @@
     <numFmt numFmtId="169" formatCode="m/d(aaa)"/>
     <numFmt numFmtId="170" formatCode="yyyy/m/d"/>
     <numFmt numFmtId="171" formatCode="m/d"/>
-    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -202,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -366,6 +362,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2025,7 +2022,7 @@
     <row r="20">
       <c r="A20" s="22" t="inlineStr">
         <is>
-          <t>※ 配点は「ラダー」シートの表から、現在の達成率に対応する点数を表示します(合計点は上表の項目の合計で、店舗全体の点数ではありません)。「あと」は件数ですが、戦略機種(Pt)のみPtです。PPCD申込・SB Goldは「目標設定」に入力した申込率で判定します。</t>
+          <t>※ 配点は「ラダー」シートの表から、現在の達成率に対応する点数を表示します(合計点は上表の項目の合計で、店舗全体の点数ではありません)。「あと」は件数ですが、戦略機種(Pt)のみPtです。PPCD申込・SB Goldは「目標設定」に入力した申込率で判定します。追加項目(率を手入力する項目)の配点は、下の「追加項目」の表で別に合計します。</t>
         </is>
       </c>
     </row>
@@ -3977,55 +3974,55 @@
 (Watch)</t>
         </is>
       </c>
-      <c r="AC3" s="9" t="n"/>
-      <c r="AD3" s="9" t="n"/>
+      <c r="AC3" s="59" t="n"/>
+      <c r="AD3" s="54" t="n"/>
       <c r="AF3" s="9" t="inlineStr">
         <is>
           <t>SB通話OP
 (SB通話OP)</t>
         </is>
       </c>
-      <c r="AG3" s="9" t="n"/>
+      <c r="AG3" s="54" t="n"/>
       <c r="AI3" s="9" t="inlineStr">
         <is>
           <t>SB保証
 (SB保証)</t>
         </is>
       </c>
-      <c r="AJ3" s="9" t="n"/>
+      <c r="AJ3" s="54" t="n"/>
       <c r="AL3" s="9" t="inlineStr">
         <is>
           <t>SBセキュリティ
 (SBセキュリティ)</t>
         </is>
       </c>
-      <c r="AM3" s="9" t="n"/>
+      <c r="AM3" s="54" t="n"/>
       <c r="AO3" s="9" t="inlineStr">
         <is>
           <t>SB店スマ
 (ラダーなし)</t>
         </is>
       </c>
-      <c r="AP3" s="9" t="n"/>
+      <c r="AP3" s="54" t="n"/>
       <c r="AR3" s="9" t="inlineStr">
         <is>
           <t>SB支払設定
 (SB支払設定)</t>
         </is>
       </c>
-      <c r="AS3" s="9" t="n"/>
+      <c r="AS3" s="54" t="n"/>
       <c r="AU3" s="9" t="inlineStr">
         <is>
           <t>SBプラン × 大容量
 (ペイトク率 × 大容量率 → 配点)</t>
         </is>
       </c>
-      <c r="AV3" s="9" t="n"/>
-      <c r="AW3" s="9" t="n"/>
-      <c r="AX3" s="9" t="n"/>
-      <c r="AY3" s="9" t="n"/>
-      <c r="AZ3" s="9" t="n"/>
-      <c r="BA3" s="9" t="n"/>
+      <c r="AV3" s="59" t="n"/>
+      <c r="AW3" s="59" t="n"/>
+      <c r="AX3" s="59" t="n"/>
+      <c r="AY3" s="59" t="n"/>
+      <c r="AZ3" s="59" t="n"/>
+      <c r="BA3" s="54" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -5899,8 +5896,8 @@
   <mergeCells count="16">
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="J3:K3"/>
+    <mergeCell ref="AF3:AG3"/>
     <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="AF3:AG3"/>
     <mergeCell ref="AI3:AJ3"/>
     <mergeCell ref="AL3:AM3"/>
     <mergeCell ref="Y3:Z3"/>
@@ -19302,7 +19299,7 @@
       <formula1>"SB,YM"</formula1>
     </dataValidation>
     <dataValidation sqref="C4:C503" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="機種マスタに登録されている機種名を選んでください。" type="list">
-      <formula1>INDIRECT(IF($B4="YM","YM機種一覧","SB機種一覧"))</formula1>
+      <formula1>OFFSET(機種マスタ!$B$4,0,IF($B4="YM",8,0),MAX(1,IF($B4="YM",COUNTA(機種マスタ!$J$4:$J$203),COUNTA(機種マスタ!$B$4:$B$363))),1)</formula1>
     </dataValidation>
     <dataValidation sqref="D4:D503" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="1以上の整数を入力してください。" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>

--- a/進捗確認.xlsx
+++ b/進捗確認.xlsx
@@ -820,10 +820,10 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2736000"/>
+    <ext cx="6840000" cy="2250000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1967,289 +1967,556 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SBプラン(ペイトク)</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>IF(N(目標設定!$D$19)&gt;0,目標設定!$D$19,"-")</f>
+        <v/>
+      </c>
+      <c r="C18" s="10">
+        <f>N(目標設定!$F$19)</f>
+        <v/>
+      </c>
+      <c r="D18" s="7">
+        <f>IF(ISNUMBER(B18),C18/B18,"-")</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>IF(ISNUMBER(B18),MAX(B18-C18,0),"-")</f>
+        <v/>
+      </c>
+      <c r="F18" s="46">
+        <f>IF(ISNUMBER(B18),B18*$H$3,"-")</f>
+        <v/>
+      </c>
+      <c r="G18" s="47">
+        <f>IF(ISNUMBER(B18),C18-F18,"-")</f>
+        <v/>
+      </c>
+      <c r="H18" s="46">
+        <f>IF(ISNUMBER(B18),IF($D$3-$F$3&gt;0,E18/($D$3-$F$3),E18),"-")</f>
+        <v/>
+      </c>
+      <c r="I18" s="13">
+        <f>IF(NOT(ISNUMBER(B18)),"目標未設定",IF(C18&gt;=B18,"達成",IF(C18&gt;=F18,"順調","遅れ")))</f>
+        <v/>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>ラダーなし</t>
+        </is>
+      </c>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>SBプラン(大容量)</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <f>IF(N(目標設定!$D$20)&gt;0,目標設定!$D$20,"-")</f>
+        <v/>
+      </c>
+      <c r="C19" s="10">
+        <f>N(目標設定!$F$20)</f>
+        <v/>
+      </c>
+      <c r="D19" s="7">
+        <f>IF(ISNUMBER(B19),C19/B19,"-")</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>IF(ISNUMBER(B19),MAX(B19-C19,0),"-")</f>
+        <v/>
+      </c>
+      <c r="F19" s="46">
+        <f>IF(ISNUMBER(B19),B19*$H$3,"-")</f>
+        <v/>
+      </c>
+      <c r="G19" s="47">
+        <f>IF(ISNUMBER(B19),C19-F19,"-")</f>
+        <v/>
+      </c>
+      <c r="H19" s="46">
+        <f>IF(ISNUMBER(B19),IF($D$3-$F$3&gt;0,E19/($D$3-$F$3),E19),"-")</f>
+        <v/>
+      </c>
+      <c r="I19" s="13">
+        <f>IF(NOT(ISNUMBER(B19)),"目標未設定",IF(C19&gt;=B19,"達成",IF(C19&gt;=F19,"順調","遅れ")))</f>
+        <v/>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>ラダーなし</t>
+        </is>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SB通話OP</t>
+        </is>
+      </c>
+      <c r="B20" s="10">
+        <f>IF(N(目標設定!$D$21)&gt;0,目標設定!$D$21,"-")</f>
+        <v/>
+      </c>
+      <c r="C20" s="10">
+        <f>N(目標設定!$F$21)</f>
+        <v/>
+      </c>
+      <c r="D20" s="7">
+        <f>IF(ISNUMBER(B20),C20/B20,"-")</f>
+        <v/>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(ISNUMBER(B20),MAX(B20-C20,0),"-")</f>
+        <v/>
+      </c>
+      <c r="F20" s="46">
+        <f>IF(ISNUMBER(B20),B20*$H$3,"-")</f>
+        <v/>
+      </c>
+      <c r="G20" s="47">
+        <f>IF(ISNUMBER(B20),C20-F20,"-")</f>
+        <v/>
+      </c>
+      <c r="H20" s="46">
+        <f>IF(ISNUMBER(B20),IF($D$3-$F$3&gt;0,E20/($D$3-$F$3),E20),"-")</f>
+        <v/>
+      </c>
+      <c r="I20" s="13">
+        <f>IF(NOT(ISNUMBER(B20)),"目標未設定",IF(C20&gt;=B20,"達成",IF(C20&gt;=F20,"順調","遅れ")))</f>
+        <v/>
+      </c>
+      <c r="J20" s="14">
+        <f>IF(ISNUMBER(D20),INDEX(ラダー!$AG$5:$AG$34,MATCH(SUMPRODUCT(MAX((ラダー!$AF$5:$AF$34&lt;=ROUND(D20,6))*ラダー!$AF$5:$AF$34)),ラダー!$AF$5:$AF$34,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="K20" s="15">
+        <f>IF(ISNUMBER(D20),IFERROR(SMALL(ラダー!$AF$5:$AF$34,COUNTIF(ラダー!$AF$5:$AF$34,"&lt;="&amp;ROUND(D20,6))+1),"最高段"),"-")</f>
+        <v/>
+      </c>
+      <c r="L20" s="16">
+        <f>IF(ISNUMBER(K20),INDEX(ラダー!$AG$5:$AG$34,MATCH(K20,ラダー!$AF$5:$AF$34,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="M20" s="10">
+        <f>IF(ISNUMBER(K20),ROUNDUP(K20*B20-C20-0.000001,0),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>SB保証</t>
+        </is>
+      </c>
+      <c r="B21" s="10">
+        <f>IF(N(目標設定!$D$22)&gt;0,目標設定!$D$22,"-")</f>
+        <v/>
+      </c>
+      <c r="C21" s="10">
+        <f>N(目標設定!$F$22)</f>
+        <v/>
+      </c>
+      <c r="D21" s="7">
+        <f>IF(ISNUMBER(B21),C21/B21,"-")</f>
+        <v/>
+      </c>
+      <c r="E21" s="10">
+        <f>IF(ISNUMBER(B21),MAX(B21-C21,0),"-")</f>
+        <v/>
+      </c>
+      <c r="F21" s="46">
+        <f>IF(ISNUMBER(B21),B21*$H$3,"-")</f>
+        <v/>
+      </c>
+      <c r="G21" s="47">
+        <f>IF(ISNUMBER(B21),C21-F21,"-")</f>
+        <v/>
+      </c>
+      <c r="H21" s="46">
+        <f>IF(ISNUMBER(B21),IF($D$3-$F$3&gt;0,E21/($D$3-$F$3),E21),"-")</f>
+        <v/>
+      </c>
+      <c r="I21" s="13">
+        <f>IF(NOT(ISNUMBER(B21)),"目標未設定",IF(C21&gt;=B21,"達成",IF(C21&gt;=F21,"順調","遅れ")))</f>
+        <v/>
+      </c>
+      <c r="J21" s="14">
+        <f>IF(ISNUMBER(D21),INDEX(ラダー!$AJ$5:$AJ$34,MATCH(SUMPRODUCT(MAX((ラダー!$AI$5:$AI$34&lt;=ROUND(D21,6))*ラダー!$AI$5:$AI$34)),ラダー!$AI$5:$AI$34,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="K21" s="15">
+        <f>IF(ISNUMBER(D21),IFERROR(SMALL(ラダー!$AI$5:$AI$34,COUNTIF(ラダー!$AI$5:$AI$34,"&lt;="&amp;ROUND(D21,6))+1),"最高段"),"-")</f>
+        <v/>
+      </c>
+      <c r="L21" s="16">
+        <f>IF(ISNUMBER(K21),INDEX(ラダー!$AJ$5:$AJ$34,MATCH(K21,ラダー!$AI$5:$AI$34,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="M21" s="10">
+        <f>IF(ISNUMBER(K21),ROUNDUP(K21*B21-C21-0.000001,0),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>SBセキュリティ</t>
+        </is>
+      </c>
+      <c r="B22" s="10">
+        <f>IF(N(目標設定!$D$23)&gt;0,目標設定!$D$23,"-")</f>
+        <v/>
+      </c>
+      <c r="C22" s="10">
+        <f>N(目標設定!$F$23)</f>
+        <v/>
+      </c>
+      <c r="D22" s="7">
+        <f>IF(ISNUMBER(B22),C22/B22,"-")</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(ISNUMBER(B22),MAX(B22-C22,0),"-")</f>
+        <v/>
+      </c>
+      <c r="F22" s="46">
+        <f>IF(ISNUMBER(B22),B22*$H$3,"-")</f>
+        <v/>
+      </c>
+      <c r="G22" s="47">
+        <f>IF(ISNUMBER(B22),C22-F22,"-")</f>
+        <v/>
+      </c>
+      <c r="H22" s="46">
+        <f>IF(ISNUMBER(B22),IF($D$3-$F$3&gt;0,E22/($D$3-$F$3),E22),"-")</f>
+        <v/>
+      </c>
+      <c r="I22" s="13">
+        <f>IF(NOT(ISNUMBER(B22)),"目標未設定",IF(C22&gt;=B22,"達成",IF(C22&gt;=F22,"順調","遅れ")))</f>
+        <v/>
+      </c>
+      <c r="J22" s="14">
+        <f>IF(ISNUMBER(D22),INDEX(ラダー!$AM$5:$AM$34,MATCH(SUMPRODUCT(MAX((ラダー!$AL$5:$AL$34&lt;=ROUND(D22,6))*ラダー!$AL$5:$AL$34)),ラダー!$AL$5:$AL$34,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="K22" s="15">
+        <f>IF(ISNUMBER(D22),IFERROR(SMALL(ラダー!$AL$5:$AL$34,COUNTIF(ラダー!$AL$5:$AL$34,"&lt;="&amp;ROUND(D22,6))+1),"最高段"),"-")</f>
+        <v/>
+      </c>
+      <c r="L22" s="16">
+        <f>IF(ISNUMBER(K22),INDEX(ラダー!$AM$5:$AM$34,MATCH(K22,ラダー!$AL$5:$AL$34,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="M22" s="10">
+        <f>IF(ISNUMBER(K22),ROUNDUP(K22*B22-C22-0.000001,0),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>SB店スマ</t>
+        </is>
+      </c>
+      <c r="B23" s="10">
+        <f>IF(N(目標設定!$D$24)&gt;0,目標設定!$D$24,"-")</f>
+        <v/>
+      </c>
+      <c r="C23" s="10">
+        <f>N(目標設定!$F$24)</f>
+        <v/>
+      </c>
+      <c r="D23" s="7">
+        <f>IF(ISNUMBER(B23),C23/B23,"-")</f>
+        <v/>
+      </c>
+      <c r="E23" s="10">
+        <f>IF(ISNUMBER(B23),MAX(B23-C23,0),"-")</f>
+        <v/>
+      </c>
+      <c r="F23" s="46">
+        <f>IF(ISNUMBER(B23),B23*$H$3,"-")</f>
+        <v/>
+      </c>
+      <c r="G23" s="47">
+        <f>IF(ISNUMBER(B23),C23-F23,"-")</f>
+        <v/>
+      </c>
+      <c r="H23" s="46">
+        <f>IF(ISNUMBER(B23),IF($D$3-$F$3&gt;0,E23/($D$3-$F$3),E23),"-")</f>
+        <v/>
+      </c>
+      <c r="I23" s="13">
+        <f>IF(NOT(ISNUMBER(B23)),"目標未設定",IF(C23&gt;=B23,"達成",IF(C23&gt;=F23,"順調","遅れ")))</f>
+        <v/>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>ラダーなし</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>SB支払設定</t>
+        </is>
+      </c>
+      <c r="B24" s="10">
+        <f>IF(N(目標設定!$D$25)&gt;0,目標設定!$D$25,"-")</f>
+        <v/>
+      </c>
+      <c r="C24" s="10">
+        <f>N(目標設定!$F$25)</f>
+        <v/>
+      </c>
+      <c r="D24" s="7">
+        <f>IF(ISNUMBER(B24),C24/B24,"-")</f>
+        <v/>
+      </c>
+      <c r="E24" s="10">
+        <f>IF(ISNUMBER(B24),MAX(B24-C24,0),"-")</f>
+        <v/>
+      </c>
+      <c r="F24" s="46">
+        <f>IF(ISNUMBER(B24),B24*$H$3,"-")</f>
+        <v/>
+      </c>
+      <c r="G24" s="47">
+        <f>IF(ISNUMBER(B24),C24-F24,"-")</f>
+        <v/>
+      </c>
+      <c r="H24" s="46">
+        <f>IF(ISNUMBER(B24),IF($D$3-$F$3&gt;0,E24/($D$3-$F$3),E24),"-")</f>
+        <v/>
+      </c>
+      <c r="I24" s="13">
+        <f>IF(NOT(ISNUMBER(B24)),"目標未設定",IF(C24&gt;=B24,"達成",IF(C24&gt;=F24,"順調","遅れ")))</f>
+        <v/>
+      </c>
+      <c r="J24" s="14">
+        <f>IF(ISNUMBER(D24),INDEX(ラダー!$AS$5:$AS$34,MATCH(SUMPRODUCT(MAX((ラダー!$AR$5:$AR$34&lt;=ROUND(D24,6))*ラダー!$AR$5:$AR$34)),ラダー!$AR$5:$AR$34,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="K24" s="15">
+        <f>IF(ISNUMBER(D24),IFERROR(SMALL(ラダー!$AR$5:$AR$34,COUNTIF(ラダー!$AR$5:$AR$34,"&lt;="&amp;ROUND(D24,6))+1),"最高段"),"-")</f>
+        <v/>
+      </c>
+      <c r="L24" s="16">
+        <f>IF(ISNUMBER(K24),INDEX(ラダー!$AS$5:$AS$34,MATCH(K24,ラダー!$AR$5:$AR$34,0)),"-")</f>
+        <v/>
+      </c>
+      <c r="M24" s="10">
+        <f>IF(ISNUMBER(K24),ROUNDUP(K24*B24-C24-0.000001,0),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>合計(目標設定済み項目)</t>
         </is>
       </c>
-      <c r="B18" s="18">
-        <f>SUMIF(目標設定!$D$7:$D$18,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="C18" s="18">
-        <f>SUMIF($B6:$B17,"&gt;0",$C6:$C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="19">
-        <f>IF(B18&gt;0,C18/B18,"-")</f>
-        <v/>
-      </c>
-      <c r="E18" s="18">
-        <f>MAX(B18-C18,0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="48">
-        <f>B18*$H$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="49">
-        <f>C18-F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="48">
-        <f>IF($D$3-$F$3&gt;0,E18/($D$3-$F$3),E18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="17">
-        <f>IF(B18=0,"-",IF(C18&gt;=B18,"達成",IF(C18&gt;=F18,"順調","遅れ")))</f>
-        <v/>
-      </c>
-      <c r="J18" s="17">
-        <f>SUM(J6:J17)</f>
-        <v/>
-      </c>
-      <c r="K18" s="17" t="n"/>
-      <c r="L18" s="17" t="n"/>
-      <c r="M18" s="17" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="B25" s="18">
+        <f>SUMIF(目標設定!$D$7:$D$25,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="C25" s="18">
+        <f>SUMIF($B6:$B24,"&gt;0",$C6:$C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="19">
+        <f>IF(B25&gt;0,C25/B25,"-")</f>
+        <v/>
+      </c>
+      <c r="E25" s="18">
+        <f>MAX(B25-C25,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="48">
+        <f>B25*$H$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="49">
+        <f>C25-F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="48">
+        <f>IF($D$3-$F$3&gt;0,E25/($D$3-$F$3),E25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>IF(B25=0,"-",IF(C25&gt;=B25,"達成",IF(C25&gt;=F25,"順調","遅れ")))</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>SUM(J6:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="17" t="n"/>
+      <c r="L25" s="17" t="n"/>
+      <c r="M25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>※ 達成率=累計実績÷月間目標 / 残数=目標−実績 / 判定:実績≧目標→達成、実績≧理想ペース→順調、それ以外→遅れ</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>※ 配点は「ラダー」シートの表から、現在の達成率に対応する点数を表示します(合計点は上表の項目の合計で、店舗全体の点数ではありません)。「あと」は件数ですが、戦略機種(Pt)のみPtです。PPCD申込・SB Goldは「目標設定」に入力した申込率で判定します。追加項目(率を手入力する項目)の配点は、下の「追加項目」の表で別に合計します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>※ 配点は「ラダー」シートの表から、現在の達成率に対応する点数を表示します(合計点は上表の項目の合計で、店舗全体の点数ではありません)。「あと」は件数ですが、戦略機種(Pt)のみPtです。PPCD申込・SB Goldは「目標設定」に入力した申込率で判定します。No.13〜19(SBプラン〜SB支払設定)は日別入力がなく、「目標設定」シートの目標(D列)と実績(F列)を手入力した数値で計算します(SBプラン・SB店スマはラダーなし)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>■ 戦略機種 点数(現時点)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>現在の戦略Pt(点数)</t>
         </is>
       </c>
-      <c r="B22" s="24">
+      <c r="B29" s="24">
         <f>C13</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>戦略対象機種の販売台数</t>
         </is>
       </c>
-      <c r="B23" s="25">
+      <c r="B30" s="25">
         <f>機種販売入力!L4</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>最終入力日の加算Pt</t>
         </is>
       </c>
-      <c r="B24" s="25">
+      <c r="B31" s="25">
         <f>IF($F$3&gt;0,INDEX(J42:J72,$F$3),0)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>戦略Pt目標</t>
         </is>
       </c>
-      <c r="B25" s="25">
+      <c r="B32" s="25">
         <f>B13</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>点数達成率(Pt÷目標)</t>
         </is>
       </c>
-      <c r="B26" s="26">
+      <c r="B33" s="26">
         <f>D13</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>残りPt</t>
         </is>
       </c>
-      <c r="B27" s="25">
+      <c r="B34" s="25">
         <f>E13</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>販売日 未入力の行数</t>
         </is>
       </c>
-      <c r="B28" s="27">
+      <c r="B35" s="27">
         <f>機種販売入力!L6</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>※ 点数は「機種販売入力」で選んだ機種の(機種Pt+戦略Pt)×台数の合計です(機種ごとの内訳は「機種マスタ」)。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>■ 追加項目(率を手入力した項目の配点)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>手入力の率</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>現在の配点</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>SBプラン(ペイトク×大容量)</t>
-        </is>
-      </c>
-      <c r="B32" s="50">
-        <f>IF(AND(ISNUMBER(目標設定!$F$19),ISNUMBER(目標設定!$F$20)),TEXT(目標設定!$F$19,"0%")&amp;" / "&amp;TEXT(目標設定!$F$20,"0%"),"-")</f>
-        <v/>
-      </c>
-      <c r="C32" s="14">
-        <f>IFERROR(IF(AND(ISNUMBER(目標設定!$F$19),ISNUMBER(目標設定!$F$20)),INDEX(ラダー!$AV$5:$BA$10,MATCH(ROUND(目標設定!$F$19,6),ラダー!$AU$5:$AU$10,1),MATCH(ROUND(目標設定!$F$20,6),ラダー!$AV$4:$BA$4,1)),"-"),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>SB通話OP</t>
-        </is>
-      </c>
-      <c r="B33" s="51">
-        <f>IF(ISNUMBER(目標設定!$F$21),目標設定!$F$21,"-")</f>
-        <v/>
-      </c>
-      <c r="C33" s="14">
-        <f>IFERROR(IF(ISNUMBER(B33),INDEX(ラダー!$AG$5:$AG$34,MATCH(SUMPRODUCT(MAX((ラダー!$AF$5:$AF$34&lt;=ROUND(B33,6))*ラダー!$AF$5:$AF$34)),ラダー!$AF$5:$AF$34,0)),"-"),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>SB保証</t>
-        </is>
-      </c>
-      <c r="B34" s="51">
-        <f>IF(ISNUMBER(目標設定!$F$22),目標設定!$F$22,"-")</f>
-        <v/>
-      </c>
-      <c r="C34" s="14">
-        <f>IFERROR(IF(ISNUMBER(B34),INDEX(ラダー!$AJ$5:$AJ$34,MATCH(SUMPRODUCT(MAX((ラダー!$AI$5:$AI$34&lt;=ROUND(B34,6))*ラダー!$AI$5:$AI$34)),ラダー!$AI$5:$AI$34,0)),"-"),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>SBセキュリティ</t>
-        </is>
-      </c>
-      <c r="B35" s="51">
-        <f>IF(ISNUMBER(目標設定!$F$23),目標設定!$F$23,"-")</f>
-        <v/>
-      </c>
-      <c r="C35" s="14">
-        <f>IFERROR(IF(ISNUMBER(B35),INDEX(ラダー!$AM$5:$AM$34,MATCH(SUMPRODUCT(MAX((ラダー!$AL$5:$AL$34&lt;=ROUND(B35,6))*ラダー!$AL$5:$AL$34)),ラダー!$AL$5:$AL$34,0)),"-"),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>SB店スマ</t>
-        </is>
-      </c>
-      <c r="B36" s="51">
-        <f>IF(ISNUMBER(目標設定!$F$24),目標設定!$F$24,"-")</f>
-        <v/>
-      </c>
-      <c r="C36" s="14">
-        <f>IFERROR(IF(ISNUMBER(B36),INDEX(ラダー!$AP$5:$AP$34,MATCH(SUMPRODUCT(MAX((ラダー!$AO$5:$AO$34&lt;=ROUND(B36,6))*ラダー!$AO$5:$AO$34)),ラダー!$AO$5:$AO$34,0)),"-"),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SB支払設定</t>
-        </is>
-      </c>
-      <c r="B37" s="51">
-        <f>IF(ISNUMBER(目標設定!$F$25),目標設定!$F$25,"-")</f>
-        <v/>
-      </c>
-      <c r="C37" s="14">
-        <f>IFERROR(IF(ISNUMBER(B37),INDEX(ラダー!$AS$5:$AS$34,MATCH(SUMPRODUCT(MAX((ラダー!$AR$5:$AR$34&lt;=ROUND(B37,6))*ラダー!$AR$5:$AR$34)),ラダー!$AR$5:$AR$34,0)),"-"),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>追加項目 合計</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="n"/>
-      <c r="C38" s="52">
-        <f>SUM(C32:C37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>※ 率は「目標設定」シートの右端の列に手入力します。配点は「ラダー」シートの表から判定します(SB店スマはラダーなし)。</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
         <is>
@@ -3312,7 +3579,7 @@
   <mergeCells count="1">
     <mergeCell ref="A73:B73"/>
   </mergeCells>
-  <conditionalFormatting sqref="I6:I18">
+  <conditionalFormatting sqref="I6:I25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"達成"</formula>
     </cfRule>
@@ -3326,12 +3593,12 @@
       <formula>"目標未設定"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G18">
+  <conditionalFormatting sqref="G6:G25">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>AND(ISNUMBER(G6),G6&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B35">
     <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -3415,7 +3682,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>No.</t>
@@ -3438,8 +3705,8 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>ラダー判定用の率
-(手入力)</t>
+          <t>手入力欄
+(No.6・7=率 / No.13〜19=実績の数値)</t>
         </is>
       </c>
     </row>
@@ -3661,17 +3928,13 @@
 (ペイトク率)</t>
         </is>
       </c>
-      <c r="D19" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D19" s="33" t="n"/>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>ペイトク率を右の列に手入力</t>
-        </is>
-      </c>
-      <c r="F19" s="35" t="n"/>
+          <t>目標=D列、実績=F列に数値を手入力(ラダーなし)</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="13" t="n">
@@ -3683,17 +3946,13 @@
 (大容量率)</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D20" s="33" t="n"/>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>大容量率を右の列に手入力</t>
-        </is>
-      </c>
-      <c r="F20" s="35" t="n"/>
+          <t>目標=D列、実績=F列に数値を手入力(ラダーなし)</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="13" t="n">
@@ -3704,17 +3963,13 @@
           <t>SB通話OP</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D21" s="33" t="n"/>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>加入率を右の列に手入力</t>
-        </is>
-      </c>
-      <c r="F21" s="35" t="n"/>
+          <t>目標=D列、実績=F列に数値を手入力</t>
+        </is>
+      </c>
+      <c r="F21" s="33" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="13" t="n">
@@ -3725,17 +3980,13 @@
           <t>SB保証</t>
         </is>
       </c>
-      <c r="D22" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D22" s="33" t="n"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>加入率を右の列に手入力</t>
-        </is>
-      </c>
-      <c r="F22" s="35" t="n"/>
+          <t>目標=D列、実績=F列に数値を手入力</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="13" t="n">
@@ -3746,19 +3997,15 @@
           <t>SBセキュリティ</t>
         </is>
       </c>
-      <c r="D23" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D23" s="33" t="n"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>加入率を右の列に手入力</t>
-        </is>
-      </c>
-      <c r="F23" s="35" t="n"/>
-    </row>
-    <row r="24">
+          <t>目標=D列、実績=F列に数値を手入力</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="B24" s="13" t="n">
         <v>18</v>
       </c>
@@ -3767,17 +4014,13 @@
           <t>SB店スマ</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D24" s="33" t="n"/>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>率を右の列に手入力(ラダーなし)</t>
-        </is>
-      </c>
-      <c r="F24" s="35" t="n"/>
+          <t>目標=D列、実績=F列に数値を手入力(ラダーなし)</t>
+        </is>
+      </c>
+      <c r="F24" s="33" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="13" t="n">
@@ -3788,17 +4031,13 @@
           <t>SB支払設定</t>
         </is>
       </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="D25" s="33" t="n"/>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>設定率を右の列に手入力</t>
-        </is>
-      </c>
-      <c r="F25" s="35" t="n"/>
+          <t>目標=D列、実績=F列に数値を手入力</t>
+        </is>
+      </c>
+      <c r="F25" s="33" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="22" t="inlineStr">
@@ -3817,7 +4056,7 @@
     <row r="29">
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>※ No.13〜19は追加項目です。右端の列に率を手入力すると、「ラダー」シートの表から配点を判定し、「進捗確認」シートの「追加項目」に表示します。SBプランはペイトク率と大容量率の2つで配点が決まります。</t>
+          <t>※ No.13〜19は追加項目です。目標(D列)と実績(F列)に数値を手入力すると、「進捗確認」シートのYouTubeと合計の間に達成率・残数・判定などを表示します(SB通話OP・SB保証・SBセキュリティ・SB支払設定は、達成率に対応する配点も「ラダー」シートから表示)。</t>
         </is>
       </c>
     </row>
